--- a/input/reg_leave_parental_home.xlsx
+++ b/input/reg_leave_parental_home.xlsx
@@ -9,13 +9,14 @@
   <sheets>
     <sheet name="P1a" sheetId="1" r:id="rId1"/>
     <sheet name="Gof" sheetId="2" r:id="rId2"/>
+    <sheet name="UK_P1a" sheetId="3" r:id="rId6"/>
   </sheets>
   <calcPr calcId="0" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="66">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -219,7 +220,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="250">
+  <fonts count="254">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -1201,6 +1202,26 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <b/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1242,7 +1263,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="245">
+  <borders count="247">
     <border>
       <left/>
       <right/>
@@ -2958,11 +2979,25 @@
       <bottom style="none"/>
       <diagonal style="none"/>
     </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
+    <border>
+      <left style="none"/>
+      <right style="none"/>
+      <top style="none"/>
+      <bottom style="none"/>
+      <diagonal style="none"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="247">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true"/>
@@ -3760,6 +3795,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="0" fontId="249" fillId="0" borderId="244" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="251" fillId="0" borderId="245" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="253" fillId="0" borderId="246" xfId="0" applyNumberFormat="true" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -6961,7 +7004,7 @@
   </cols>
   <sheetData>
     <row r="3">
-      <c r="A3" s="244" t="s">
+      <c r="A3" s="246" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6970,13 +7013,13 @@
         <v>30</v>
       </c>
       <c r="B5">
-        <v>0.043119601598717527</v>
+        <v>0.043286872598459425</v>
       </c>
       <c r="E5" t="s">
         <v>32</v>
       </c>
       <c r="F5">
-        <v>405.1082203491747</v>
+        <v>403.3238013905825</v>
       </c>
     </row>
     <row r="6">
@@ -6984,16 +7027,2875 @@
         <v>31</v>
       </c>
       <c r="B6">
-        <v>28960</v>
+        <v>28955</v>
       </c>
       <c r="E6" t="s">
         <v>33</v>
       </c>
       <c r="F6">
-        <v>-6388.1855597765943</v>
+        <v>-6386.7241757287529</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AE30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" t="s">
+        <v>12</v>
+      </c>
+      <c r="O1" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" t="s">
+        <v>14</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>15</v>
+      </c>
+      <c r="R1" t="s">
+        <v>16</v>
+      </c>
+      <c r="S1" t="s">
+        <v>17</v>
+      </c>
+      <c r="T1" t="s">
+        <v>18</v>
+      </c>
+      <c r="U1" t="s">
+        <v>19</v>
+      </c>
+      <c r="V1" t="s">
+        <v>20</v>
+      </c>
+      <c r="W1" t="s">
+        <v>21</v>
+      </c>
+      <c r="X1" t="s">
+        <v>22</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>64</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>65</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>-0.28298153112230012</v>
+      </c>
+      <c r="C2">
+        <v>0.00089110776221820688</v>
+      </c>
+      <c r="D2">
+        <v>-2.6544044504785201e-005</v>
+      </c>
+      <c r="E2">
+        <v>3.1465375280620552e-007</v>
+      </c>
+      <c r="F2">
+        <v>-0.00011904561676683809</v>
+      </c>
+      <c r="G2">
+        <v>-0.00014292808597463319</v>
+      </c>
+      <c r="H2">
+        <v>9.6861969303827842e-005</v>
+      </c>
+      <c r="I2">
+        <v>2.408016643033453e-005</v>
+      </c>
+      <c r="J2">
+        <v>0.00013622279815488845</v>
+      </c>
+      <c r="K2">
+        <v>0.00014200205900610137</v>
+      </c>
+      <c r="L2">
+        <v>6.0594948023574949e-005</v>
+      </c>
+      <c r="M2">
+        <v>5.2021065018809095e-006</v>
+      </c>
+      <c r="N2">
+        <v>-5.8460765848974088e-005</v>
+      </c>
+      <c r="O2">
+        <v>3.0247009458892162e-005</v>
+      </c>
+      <c r="P2">
+        <v>-3.9283592258444852e-006</v>
+      </c>
+      <c r="Q2">
+        <v>-6.2379929981665888e-005</v>
+      </c>
+      <c r="R2">
+        <v>3.371067614290426e-005</v>
+      </c>
+      <c r="S2">
+        <v>-7.9844343404750182e-005</v>
+      </c>
+      <c r="T2">
+        <v>5.0363820741853534e-005</v>
+      </c>
+      <c r="U2">
+        <v>0.00011181013736597909</v>
+      </c>
+      <c r="V2">
+        <v>1.402536366660787e-006</v>
+      </c>
+      <c r="W2">
+        <v>0.00010647482951627222</v>
+      </c>
+      <c r="X2">
+        <v>3.4137192050686459e-005</v>
+      </c>
+      <c r="Y2">
+        <v>-4.9311556265419157e-006</v>
+      </c>
+      <c r="Z2">
+        <v>-1.0787907954078364e-005</v>
+      </c>
+      <c r="AA2">
+        <v>2.2157136138186527e-005</v>
+      </c>
+      <c r="AB2">
+        <v>5.4924177902638074e-005</v>
+      </c>
+      <c r="AC2">
+        <v>-3.6713838358304692e-005</v>
+      </c>
+      <c r="AD2">
+        <v>-2.4540986930661353e-005</v>
+      </c>
+      <c r="AE2">
+        <v>8.3440410491761433e-005</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>-0.02160945461231507</v>
+      </c>
+      <c r="C3">
+        <v>-2.6544044504785201e-005</v>
+      </c>
+      <c r="D3">
+        <v>8.5681188587438805e-005</v>
+      </c>
+      <c r="E3">
+        <v>-1.1154943446824942e-006</v>
+      </c>
+      <c r="F3">
+        <v>6.3744542601724949e-005</v>
+      </c>
+      <c r="G3">
+        <v>5.5397598361516881e-005</v>
+      </c>
+      <c r="H3">
+        <v>0.00017549860209374393</v>
+      </c>
+      <c r="I3">
+        <v>0.00012426242944792406</v>
+      </c>
+      <c r="J3">
+        <v>0.00011385949208549752</v>
+      </c>
+      <c r="K3">
+        <v>0.00012552472889933991</v>
+      </c>
+      <c r="L3">
+        <v>8.5027124691176978e-005</v>
+      </c>
+      <c r="M3">
+        <v>9.6174226206568916e-005</v>
+      </c>
+      <c r="N3">
+        <v>-1.2476099615596134e-005</v>
+      </c>
+      <c r="O3">
+        <v>1.6043452185874325e-005</v>
+      </c>
+      <c r="P3">
+        <v>-6.0676156975564911e-006</v>
+      </c>
+      <c r="Q3">
+        <v>-1.1433032268695024e-005</v>
+      </c>
+      <c r="R3">
+        <v>-1.6643981312167935e-005</v>
+      </c>
+      <c r="S3">
+        <v>5.8307866221793847e-006</v>
+      </c>
+      <c r="T3">
+        <v>-1.9325727017326707e-006</v>
+      </c>
+      <c r="U3">
+        <v>8.9406633026548055e-007</v>
+      </c>
+      <c r="V3">
+        <v>-1.2095390647407162e-006</v>
+      </c>
+      <c r="W3">
+        <v>1.3349872169014538e-005</v>
+      </c>
+      <c r="X3">
+        <v>-1.1630343278863121e-005</v>
+      </c>
+      <c r="Y3">
+        <v>-7.1365286076810995e-008</v>
+      </c>
+      <c r="Z3">
+        <v>-4.2550648915218493e-006</v>
+      </c>
+      <c r="AA3">
+        <v>-7.2023131823159672e-006</v>
+      </c>
+      <c r="AB3">
+        <v>-2.1692380901941304e-005</v>
+      </c>
+      <c r="AC3">
+        <v>-2.6876023877973063e-005</v>
+      </c>
+      <c r="AD3">
+        <v>-5.2129313585139018e-006</v>
+      </c>
+      <c r="AE3">
+        <v>-0.0015548025461564691</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>0.00044385961479229981</v>
+      </c>
+      <c r="C4">
+        <v>3.1465375280620552e-007</v>
+      </c>
+      <c r="D4">
+        <v>-1.1154943446824942e-006</v>
+      </c>
+      <c r="E4">
+        <v>1.4918246609606314e-008</v>
+      </c>
+      <c r="F4">
+        <v>-7.7221376096502976e-007</v>
+      </c>
+      <c r="G4">
+        <v>-9.6484803822887851e-007</v>
+      </c>
+      <c r="H4">
+        <v>-2.0849610975567778e-006</v>
+      </c>
+      <c r="I4">
+        <v>-1.6025920581141122e-006</v>
+      </c>
+      <c r="J4">
+        <v>-1.4070508293908467e-006</v>
+      </c>
+      <c r="K4">
+        <v>-1.5666899560463831e-006</v>
+      </c>
+      <c r="L4">
+        <v>-1.1125734132390706e-006</v>
+      </c>
+      <c r="M4">
+        <v>-1.3396437273161059e-006</v>
+      </c>
+      <c r="N4">
+        <v>5.2323666850330862e-008</v>
+      </c>
+      <c r="O4">
+        <v>-3.283959955332303e-007</v>
+      </c>
+      <c r="P4">
+        <v>-3.5020463021728397e-008</v>
+      </c>
+      <c r="Q4">
+        <v>6.3337015300660282e-009</v>
+      </c>
+      <c r="R4">
+        <v>1.2821859060781969e-007</v>
+      </c>
+      <c r="S4">
+        <v>-1.9439998583913155e-007</v>
+      </c>
+      <c r="T4">
+        <v>-8.0307127386476586e-009</v>
+      </c>
+      <c r="U4">
+        <v>-1.5962950008511749e-007</v>
+      </c>
+      <c r="V4">
+        <v>-1.2355250592429246e-007</v>
+      </c>
+      <c r="W4">
+        <v>-3.5065492590082775e-007</v>
+      </c>
+      <c r="X4">
+        <v>3.1396265845078558e-008</v>
+      </c>
+      <c r="Y4">
+        <v>4.2307766369329244e-010</v>
+      </c>
+      <c r="Z4">
+        <v>7.5553596077281995e-008</v>
+      </c>
+      <c r="AA4">
+        <v>1.0187974634759229e-007</v>
+      </c>
+      <c r="AB4">
+        <v>3.4920146561629916e-007</v>
+      </c>
+      <c r="AC4">
+        <v>3.1108552852123559e-007</v>
+      </c>
+      <c r="AD4">
+        <v>1.0003781509743627e-007</v>
+      </c>
+      <c r="AE4">
+        <v>1.9938384833170706e-005</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>-0.27308596608915003</v>
+      </c>
+      <c r="C5">
+        <v>-0.00011904561676683809</v>
+      </c>
+      <c r="D5">
+        <v>6.3744542601724949e-005</v>
+      </c>
+      <c r="E5">
+        <v>-7.7221376096502976e-007</v>
+      </c>
+      <c r="F5">
+        <v>0.0011790775897404465</v>
+      </c>
+      <c r="G5">
+        <v>0.00082058018436639174</v>
+      </c>
+      <c r="H5">
+        <v>2.6744849370859467e-005</v>
+      </c>
+      <c r="I5">
+        <v>-3.0857159342256938e-005</v>
+      </c>
+      <c r="J5">
+        <v>3.7535320455825286e-005</v>
+      </c>
+      <c r="K5">
+        <v>-1.5312320586813679e-005</v>
+      </c>
+      <c r="L5">
+        <v>4.3233737276070759e-005</v>
+      </c>
+      <c r="M5">
+        <v>6.9544730385728254e-005</v>
+      </c>
+      <c r="N5">
+        <v>4.956082152354443e-005</v>
+      </c>
+      <c r="O5">
+        <v>-2.7822229458093753e-005</v>
+      </c>
+      <c r="P5">
+        <v>-0.00010693377281242433</v>
+      </c>
+      <c r="Q5">
+        <v>-0.00025150836900189312</v>
+      </c>
+      <c r="R5">
+        <v>-3.3272320010768213e-005</v>
+      </c>
+      <c r="S5">
+        <v>6.7365303395574129e-005</v>
+      </c>
+      <c r="T5">
+        <v>2.6094426833276458e-005</v>
+      </c>
+      <c r="U5">
+        <v>-0.0002206694084850991</v>
+      </c>
+      <c r="V5">
+        <v>-0.00011589134803618127</v>
+      </c>
+      <c r="W5">
+        <v>-4.8241457278754929e-005</v>
+      </c>
+      <c r="X5">
+        <v>3.0755205554420855e-005</v>
+      </c>
+      <c r="Y5">
+        <v>4.408407015140093e-006</v>
+      </c>
+      <c r="Z5">
+        <v>7.6141975321154408e-005</v>
+      </c>
+      <c r="AA5">
+        <v>4.8533594174586368e-005</v>
+      </c>
+      <c r="AB5">
+        <v>0.00037316560902281</v>
+      </c>
+      <c r="AC5">
+        <v>0.00013942371223252866</v>
+      </c>
+      <c r="AD5">
+        <v>0.00011456336596575144</v>
+      </c>
+      <c r="AE5">
+        <v>-0.0019188094309747551</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>-0.3161660199740603</v>
+      </c>
+      <c r="C6">
+        <v>-0.00014292808597463319</v>
+      </c>
+      <c r="D6">
+        <v>5.5397598361516881e-005</v>
+      </c>
+      <c r="E6">
+        <v>-9.6484803822887851e-007</v>
+      </c>
+      <c r="F6">
+        <v>0.00082058018436639174</v>
+      </c>
+      <c r="G6">
+        <v>0.004516504072386688</v>
+      </c>
+      <c r="H6">
+        <v>-4.1007402414743044e-005</v>
+      </c>
+      <c r="I6">
+        <v>-0.00048361038973112415</v>
+      </c>
+      <c r="J6">
+        <v>0.00017416652531129702</v>
+      </c>
+      <c r="K6">
+        <v>0.00017774139871740336</v>
+      </c>
+      <c r="L6">
+        <v>0.00026291642830834536</v>
+      </c>
+      <c r="M6">
+        <v>0.00045040330324155268</v>
+      </c>
+      <c r="N6">
+        <v>0.00054196043158473515</v>
+      </c>
+      <c r="O6">
+        <v>0.0003127618921197168</v>
+      </c>
+      <c r="P6">
+        <v>0.00026323417279885047</v>
+      </c>
+      <c r="Q6">
+        <v>0.00010850463840107411</v>
+      </c>
+      <c r="R6">
+        <v>0.0001576780104881896</v>
+      </c>
+      <c r="S6">
+        <v>-2.4178292399237043e-005</v>
+      </c>
+      <c r="T6">
+        <v>0.00038106740814587302</v>
+      </c>
+      <c r="U6">
+        <v>0.00011310756309257089</v>
+      </c>
+      <c r="V6">
+        <v>0.00010918605240317506</v>
+      </c>
+      <c r="W6">
+        <v>0.00018791140235520796</v>
+      </c>
+      <c r="X6">
+        <v>9.1101634324794846e-005</v>
+      </c>
+      <c r="Y6">
+        <v>2.8441285669955818e-005</v>
+      </c>
+      <c r="Z6">
+        <v>-8.8374269448711788e-005</v>
+      </c>
+      <c r="AA6">
+        <v>-9.9243764042209544e-005</v>
+      </c>
+      <c r="AB6">
+        <v>0.0004015496887424504</v>
+      </c>
+      <c r="AC6">
+        <v>0.00028220509488973962</v>
+      </c>
+      <c r="AD6">
+        <v>0.00032305895848009123</v>
+      </c>
+      <c r="AE6">
+        <v>-0.0022087242446957389</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>-0.17485756868852073</v>
+      </c>
+      <c r="C7">
+        <v>9.6861969303827842e-005</v>
+      </c>
+      <c r="D7">
+        <v>0.00017549860209374393</v>
+      </c>
+      <c r="E7">
+        <v>-2.0849610975567778e-006</v>
+      </c>
+      <c r="F7">
+        <v>2.6744849370859467e-005</v>
+      </c>
+      <c r="G7">
+        <v>-4.1007402414743044e-005</v>
+      </c>
+      <c r="H7">
+        <v>0.0021518971114249559</v>
+      </c>
+      <c r="I7">
+        <v>0.0009693001240384119</v>
+      </c>
+      <c r="J7">
+        <v>0.00071660760077077424</v>
+      </c>
+      <c r="K7">
+        <v>0.0009820304924515928</v>
+      </c>
+      <c r="L7">
+        <v>0.0008330319685443732</v>
+      </c>
+      <c r="M7">
+        <v>0.00049302754983907287</v>
+      </c>
+      <c r="N7">
+        <v>-0.0001964961054141325</v>
+      </c>
+      <c r="O7">
+        <v>-3.8914182525600456e-005</v>
+      </c>
+      <c r="P7">
+        <v>-0.00013125257370743615</v>
+      </c>
+      <c r="Q7">
+        <v>-0.00011434119118769145</v>
+      </c>
+      <c r="R7">
+        <v>-0.00020507560406223687</v>
+      </c>
+      <c r="S7">
+        <v>-0.00018479037067188676</v>
+      </c>
+      <c r="T7">
+        <v>-9.9085484095743476e-005</v>
+      </c>
+      <c r="U7">
+        <v>-2.5202366787791214e-005</v>
+      </c>
+      <c r="V7">
+        <v>1.6753080447032276e-005</v>
+      </c>
+      <c r="W7">
+        <v>-4.5216342418121901e-005</v>
+      </c>
+      <c r="X7">
+        <v>-9.10004407589011e-005</v>
+      </c>
+      <c r="Y7">
+        <v>1.8184367273823686e-006</v>
+      </c>
+      <c r="Z7">
+        <v>-0.00015674405732034628</v>
+      </c>
+      <c r="AA7">
+        <v>-0.00011260891038819504</v>
+      </c>
+      <c r="AB7">
+        <v>2.8270173464144902e-005</v>
+      </c>
+      <c r="AC7">
+        <v>2.4024677142782044e-006</v>
+      </c>
+      <c r="AD7">
+        <v>7.7295078950241321e-005</v>
+      </c>
+      <c r="AE7">
+        <v>-0.0042096053654617407</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>-0.15143953574978394</v>
+      </c>
+      <c r="C8">
+        <v>2.408016643033453e-005</v>
+      </c>
+      <c r="D8">
+        <v>0.00012426242944792406</v>
+      </c>
+      <c r="E8">
+        <v>-1.6025920581141122e-006</v>
+      </c>
+      <c r="F8">
+        <v>-3.0857159342256938e-005</v>
+      </c>
+      <c r="G8">
+        <v>-0.00048361038973112415</v>
+      </c>
+      <c r="H8">
+        <v>0.0009693001240384119</v>
+      </c>
+      <c r="I8">
+        <v>0.0024356421913506255</v>
+      </c>
+      <c r="J8">
+        <v>0.0013568239352809625</v>
+      </c>
+      <c r="K8">
+        <v>0.0015752242186613807</v>
+      </c>
+      <c r="L8">
+        <v>0.0014222604352087536</v>
+      </c>
+      <c r="M8">
+        <v>0.0011174131917346905</v>
+      </c>
+      <c r="N8">
+        <v>-0.00030541338284988378</v>
+      </c>
+      <c r="O8">
+        <v>-3.9453299579033946e-005</v>
+      </c>
+      <c r="P8">
+        <v>-0.00018665813198023243</v>
+      </c>
+      <c r="Q8">
+        <v>-0.00030188682534425205</v>
+      </c>
+      <c r="R8">
+        <v>-0.0002448243328716752</v>
+      </c>
+      <c r="S8">
+        <v>-4.9582572285289389e-006</v>
+      </c>
+      <c r="T8">
+        <v>-1.696163585917967e-005</v>
+      </c>
+      <c r="U8">
+        <v>-0.00018164059965022759</v>
+      </c>
+      <c r="V8">
+        <v>-0.0001131500937367972</v>
+      </c>
+      <c r="W8">
+        <v>-2.7302839536066633e-006</v>
+      </c>
+      <c r="X8">
+        <v>-0.00010408440354341434</v>
+      </c>
+      <c r="Y8">
+        <v>-1.9514786708447915e-006</v>
+      </c>
+      <c r="Z8">
+        <v>-0.00017436455763986363</v>
+      </c>
+      <c r="AA8">
+        <v>-7.3580414676958905e-005</v>
+      </c>
+      <c r="AB8">
+        <v>0.00010586853365773504</v>
+      </c>
+      <c r="AC8">
+        <v>1.7808302128676477e-005</v>
+      </c>
+      <c r="AD8">
+        <v>0.00026501419097670845</v>
+      </c>
+      <c r="AE8">
+        <v>-0.0036083293383268635</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>-0.1714112645250187</v>
+      </c>
+      <c r="C9">
+        <v>0.00013622279815488845</v>
+      </c>
+      <c r="D9">
+        <v>0.00011385949208549752</v>
+      </c>
+      <c r="E9">
+        <v>-1.4070508293908467e-006</v>
+      </c>
+      <c r="F9">
+        <v>3.7535320455825286e-005</v>
+      </c>
+      <c r="G9">
+        <v>0.00017416652531129702</v>
+      </c>
+      <c r="H9">
+        <v>0.00071660760077077424</v>
+      </c>
+      <c r="I9">
+        <v>0.0013568239352809625</v>
+      </c>
+      <c r="J9">
+        <v>0.0029231968465299792</v>
+      </c>
+      <c r="K9">
+        <v>0.0019542057228681556</v>
+      </c>
+      <c r="L9">
+        <v>0.0018345283351852298</v>
+      </c>
+      <c r="M9">
+        <v>0.0016747211947203192</v>
+      </c>
+      <c r="N9">
+        <v>0.00028810419402787598</v>
+      </c>
+      <c r="O9">
+        <v>2.4445006637660718e-005</v>
+      </c>
+      <c r="P9">
+        <v>-2.5700361891442026e-005</v>
+      </c>
+      <c r="Q9">
+        <v>-0.00025237003667107777</v>
+      </c>
+      <c r="R9">
+        <v>-0.00028238373315389939</v>
+      </c>
+      <c r="S9">
+        <v>-0.00013616593647829611</v>
+      </c>
+      <c r="T9">
+        <v>4.8198850616078715e-005</v>
+      </c>
+      <c r="U9">
+        <v>-0.00015198363930017059</v>
+      </c>
+      <c r="V9">
+        <v>1.8933567812122465e-005</v>
+      </c>
+      <c r="W9">
+        <v>3.7672229702493017e-005</v>
+      </c>
+      <c r="X9">
+        <v>5.232867210725866e-005</v>
+      </c>
+      <c r="Y9">
+        <v>4.0059845813835722e-006</v>
+      </c>
+      <c r="Z9">
+        <v>-0.00015350412130647688</v>
+      </c>
+      <c r="AA9">
+        <v>-2.5530667434722922e-005</v>
+      </c>
+      <c r="AB9">
+        <v>0.0002592626601205239</v>
+      </c>
+      <c r="AC9">
+        <v>0.00011721681639982173</v>
+      </c>
+      <c r="AD9">
+        <v>0.00032244911903909134</v>
+      </c>
+      <c r="AE9">
+        <v>-0.004087867188814741</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>-0.26084705691095755</v>
+      </c>
+      <c r="C10">
+        <v>0.00014200205900610137</v>
+      </c>
+      <c r="D10">
+        <v>0.00012552472889933991</v>
+      </c>
+      <c r="E10">
+        <v>-1.5666899560463831e-006</v>
+      </c>
+      <c r="F10">
+        <v>-1.5312320586813679e-005</v>
+      </c>
+      <c r="G10">
+        <v>0.00017774139871740336</v>
+      </c>
+      <c r="H10">
+        <v>0.0009820304924515928</v>
+      </c>
+      <c r="I10">
+        <v>0.0015752242186613807</v>
+      </c>
+      <c r="J10">
+        <v>0.0019542057228681556</v>
+      </c>
+      <c r="K10">
+        <v>0.0030709791877172915</v>
+      </c>
+      <c r="L10">
+        <v>0.0019814070626886903</v>
+      </c>
+      <c r="M10">
+        <v>0.001754723478991806</v>
+      </c>
+      <c r="N10">
+        <v>0.00012988654967265403</v>
+      </c>
+      <c r="O10">
+        <v>-1.8557229465389119e-006</v>
+      </c>
+      <c r="P10">
+        <v>-8.9947723714290371e-005</v>
+      </c>
+      <c r="Q10">
+        <v>-0.00036455343653250404</v>
+      </c>
+      <c r="R10">
+        <v>-0.0002771351175657904</v>
+      </c>
+      <c r="S10">
+        <v>-0.00023203110102269818</v>
+      </c>
+      <c r="T10">
+        <v>-2.5317213062155011e-005</v>
+      </c>
+      <c r="U10">
+        <v>-0.0002320829359623218</v>
+      </c>
+      <c r="V10">
+        <v>5.2008275478468251e-005</v>
+      </c>
+      <c r="W10">
+        <v>4.9088773089981004e-006</v>
+      </c>
+      <c r="X10">
+        <v>-4.1399863636967186e-005</v>
+      </c>
+      <c r="Y10">
+        <v>2.0592966853558731e-005</v>
+      </c>
+      <c r="Z10">
+        <v>-0.00034517134978559211</v>
+      </c>
+      <c r="AA10">
+        <v>-0.00014415966650339098</v>
+      </c>
+      <c r="AB10">
+        <v>0.00022971819166165124</v>
+      </c>
+      <c r="AC10">
+        <v>0.00014697569960548783</v>
+      </c>
+      <c r="AD10">
+        <v>0.0002898025676345414</v>
+      </c>
+      <c r="AE10">
+        <v>-0.0046480309574214243</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>-0.11409040314158277</v>
+      </c>
+      <c r="C11">
+        <v>6.0594948023574949e-005</v>
+      </c>
+      <c r="D11">
+        <v>8.5027124691176978e-005</v>
+      </c>
+      <c r="E11">
+        <v>-1.1125734132390706e-006</v>
+      </c>
+      <c r="F11">
+        <v>4.3233737276070759e-005</v>
+      </c>
+      <c r="G11">
+        <v>0.00026291642830834536</v>
+      </c>
+      <c r="H11">
+        <v>0.0008330319685443732</v>
+      </c>
+      <c r="I11">
+        <v>0.0014222604352087536</v>
+      </c>
+      <c r="J11">
+        <v>0.0018345283351852298</v>
+      </c>
+      <c r="K11">
+        <v>0.0019814070626886903</v>
+      </c>
+      <c r="L11">
+        <v>0.0027100000207989925</v>
+      </c>
+      <c r="M11">
+        <v>0.0016597846300744183</v>
+      </c>
+      <c r="N11">
+        <v>3.0311181187234692e-005</v>
+      </c>
+      <c r="O11">
+        <v>3.7273955116987826e-005</v>
+      </c>
+      <c r="P11">
+        <v>6.6303089200821729e-005</v>
+      </c>
+      <c r="Q11">
+        <v>-0.00021782162351067461</v>
+      </c>
+      <c r="R11">
+        <v>-0.00025159069364695481</v>
+      </c>
+      <c r="S11">
+        <v>-3.6497441578182439e-005</v>
+      </c>
+      <c r="T11">
+        <v>4.8213566854139116e-005</v>
+      </c>
+      <c r="U11">
+        <v>-0.00016727729067834366</v>
+      </c>
+      <c r="V11">
+        <v>0.00014444590519336817</v>
+      </c>
+      <c r="W11">
+        <v>7.069809087567006e-005</v>
+      </c>
+      <c r="X11">
+        <v>8.0542994243797822e-005</v>
+      </c>
+      <c r="Y11">
+        <v>3.7457318080623897e-006</v>
+      </c>
+      <c r="Z11">
+        <v>-0.00013816069335462628</v>
+      </c>
+      <c r="AA11">
+        <v>5.0804757637224737e-005</v>
+      </c>
+      <c r="AB11">
+        <v>0.0002119024471781087</v>
+      </c>
+      <c r="AC11">
+        <v>0.0001430421418352648</v>
+      </c>
+      <c r="AD11">
+        <v>0.00031481929150526506</v>
+      </c>
+      <c r="AE11">
+        <v>-0.0036081682074562819</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>-0.0095437182677831391</v>
+      </c>
+      <c r="C12">
+        <v>5.2021065018809095e-006</v>
+      </c>
+      <c r="D12">
+        <v>9.6174226206568916e-005</v>
+      </c>
+      <c r="E12">
+        <v>-1.3396437273161059e-006</v>
+      </c>
+      <c r="F12">
+        <v>6.9544730385728254e-005</v>
+      </c>
+      <c r="G12">
+        <v>0.00045040330324155268</v>
+      </c>
+      <c r="H12">
+        <v>0.00049302754983907287</v>
+      </c>
+      <c r="I12">
+        <v>0.0011174131917346905</v>
+      </c>
+      <c r="J12">
+        <v>0.0016747211947203192</v>
+      </c>
+      <c r="K12">
+        <v>0.001754723478991806</v>
+      </c>
+      <c r="L12">
+        <v>0.0016597846300744183</v>
+      </c>
+      <c r="M12">
+        <v>0.0037121200573981472</v>
+      </c>
+      <c r="N12">
+        <v>0.00046595982112609697</v>
+      </c>
+      <c r="O12">
+        <v>0.0003590809415783317</v>
+      </c>
+      <c r="P12">
+        <v>0.00023991050728174856</v>
+      </c>
+      <c r="Q12">
+        <v>-5.5796989506346427e-005</v>
+      </c>
+      <c r="R12">
+        <v>0.00012882058694468668</v>
+      </c>
+      <c r="S12">
+        <v>3.6943146817129961e-005</v>
+      </c>
+      <c r="T12">
+        <v>0.00014092799565458759</v>
+      </c>
+      <c r="U12">
+        <v>-4.7977738492479237e-005</v>
+      </c>
+      <c r="V12">
+        <v>0.00030198831036498349</v>
+      </c>
+      <c r="W12">
+        <v>0.00023770638890161628</v>
+      </c>
+      <c r="X12">
+        <v>0.00031828192757619826</v>
+      </c>
+      <c r="Y12">
+        <v>5.8126364268046803e-007</v>
+      </c>
+      <c r="Z12">
+        <v>-9.4030945990691115e-005</v>
+      </c>
+      <c r="AA12">
+        <v>4.9218357950740272e-005</v>
+      </c>
+      <c r="AB12">
+        <v>4.9829191017414492e-005</v>
+      </c>
+      <c r="AC12">
+        <v>0.00019549808676047609</v>
+      </c>
+      <c r="AD12">
+        <v>0.00055622552068529971</v>
+      </c>
+      <c r="AE12">
+        <v>-0.0035837109712486522</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13">
+        <v>-0.017826784980051111</v>
+      </c>
+      <c r="C13">
+        <v>-5.8460765848974088e-005</v>
+      </c>
+      <c r="D13">
+        <v>-1.2476099615596134e-005</v>
+      </c>
+      <c r="E13">
+        <v>5.2323666850330862e-008</v>
+      </c>
+      <c r="F13">
+        <v>4.956082152354443e-005</v>
+      </c>
+      <c r="G13">
+        <v>0.00054196043158473515</v>
+      </c>
+      <c r="H13">
+        <v>-0.0001964961054141325</v>
+      </c>
+      <c r="I13">
+        <v>-0.00030541338284988378</v>
+      </c>
+      <c r="J13">
+        <v>0.00028810419402787598</v>
+      </c>
+      <c r="K13">
+        <v>0.00012988654967265403</v>
+      </c>
+      <c r="L13">
+        <v>3.0311181187234692e-005</v>
+      </c>
+      <c r="M13">
+        <v>0.00046595982112609697</v>
+      </c>
+      <c r="N13">
+        <v>0.0072128530938373823</v>
+      </c>
+      <c r="O13">
+        <v>0.0023444834954829165</v>
+      </c>
+      <c r="P13">
+        <v>0.0023773555100335534</v>
+      </c>
+      <c r="Q13">
+        <v>0.0023952414123721306</v>
+      </c>
+      <c r="R13">
+        <v>0.0022503269229464306</v>
+      </c>
+      <c r="S13">
+        <v>0.0022710689083376562</v>
+      </c>
+      <c r="T13">
+        <v>0.0023500422317761292</v>
+      </c>
+      <c r="U13">
+        <v>0.0024160756257084982</v>
+      </c>
+      <c r="V13">
+        <v>0.0024703939841392332</v>
+      </c>
+      <c r="W13">
+        <v>0.002424054473727991</v>
+      </c>
+      <c r="X13">
+        <v>0.0024694059302184674</v>
+      </c>
+      <c r="Y13">
+        <v>3.0748892442776713e-006</v>
+      </c>
+      <c r="Z13">
+        <v>-0.0001827363655809362</v>
+      </c>
+      <c r="AA13">
+        <v>-6.9913850603355959e-005</v>
+      </c>
+      <c r="AB13">
+        <v>0.0011140082769774341</v>
+      </c>
+      <c r="AC13">
+        <v>0.0022254238923909379</v>
+      </c>
+      <c r="AD13">
+        <v>0.0010622122850906931</v>
+      </c>
+      <c r="AE13">
+        <v>-0.0022679666119874643</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14">
+        <v>0.16455601037135331</v>
+      </c>
+      <c r="C14">
+        <v>3.0247009458892162e-005</v>
+      </c>
+      <c r="D14">
+        <v>1.6043452185874325e-005</v>
+      </c>
+      <c r="E14">
+        <v>-3.283959955332303e-007</v>
+      </c>
+      <c r="F14">
+        <v>-2.7822229458093753e-005</v>
+      </c>
+      <c r="G14">
+        <v>0.0003127618921197168</v>
+      </c>
+      <c r="H14">
+        <v>-3.8914182525600456e-005</v>
+      </c>
+      <c r="I14">
+        <v>-3.9453299579033946e-005</v>
+      </c>
+      <c r="J14">
+        <v>2.4445006637660718e-005</v>
+      </c>
+      <c r="K14">
+        <v>-1.8557229465389119e-006</v>
+      </c>
+      <c r="L14">
+        <v>3.7273955116987826e-005</v>
+      </c>
+      <c r="M14">
+        <v>0.0003590809415783317</v>
+      </c>
+      <c r="N14">
+        <v>0.0023444834954829165</v>
+      </c>
+      <c r="O14">
+        <v>0.0040964822450468685</v>
+      </c>
+      <c r="P14">
+        <v>0.0022668280748347905</v>
+      </c>
+      <c r="Q14">
+        <v>0.0023006640784174383</v>
+      </c>
+      <c r="R14">
+        <v>0.002199639520438289</v>
+      </c>
+      <c r="S14">
+        <v>0.0022059064598339115</v>
+      </c>
+      <c r="T14">
+        <v>0.0022439203929961685</v>
+      </c>
+      <c r="U14">
+        <v>0.0023192034308985522</v>
+      </c>
+      <c r="V14">
+        <v>0.0023516834042621318</v>
+      </c>
+      <c r="W14">
+        <v>0.0023409811520170806</v>
+      </c>
+      <c r="X14">
+        <v>0.0023395557341882129</v>
+      </c>
+      <c r="Y14">
+        <v>-8.8155477690423267e-007</v>
+      </c>
+      <c r="Z14">
+        <v>-0.00023289918249270994</v>
+      </c>
+      <c r="AA14">
+        <v>6.5058756591275592e-005</v>
+      </c>
+      <c r="AB14">
+        <v>0.00076409314393045</v>
+      </c>
+      <c r="AC14">
+        <v>0.001884026264625467</v>
+      </c>
+      <c r="AD14">
+        <v>0.00078573604171323713</v>
+      </c>
+      <c r="AE14">
+        <v>-0.0025184587412703367</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>14</v>
+      </c>
+      <c r="B15">
+        <v>0.18978867918877076</v>
+      </c>
+      <c r="C15">
+        <v>-3.9283592258444852e-006</v>
+      </c>
+      <c r="D15">
+        <v>-6.0676156975564911e-006</v>
+      </c>
+      <c r="E15">
+        <v>-3.5020463021728397e-008</v>
+      </c>
+      <c r="F15">
+        <v>-0.00010693377281242433</v>
+      </c>
+      <c r="G15">
+        <v>0.00026323417279885047</v>
+      </c>
+      <c r="H15">
+        <v>-0.00013125257370743615</v>
+      </c>
+      <c r="I15">
+        <v>-0.00018665813198023243</v>
+      </c>
+      <c r="J15">
+        <v>-2.5700361891442026e-005</v>
+      </c>
+      <c r="K15">
+        <v>-8.9947723714290371e-005</v>
+      </c>
+      <c r="L15">
+        <v>6.6303089200821729e-005</v>
+      </c>
+      <c r="M15">
+        <v>0.00023991050728174856</v>
+      </c>
+      <c r="N15">
+        <v>0.0023773555100335534</v>
+      </c>
+      <c r="O15">
+        <v>0.0022668280748347905</v>
+      </c>
+      <c r="P15">
+        <v>0.0045962180279628768</v>
+      </c>
+      <c r="Q15">
+        <v>0.0023332545114379305</v>
+      </c>
+      <c r="R15">
+        <v>0.0021956071828246348</v>
+      </c>
+      <c r="S15">
+        <v>0.0021853965545233752</v>
+      </c>
+      <c r="T15">
+        <v>0.0022546484689437581</v>
+      </c>
+      <c r="U15">
+        <v>0.0023349185794742408</v>
+      </c>
+      <c r="V15">
+        <v>0.0023766806181526141</v>
+      </c>
+      <c r="W15">
+        <v>0.0023421768120842849</v>
+      </c>
+      <c r="X15">
+        <v>0.0023502862408103444</v>
+      </c>
+      <c r="Y15">
+        <v>-4.4625313866024168e-006</v>
+      </c>
+      <c r="Z15">
+        <v>-0.0002511081884967822</v>
+      </c>
+      <c r="AA15">
+        <v>0.00029947993281955886</v>
+      </c>
+      <c r="AB15">
+        <v>0.00075453485633682953</v>
+      </c>
+      <c r="AC15">
+        <v>0.0018407872377880709</v>
+      </c>
+      <c r="AD15">
+        <v>0.0010340295999819056</v>
+      </c>
+      <c r="AE15">
+        <v>-0.0019820275231181082</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>0.072479293891244675</v>
+      </c>
+      <c r="C16">
+        <v>-6.2379929981665888e-005</v>
+      </c>
+      <c r="D16">
+        <v>-1.1433032268695024e-005</v>
+      </c>
+      <c r="E16">
+        <v>6.3337015300660282e-009</v>
+      </c>
+      <c r="F16">
+        <v>-0.00025150836900189312</v>
+      </c>
+      <c r="G16">
+        <v>0.00010850463840107411</v>
+      </c>
+      <c r="H16">
+        <v>-0.00011434119118769145</v>
+      </c>
+      <c r="I16">
+        <v>-0.00030188682534425205</v>
+      </c>
+      <c r="J16">
+        <v>-0.00025237003667107777</v>
+      </c>
+      <c r="K16">
+        <v>-0.00036455343653250404</v>
+      </c>
+      <c r="L16">
+        <v>-0.00021782162351067461</v>
+      </c>
+      <c r="M16">
+        <v>-5.5796989506346427e-005</v>
+      </c>
+      <c r="N16">
+        <v>0.0023952414123721306</v>
+      </c>
+      <c r="O16">
+        <v>0.0023006640784174383</v>
+      </c>
+      <c r="P16">
+        <v>0.0023332545114379305</v>
+      </c>
+      <c r="Q16">
+        <v>0.0050220032680155079</v>
+      </c>
+      <c r="R16">
+        <v>0.0022365263444139682</v>
+      </c>
+      <c r="S16">
+        <v>0.0022457477768828556</v>
+      </c>
+      <c r="T16">
+        <v>0.0022945497834549002</v>
+      </c>
+      <c r="U16">
+        <v>0.0024078495046351922</v>
+      </c>
+      <c r="V16">
+        <v>0.0024218993067849819</v>
+      </c>
+      <c r="W16">
+        <v>0.0023986616794864656</v>
+      </c>
+      <c r="X16">
+        <v>0.0023901993389608594</v>
+      </c>
+      <c r="Y16">
+        <v>1.5968090396671248e-005</v>
+      </c>
+      <c r="Z16">
+        <v>-0.00029757047602522503</v>
+      </c>
+      <c r="AA16">
+        <v>-0.0001306359182356536</v>
+      </c>
+      <c r="AB16">
+        <v>0.00087842371300339821</v>
+      </c>
+      <c r="AC16">
+        <v>0.0017707378709228166</v>
+      </c>
+      <c r="AD16">
+        <v>0.00088833534944392429</v>
+      </c>
+      <c r="AE16">
+        <v>-0.0018535689733727673</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>16</v>
+      </c>
+      <c r="B17">
+        <v>0.0030311534920225503</v>
+      </c>
+      <c r="C17">
+        <v>3.371067614290426e-005</v>
+      </c>
+      <c r="D17">
+        <v>-1.6643981312167935e-005</v>
+      </c>
+      <c r="E17">
+        <v>1.2821859060781969e-007</v>
+      </c>
+      <c r="F17">
+        <v>-3.3272320010768213e-005</v>
+      </c>
+      <c r="G17">
+        <v>0.0001576780104881896</v>
+      </c>
+      <c r="H17">
+        <v>-0.00020507560406223687</v>
+      </c>
+      <c r="I17">
+        <v>-0.0002448243328716752</v>
+      </c>
+      <c r="J17">
+        <v>-0.00028238373315389939</v>
+      </c>
+      <c r="K17">
+        <v>-0.0002771351175657904</v>
+      </c>
+      <c r="L17">
+        <v>-0.00025159069364695481</v>
+      </c>
+      <c r="M17">
+        <v>0.00012882058694468668</v>
+      </c>
+      <c r="N17">
+        <v>0.0022503269229464306</v>
+      </c>
+      <c r="O17">
+        <v>0.002199639520438289</v>
+      </c>
+      <c r="P17">
+        <v>0.0021956071828246348</v>
+      </c>
+      <c r="Q17">
+        <v>0.0022365263444139682</v>
+      </c>
+      <c r="R17">
+        <v>0.0050893390245263584</v>
+      </c>
+      <c r="S17">
+        <v>0.0021190929733722308</v>
+      </c>
+      <c r="T17">
+        <v>0.0021862910279679638</v>
+      </c>
+      <c r="U17">
+        <v>0.0022516074075661194</v>
+      </c>
+      <c r="V17">
+        <v>0.0022584602951255554</v>
+      </c>
+      <c r="W17">
+        <v>0.002254751833246897</v>
+      </c>
+      <c r="X17">
+        <v>0.0022441461683670541</v>
+      </c>
+      <c r="Y17">
+        <v>1.3723115086770813e-005</v>
+      </c>
+      <c r="Z17">
+        <v>-0.00011562808942733968</v>
+      </c>
+      <c r="AA17">
+        <v>0.00012086393746250557</v>
+      </c>
+      <c r="AB17">
+        <v>0.00056622743970303688</v>
+      </c>
+      <c r="AC17">
+        <v>0.0017240727322733278</v>
+      </c>
+      <c r="AD17">
+        <v>0.00048769848131170767</v>
+      </c>
+      <c r="AE17">
+        <v>-0.0018856426168847146</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>17</v>
+      </c>
+      <c r="B18">
+        <v>-0.10968321251233076</v>
+      </c>
+      <c r="C18">
+        <v>-7.9844343404750182e-005</v>
+      </c>
+      <c r="D18">
+        <v>5.8307866221793847e-006</v>
+      </c>
+      <c r="E18">
+        <v>-1.9439998583913155e-007</v>
+      </c>
+      <c r="F18">
+        <v>6.7365303395574129e-005</v>
+      </c>
+      <c r="G18">
+        <v>-2.4178292399237043e-005</v>
+      </c>
+      <c r="H18">
+        <v>-0.00018479037067188676</v>
+      </c>
+      <c r="I18">
+        <v>-4.9582572285289389e-006</v>
+      </c>
+      <c r="J18">
+        <v>-0.00013616593647829611</v>
+      </c>
+      <c r="K18">
+        <v>-0.00023203110102269818</v>
+      </c>
+      <c r="L18">
+        <v>-3.6497441578182439e-005</v>
+      </c>
+      <c r="M18">
+        <v>3.6943146817129961e-005</v>
+      </c>
+      <c r="N18">
+        <v>0.0022710689083376562</v>
+      </c>
+      <c r="O18">
+        <v>0.0022059064598339115</v>
+      </c>
+      <c r="P18">
+        <v>0.0021853965545233752</v>
+      </c>
+      <c r="Q18">
+        <v>0.0022457477768828556</v>
+      </c>
+      <c r="R18">
+        <v>0.0021190929733722308</v>
+      </c>
+      <c r="S18">
+        <v>0.0053262038021693004</v>
+      </c>
+      <c r="T18">
+        <v>0.0022262666216429413</v>
+      </c>
+      <c r="U18">
+        <v>0.0022776245691880641</v>
+      </c>
+      <c r="V18">
+        <v>0.00228875944307939</v>
+      </c>
+      <c r="W18">
+        <v>0.0022907244623124878</v>
+      </c>
+      <c r="X18">
+        <v>0.0022916245428352242</v>
+      </c>
+      <c r="Y18">
+        <v>-1.7424654538458882e-005</v>
+      </c>
+      <c r="Z18">
+        <v>-0.00012639591127056114</v>
+      </c>
+      <c r="AA18">
+        <v>0.00016946380782861646</v>
+      </c>
+      <c r="AB18">
+        <v>0.00087656963168953835</v>
+      </c>
+      <c r="AC18">
+        <v>0.0016623791013318113</v>
+      </c>
+      <c r="AD18">
+        <v>0.00059793389975717765</v>
+      </c>
+      <c r="AE18">
+        <v>-0.0018805984434090289</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>18</v>
+      </c>
+      <c r="B19">
+        <v>-0.061035660867585474</v>
+      </c>
+      <c r="C19">
+        <v>5.0363820741853534e-005</v>
+      </c>
+      <c r="D19">
+        <v>-1.9325727017326707e-006</v>
+      </c>
+      <c r="E19">
+        <v>-8.0307127386476586e-009</v>
+      </c>
+      <c r="F19">
+        <v>2.6094426833276458e-005</v>
+      </c>
+      <c r="G19">
+        <v>0.00038106740814587302</v>
+      </c>
+      <c r="H19">
+        <v>-9.9085484095743476e-005</v>
+      </c>
+      <c r="I19">
+        <v>-1.696163585917967e-005</v>
+      </c>
+      <c r="J19">
+        <v>4.8198850616078715e-005</v>
+      </c>
+      <c r="K19">
+        <v>-2.5317213062155011e-005</v>
+      </c>
+      <c r="L19">
+        <v>4.8213566854139116e-005</v>
+      </c>
+      <c r="M19">
+        <v>0.00014092799565458759</v>
+      </c>
+      <c r="N19">
+        <v>0.0023500422317761292</v>
+      </c>
+      <c r="O19">
+        <v>0.0022439203929961685</v>
+      </c>
+      <c r="P19">
+        <v>0.0022546484689437581</v>
+      </c>
+      <c r="Q19">
+        <v>0.0022945497834549002</v>
+      </c>
+      <c r="R19">
+        <v>0.0021862910279679638</v>
+      </c>
+      <c r="S19">
+        <v>0.0022262666216429413</v>
+      </c>
+      <c r="T19">
+        <v>0.0040430071569087043</v>
+      </c>
+      <c r="U19">
+        <v>0.0023217182155871032</v>
+      </c>
+      <c r="V19">
+        <v>0.0023376851475078383</v>
+      </c>
+      <c r="W19">
+        <v>0.0023319078747728343</v>
+      </c>
+      <c r="X19">
+        <v>0.0023440211281454248</v>
+      </c>
+      <c r="Y19">
+        <v>-1.2297362592883067e-005</v>
+      </c>
+      <c r="Z19">
+        <v>-0.00017518121049973291</v>
+      </c>
+      <c r="AA19">
+        <v>1.9128976807980378e-005</v>
+      </c>
+      <c r="AB19">
+        <v>0.0010206844507923544</v>
+      </c>
+      <c r="AC19">
+        <v>0.0018909598129262456</v>
+      </c>
+      <c r="AD19">
+        <v>0.0008509515812796703</v>
+      </c>
+      <c r="AE19">
+        <v>-0.0021533469062982036</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>19</v>
+      </c>
+      <c r="B20">
+        <v>0.080700412232011479</v>
+      </c>
+      <c r="C20">
+        <v>0.00011181013736597909</v>
+      </c>
+      <c r="D20">
+        <v>8.9406633026548055e-007</v>
+      </c>
+      <c r="E20">
+        <v>-1.5962950008511749e-007</v>
+      </c>
+      <c r="F20">
+        <v>-0.0002206694084850991</v>
+      </c>
+      <c r="G20">
+        <v>0.00011310756309257089</v>
+      </c>
+      <c r="H20">
+        <v>-2.5202366787791214e-005</v>
+      </c>
+      <c r="I20">
+        <v>-0.00018164059965022759</v>
+      </c>
+      <c r="J20">
+        <v>-0.00015198363930017059</v>
+      </c>
+      <c r="K20">
+        <v>-0.0002320829359623218</v>
+      </c>
+      <c r="L20">
+        <v>-0.00016727729067834366</v>
+      </c>
+      <c r="M20">
+        <v>-4.7977738492479237e-005</v>
+      </c>
+      <c r="N20">
+        <v>0.0024160756257084982</v>
+      </c>
+      <c r="O20">
+        <v>0.0023192034308985522</v>
+      </c>
+      <c r="P20">
+        <v>0.0023349185794742408</v>
+      </c>
+      <c r="Q20">
+        <v>0.0024078495046351922</v>
+      </c>
+      <c r="R20">
+        <v>0.0022516074075661194</v>
+      </c>
+      <c r="S20">
+        <v>0.0022776245691880641</v>
+      </c>
+      <c r="T20">
+        <v>0.0023217182155871032</v>
+      </c>
+      <c r="U20">
+        <v>0.0053355167310207311</v>
+      </c>
+      <c r="V20">
+        <v>0.0024335694644551042</v>
+      </c>
+      <c r="W20">
+        <v>0.0024214952238894227</v>
+      </c>
+      <c r="X20">
+        <v>0.0024223248990294767</v>
+      </c>
+      <c r="Y20">
+        <v>-8.9728252839167076e-006</v>
+      </c>
+      <c r="Z20">
+        <v>-0.00016740583698949949</v>
+      </c>
+      <c r="AA20">
+        <v>0.00023988605909825258</v>
+      </c>
+      <c r="AB20">
+        <v>0.00096221091321998338</v>
+      </c>
+      <c r="AC20">
+        <v>0.001915420241291029</v>
+      </c>
+      <c r="AD20">
+        <v>0.0010919000695680347</v>
+      </c>
+      <c r="AE20">
+        <v>-0.0019120563790466266</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>20</v>
+      </c>
+      <c r="B21">
+        <v>-0.051506093769564408</v>
+      </c>
+      <c r="C21">
+        <v>1.402536366660787e-006</v>
+      </c>
+      <c r="D21">
+        <v>-1.2095390647407162e-006</v>
+      </c>
+      <c r="E21">
+        <v>-1.2355250592429246e-007</v>
+      </c>
+      <c r="F21">
+        <v>-0.00011589134803618127</v>
+      </c>
+      <c r="G21">
+        <v>0.00010918605240317506</v>
+      </c>
+      <c r="H21">
+        <v>1.6753080447032276e-005</v>
+      </c>
+      <c r="I21">
+        <v>-0.0001131500937367972</v>
+      </c>
+      <c r="J21">
+        <v>1.8933567812122465e-005</v>
+      </c>
+      <c r="K21">
+        <v>5.2008275478468251e-005</v>
+      </c>
+      <c r="L21">
+        <v>0.00014444590519336817</v>
+      </c>
+      <c r="M21">
+        <v>0.00030198831036498349</v>
+      </c>
+      <c r="N21">
+        <v>0.0024703939841392332</v>
+      </c>
+      <c r="O21">
+        <v>0.0023516834042621318</v>
+      </c>
+      <c r="P21">
+        <v>0.0023766806181526141</v>
+      </c>
+      <c r="Q21">
+        <v>0.0024218993067849819</v>
+      </c>
+      <c r="R21">
+        <v>0.0022584602951255554</v>
+      </c>
+      <c r="S21">
+        <v>0.00228875944307939</v>
+      </c>
+      <c r="T21">
+        <v>0.0023376851475078383</v>
+      </c>
+      <c r="U21">
+        <v>0.0024335694644551042</v>
+      </c>
+      <c r="V21">
+        <v>0.0053873697323260118</v>
+      </c>
+      <c r="W21">
+        <v>0.0024465071428011382</v>
+      </c>
+      <c r="X21">
+        <v>0.0024737820077519587</v>
+      </c>
+      <c r="Y21">
+        <v>-1.4306694862061765e-006</v>
+      </c>
+      <c r="Z21">
+        <v>-0.00011224418114208143</v>
+      </c>
+      <c r="AA21">
+        <v>-5.1395325397734614e-006</v>
+      </c>
+      <c r="AB21">
+        <v>0.0010457836207411063</v>
+      </c>
+      <c r="AC21">
+        <v>0.0019936190015478589</v>
+      </c>
+      <c r="AD21">
+        <v>0.001054379256513218</v>
+      </c>
+      <c r="AE21">
+        <v>-0.0022749513191838806</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>21</v>
+      </c>
+      <c r="B22">
+        <v>0.12254009603103537</v>
+      </c>
+      <c r="C22">
+        <v>0.00010647482951627222</v>
+      </c>
+      <c r="D22">
+        <v>1.3349872169014538e-005</v>
+      </c>
+      <c r="E22">
+        <v>-3.5065492590082775e-007</v>
+      </c>
+      <c r="F22">
+        <v>-4.8241457278754929e-005</v>
+      </c>
+      <c r="G22">
+        <v>0.00018791140235520796</v>
+      </c>
+      <c r="H22">
+        <v>-4.5216342418121901e-005</v>
+      </c>
+      <c r="I22">
+        <v>-2.7302839536066633e-006</v>
+      </c>
+      <c r="J22">
+        <v>3.7672229702493017e-005</v>
+      </c>
+      <c r="K22">
+        <v>4.9088773089981004e-006</v>
+      </c>
+      <c r="L22">
+        <v>7.069809087567006e-005</v>
+      </c>
+      <c r="M22">
+        <v>0.00023770638890161628</v>
+      </c>
+      <c r="N22">
+        <v>0.002424054473727991</v>
+      </c>
+      <c r="O22">
+        <v>0.0023409811520170806</v>
+      </c>
+      <c r="P22">
+        <v>0.0023421768120842849</v>
+      </c>
+      <c r="Q22">
+        <v>0.0023986616794864656</v>
+      </c>
+      <c r="R22">
+        <v>0.002254751833246897</v>
+      </c>
+      <c r="S22">
+        <v>0.0022907244623124878</v>
+      </c>
+      <c r="T22">
+        <v>0.0023319078747728343</v>
+      </c>
+      <c r="U22">
+        <v>0.0024214952238894227</v>
+      </c>
+      <c r="V22">
+        <v>0.0024465071428011382</v>
+      </c>
+      <c r="W22">
+        <v>0.0047221972899465494</v>
+      </c>
+      <c r="X22">
+        <v>0.0024545073133004102</v>
+      </c>
+      <c r="Y22">
+        <v>7.5782696733750216e-006</v>
+      </c>
+      <c r="Z22">
+        <v>-0.00012997078706766162</v>
+      </c>
+      <c r="AA22">
+        <v>4.3240879558507542e-005</v>
+      </c>
+      <c r="AB22">
+        <v>0.0011133018826939927</v>
+      </c>
+      <c r="AC22">
+        <v>0.0019484267750705783</v>
+      </c>
+      <c r="AD22">
+        <v>0.0010319981829071002</v>
+      </c>
+      <c r="AE22">
+        <v>-0.0026943890463013466</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23">
+        <v>-0.11648585936585516</v>
+      </c>
+      <c r="C23">
+        <v>3.4137192050686459e-005</v>
+      </c>
+      <c r="D23">
+        <v>-1.1630343278863121e-005</v>
+      </c>
+      <c r="E23">
+        <v>3.1396265845078558e-008</v>
+      </c>
+      <c r="F23">
+        <v>3.0755205554420855e-005</v>
+      </c>
+      <c r="G23">
+        <v>9.1101634324794846e-005</v>
+      </c>
+      <c r="H23">
+        <v>-9.10004407589011e-005</v>
+      </c>
+      <c r="I23">
+        <v>-0.00010408440354341434</v>
+      </c>
+      <c r="J23">
+        <v>5.232867210725866e-005</v>
+      </c>
+      <c r="K23">
+        <v>-4.1399863636967186e-005</v>
+      </c>
+      <c r="L23">
+        <v>8.0542994243797822e-005</v>
+      </c>
+      <c r="M23">
+        <v>0.00031828192757619826</v>
+      </c>
+      <c r="N23">
+        <v>0.0024694059302184674</v>
+      </c>
+      <c r="O23">
+        <v>0.0023395557341882129</v>
+      </c>
+      <c r="P23">
+        <v>0.0023502862408103444</v>
+      </c>
+      <c r="Q23">
+        <v>0.0023901993389608594</v>
+      </c>
+      <c r="R23">
+        <v>0.0022441461683670541</v>
+      </c>
+      <c r="S23">
+        <v>0.0022916245428352242</v>
+      </c>
+      <c r="T23">
+        <v>0.0023440211281454248</v>
+      </c>
+      <c r="U23">
+        <v>0.0024223248990294767</v>
+      </c>
+      <c r="V23">
+        <v>0.0024737820077519587</v>
+      </c>
+      <c r="W23">
+        <v>0.0024545073133004102</v>
+      </c>
+      <c r="X23">
+        <v>0.004987326808915977</v>
+      </c>
+      <c r="Y23">
+        <v>-1.1229574756527118e-006</v>
+      </c>
+      <c r="Z23">
+        <v>-0.0002069333340413066</v>
+      </c>
+      <c r="AA23">
+        <v>4.9921226968485454e-005</v>
+      </c>
+      <c r="AB23">
+        <v>0.0011263123856762949</v>
+      </c>
+      <c r="AC23">
+        <v>0.0020138036249790613</v>
+      </c>
+      <c r="AD23">
+        <v>0.0010770280307167326</v>
+      </c>
+      <c r="AE23">
+        <v>-0.0021877738494345011</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <v>-0.00024604709787195614</v>
+      </c>
+      <c r="C24">
+        <v>-4.9311556265419157e-006</v>
+      </c>
+      <c r="D24">
+        <v>-7.1365286076810995e-008</v>
+      </c>
+      <c r="E24">
+        <v>4.2307766369329244e-010</v>
+      </c>
+      <c r="F24">
+        <v>4.408407015140093e-006</v>
+      </c>
+      <c r="G24">
+        <v>2.8441285669955818e-005</v>
+      </c>
+      <c r="H24">
+        <v>1.8184367273823686e-006</v>
+      </c>
+      <c r="I24">
+        <v>-1.9514786708447915e-006</v>
+      </c>
+      <c r="J24">
+        <v>4.0059845813835722e-006</v>
+      </c>
+      <c r="K24">
+        <v>2.0592966853558731e-005</v>
+      </c>
+      <c r="L24">
+        <v>3.7457318080623897e-006</v>
+      </c>
+      <c r="M24">
+        <v>5.8126364268046803e-007</v>
+      </c>
+      <c r="N24">
+        <v>3.0748892442776713e-006</v>
+      </c>
+      <c r="O24">
+        <v>-8.8155477690423267e-007</v>
+      </c>
+      <c r="P24">
+        <v>-4.4625313866024168e-006</v>
+      </c>
+      <c r="Q24">
+        <v>1.5968090396671248e-005</v>
+      </c>
+      <c r="R24">
+        <v>1.3723115086770813e-005</v>
+      </c>
+      <c r="S24">
+        <v>-1.7424654538458882e-005</v>
+      </c>
+      <c r="T24">
+        <v>-1.2297362592883067e-005</v>
+      </c>
+      <c r="U24">
+        <v>-8.9728252839167076e-006</v>
+      </c>
+      <c r="V24">
+        <v>-1.4306694862061765e-006</v>
+      </c>
+      <c r="W24">
+        <v>7.5782696733750216e-006</v>
+      </c>
+      <c r="X24">
+        <v>-1.1229574756527118e-006</v>
+      </c>
+      <c r="Y24">
+        <v>2.5413896785198515e-005</v>
+      </c>
+      <c r="Z24">
+        <v>-0.00011057154138606457</v>
+      </c>
+      <c r="AA24">
+        <v>-0.00013304427233899914</v>
+      </c>
+      <c r="AB24">
+        <v>-7.7920272591807077e-006</v>
+      </c>
+      <c r="AC24">
+        <v>-1.1253326945393145e-005</v>
+      </c>
+      <c r="AD24">
+        <v>-1.6836646099729354e-005</v>
+      </c>
+      <c r="AE24">
+        <v>-0.00040411488211068556</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25">
+        <v>0.13874857548682401</v>
+      </c>
+      <c r="C25">
+        <v>-1.0787907954078364e-005</v>
+      </c>
+      <c r="D25">
+        <v>-4.2550648915218493e-006</v>
+      </c>
+      <c r="E25">
+        <v>7.5553596077281995e-008</v>
+      </c>
+      <c r="F25">
+        <v>7.6141975321154408e-005</v>
+      </c>
+      <c r="G25">
+        <v>-8.8374269448711788e-005</v>
+      </c>
+      <c r="H25">
+        <v>-0.00015674405732034628</v>
+      </c>
+      <c r="I25">
+        <v>-0.00017436455763986363</v>
+      </c>
+      <c r="J25">
+        <v>-0.00015350412130647688</v>
+      </c>
+      <c r="K25">
+        <v>-0.00034517134978559211</v>
+      </c>
+      <c r="L25">
+        <v>-0.00013816069335462628</v>
+      </c>
+      <c r="M25">
+        <v>-9.4030945990691115e-005</v>
+      </c>
+      <c r="N25">
+        <v>-0.0001827363655809362</v>
+      </c>
+      <c r="O25">
+        <v>-0.00023289918249270994</v>
+      </c>
+      <c r="P25">
+        <v>-0.0002511081884967822</v>
+      </c>
+      <c r="Q25">
+        <v>-0.00029757047602522503</v>
+      </c>
+      <c r="R25">
+        <v>-0.00011562808942733968</v>
+      </c>
+      <c r="S25">
+        <v>-0.00012639591127056114</v>
+      </c>
+      <c r="T25">
+        <v>-0.00017518121049973291</v>
+      </c>
+      <c r="U25">
+        <v>-0.00016740583698949949</v>
+      </c>
+      <c r="V25">
+        <v>-0.00011224418114208143</v>
+      </c>
+      <c r="W25">
+        <v>-0.00012997078706766162</v>
+      </c>
+      <c r="X25">
+        <v>-0.0002069333340413066</v>
+      </c>
+      <c r="Y25">
+        <v>-0.00011057154138606457</v>
+      </c>
+      <c r="Z25">
+        <v>0.0031623523352178285</v>
+      </c>
+      <c r="AA25">
+        <v>0.00080212533320053541</v>
+      </c>
+      <c r="AB25">
+        <v>-7.4614833269879503e-005</v>
+      </c>
+      <c r="AC25">
+        <v>-8.0756431916998556e-005</v>
+      </c>
+      <c r="AD25">
+        <v>0.00029099560502216361</v>
+      </c>
+      <c r="AE25">
+        <v>0.0018795641470831887</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26">
+        <v>0.10785657860263786</v>
+      </c>
+      <c r="C26">
+        <v>2.2157136138186527e-005</v>
+      </c>
+      <c r="D26">
+        <v>-7.2023131823159672e-006</v>
+      </c>
+      <c r="E26">
+        <v>1.0187974634759229e-007</v>
+      </c>
+      <c r="F26">
+        <v>4.8533594174586368e-005</v>
+      </c>
+      <c r="G26">
+        <v>-9.9243764042209544e-005</v>
+      </c>
+      <c r="H26">
+        <v>-0.00011260891038819504</v>
+      </c>
+      <c r="I26">
+        <v>-7.3580414676958905e-005</v>
+      </c>
+      <c r="J26">
+        <v>-2.5530667434722922e-005</v>
+      </c>
+      <c r="K26">
+        <v>-0.00014415966650339098</v>
+      </c>
+      <c r="L26">
+        <v>5.0804757637224737e-005</v>
+      </c>
+      <c r="M26">
+        <v>4.9218357950740272e-005</v>
+      </c>
+      <c r="N26">
+        <v>-6.9913850603355959e-005</v>
+      </c>
+      <c r="O26">
+        <v>6.5058756591275592e-005</v>
+      </c>
+      <c r="P26">
+        <v>0.00029947993281955886</v>
+      </c>
+      <c r="Q26">
+        <v>-0.0001306359182356536</v>
+      </c>
+      <c r="R26">
+        <v>0.00012086393746250557</v>
+      </c>
+      <c r="S26">
+        <v>0.00016946380782861646</v>
+      </c>
+      <c r="T26">
+        <v>1.9128976807980378e-005</v>
+      </c>
+      <c r="U26">
+        <v>0.00023988605909825258</v>
+      </c>
+      <c r="V26">
+        <v>-5.1395325397734614e-006</v>
+      </c>
+      <c r="W26">
+        <v>4.3240879558507542e-005</v>
+      </c>
+      <c r="X26">
+        <v>4.9921226968485454e-005</v>
+      </c>
+      <c r="Y26">
+        <v>-0.00013304427233899914</v>
+      </c>
+      <c r="Z26">
+        <v>0.00080212533320053541</v>
+      </c>
+      <c r="AA26">
+        <v>0.0039361846467669713</v>
+      </c>
+      <c r="AB26">
+        <v>-3.0594902941428114e-005</v>
+      </c>
+      <c r="AC26">
+        <v>-8.8227677405194622e-005</v>
+      </c>
+      <c r="AD26">
+        <v>-0.00013231673637799704</v>
+      </c>
+      <c r="AE26">
+        <v>0.0019078209628953212</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s">
+        <v>24</v>
+      </c>
+      <c r="B27">
+        <v>-0.4121080261905975</v>
+      </c>
+      <c r="C27">
+        <v>5.4924177902638074e-005</v>
+      </c>
+      <c r="D27">
+        <v>-2.1692380901941304e-005</v>
+      </c>
+      <c r="E27">
+        <v>3.4920146561629916e-007</v>
+      </c>
+      <c r="F27">
+        <v>0.00037316560902281</v>
+      </c>
+      <c r="G27">
+        <v>0.0004015496887424504</v>
+      </c>
+      <c r="H27">
+        <v>2.8270173464144902e-005</v>
+      </c>
+      <c r="I27">
+        <v>0.00010586853365773504</v>
+      </c>
+      <c r="J27">
+        <v>0.0002592626601205239</v>
+      </c>
+      <c r="K27">
+        <v>0.00022971819166165124</v>
+      </c>
+      <c r="L27">
+        <v>0.0002119024471781087</v>
+      </c>
+      <c r="M27">
+        <v>4.9829191017414492e-005</v>
+      </c>
+      <c r="N27">
+        <v>0.0011140082769774341</v>
+      </c>
+      <c r="O27">
+        <v>0.00076409314393045</v>
+      </c>
+      <c r="P27">
+        <v>0.00075453485633682953</v>
+      </c>
+      <c r="Q27">
+        <v>0.00087842371300339821</v>
+      </c>
+      <c r="R27">
+        <v>0.00056622743970303688</v>
+      </c>
+      <c r="S27">
+        <v>0.00087656963168953835</v>
+      </c>
+      <c r="T27">
+        <v>0.0010206844507923544</v>
+      </c>
+      <c r="U27">
+        <v>0.00096221091321998338</v>
+      </c>
+      <c r="V27">
+        <v>0.0010457836207411063</v>
+      </c>
+      <c r="W27">
+        <v>0.0011133018826939927</v>
+      </c>
+      <c r="X27">
+        <v>0.0011263123856762949</v>
+      </c>
+      <c r="Y27">
+        <v>-7.7920272591807077e-006</v>
+      </c>
+      <c r="Z27">
+        <v>-7.4614833269879503e-005</v>
+      </c>
+      <c r="AA27">
+        <v>-3.0594902941428114e-005</v>
+      </c>
+      <c r="AB27">
+        <v>0.0031444734154494418</v>
+      </c>
+      <c r="AC27">
+        <v>0.0010481394483260284</v>
+      </c>
+      <c r="AD27">
+        <v>0.00072173979381726506</v>
+      </c>
+      <c r="AE27">
+        <v>-0.00116608861737214</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28">
+        <v>-0.23613900227476614</v>
+      </c>
+      <c r="C28">
+        <v>-3.6713838358304692e-005</v>
+      </c>
+      <c r="D28">
+        <v>-2.6876023877973063e-005</v>
+      </c>
+      <c r="E28">
+        <v>3.1108552852123559e-007</v>
+      </c>
+      <c r="F28">
+        <v>0.00013942371223252866</v>
+      </c>
+      <c r="G28">
+        <v>0.00028220509488973962</v>
+      </c>
+      <c r="H28">
+        <v>2.4024677142782044e-006</v>
+      </c>
+      <c r="I28">
+        <v>1.7808302128676477e-005</v>
+      </c>
+      <c r="J28">
+        <v>0.00011721681639982173</v>
+      </c>
+      <c r="K28">
+        <v>0.00014697569960548783</v>
+      </c>
+      <c r="L28">
+        <v>0.0001430421418352648</v>
+      </c>
+      <c r="M28">
+        <v>0.00019549808676047609</v>
+      </c>
+      <c r="N28">
+        <v>0.0022254238923909379</v>
+      </c>
+      <c r="O28">
+        <v>0.001884026264625467</v>
+      </c>
+      <c r="P28">
+        <v>0.0018407872377880709</v>
+      </c>
+      <c r="Q28">
+        <v>0.0017707378709228166</v>
+      </c>
+      <c r="R28">
+        <v>0.0017240727322733278</v>
+      </c>
+      <c r="S28">
+        <v>0.0016623791013318113</v>
+      </c>
+      <c r="T28">
+        <v>0.0018909598129262456</v>
+      </c>
+      <c r="U28">
+        <v>0.001915420241291029</v>
+      </c>
+      <c r="V28">
+        <v>0.0019936190015478589</v>
+      </c>
+      <c r="W28">
+        <v>0.0019484267750705783</v>
+      </c>
+      <c r="X28">
+        <v>0.0020138036249790613</v>
+      </c>
+      <c r="Y28">
+        <v>-1.1253326945393145e-005</v>
+      </c>
+      <c r="Z28">
+        <v>-8.0756431916998556e-005</v>
+      </c>
+      <c r="AA28">
+        <v>-8.8227677405194622e-005</v>
+      </c>
+      <c r="AB28">
+        <v>0.0010481394483260284</v>
+      </c>
+      <c r="AC28">
+        <v>0.0067294054282205406</v>
+      </c>
+      <c r="AD28">
+        <v>0.00098456111335186967</v>
+      </c>
+      <c r="AE28">
+        <v>-0.0015355488791964633</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B29">
+        <v>-0.13878565493523215</v>
+      </c>
+      <c r="C29">
+        <v>-2.4540986930661353e-005</v>
+      </c>
+      <c r="D29">
+        <v>-5.2129313585139018e-006</v>
+      </c>
+      <c r="E29">
+        <v>1.0003781509743627e-007</v>
+      </c>
+      <c r="F29">
+        <v>0.00011456336596575144</v>
+      </c>
+      <c r="G29">
+        <v>0.00032305895848009123</v>
+      </c>
+      <c r="H29">
+        <v>7.7295078950241321e-005</v>
+      </c>
+      <c r="I29">
+        <v>0.00026501419097670845</v>
+      </c>
+      <c r="J29">
+        <v>0.00032244911903909134</v>
+      </c>
+      <c r="K29">
+        <v>0.0002898025676345414</v>
+      </c>
+      <c r="L29">
+        <v>0.00031481929150526506</v>
+      </c>
+      <c r="M29">
+        <v>0.00055622552068529971</v>
+      </c>
+      <c r="N29">
+        <v>0.0010622122850906931</v>
+      </c>
+      <c r="O29">
+        <v>0.00078573604171323713</v>
+      </c>
+      <c r="P29">
+        <v>0.0010340295999819056</v>
+      </c>
+      <c r="Q29">
+        <v>0.00088833534944392429</v>
+      </c>
+      <c r="R29">
+        <v>0.00048769848131170767</v>
+      </c>
+      <c r="S29">
+        <v>0.00059793389975717765</v>
+      </c>
+      <c r="T29">
+        <v>0.0008509515812796703</v>
+      </c>
+      <c r="U29">
+        <v>0.0010919000695680347</v>
+      </c>
+      <c r="V29">
+        <v>0.001054379256513218</v>
+      </c>
+      <c r="W29">
+        <v>0.0010319981829071002</v>
+      </c>
+      <c r="X29">
+        <v>0.0010770280307167326</v>
+      </c>
+      <c r="Y29">
+        <v>-1.6836646099729354e-005</v>
+      </c>
+      <c r="Z29">
+        <v>0.00029099560502216361</v>
+      </c>
+      <c r="AA29">
+        <v>-0.00013231673637799704</v>
+      </c>
+      <c r="AB29">
+        <v>0.00072173979381726506</v>
+      </c>
+      <c r="AC29">
+        <v>0.00098456111335186967</v>
+      </c>
+      <c r="AD29">
+        <v>0.0063095662950000018</v>
+      </c>
+      <c r="AE29">
+        <v>-0.0011863085508093745</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s">
+        <v>27</v>
+      </c>
+      <c r="B30">
+        <v>-0.9839830291038183</v>
+      </c>
+      <c r="C30">
+        <v>8.3440410491761433e-005</v>
+      </c>
+      <c r="D30">
+        <v>-0.0015548025461564691</v>
+      </c>
+      <c r="E30">
+        <v>1.9938384833170706e-005</v>
+      </c>
+      <c r="F30">
+        <v>-0.0019188094309747551</v>
+      </c>
+      <c r="G30">
+        <v>-0.0022087242446957389</v>
+      </c>
+      <c r="H30">
+        <v>-0.0042096053654617407</v>
+      </c>
+      <c r="I30">
+        <v>-0.0036083293383268635</v>
+      </c>
+      <c r="J30">
+        <v>-0.004087867188814741</v>
+      </c>
+      <c r="K30">
+        <v>-0.0046480309574214243</v>
+      </c>
+      <c r="L30">
+        <v>-0.0036081682074562819</v>
+      </c>
+      <c r="M30">
+        <v>-0.0035837109712486522</v>
+      </c>
+      <c r="N30">
+        <v>-0.0022679666119874643</v>
+      </c>
+      <c r="O30">
+        <v>-0.0025184587412703367</v>
+      </c>
+      <c r="P30">
+        <v>-0.0019820275231181082</v>
+      </c>
+      <c r="Q30">
+        <v>-0.0018535689733727673</v>
+      </c>
+      <c r="R30">
+        <v>-0.0018856426168847146</v>
+      </c>
+      <c r="S30">
+        <v>-0.0018805984434090289</v>
+      </c>
+      <c r="T30">
+        <v>-0.0021533469062982036</v>
+      </c>
+      <c r="U30">
+        <v>-0.0019120563790466266</v>
+      </c>
+      <c r="V30">
+        <v>-0.0022749513191838806</v>
+      </c>
+      <c r="W30">
+        <v>-0.0026943890463013466</v>
+      </c>
+      <c r="X30">
+        <v>-0.0021877738494345011</v>
+      </c>
+      <c r="Y30">
+        <v>-0.00040411488211068556</v>
+      </c>
+      <c r="Z30">
+        <v>0.0018795641470831887</v>
+      </c>
+      <c r="AA30">
+        <v>0.0019078209628953212</v>
+      </c>
+      <c r="AB30">
+        <v>-0.00116608861737214</v>
+      </c>
+      <c r="AC30">
+        <v>-0.0015355488791964633</v>
+      </c>
+      <c r="AD30">
+        <v>-0.0011863085508093745</v>
+      </c>
+      <c r="AE30">
+        <v>0.040025960466584465</v>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>
--- a/input/reg_leave_parental_home.xlsx
+++ b/input/reg_leave_parental_home.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/Desktop/initial_populations/regression_estimates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{602D23E5-3EAC-1A4F-9C75-3C6EBD2F4375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8817BEC6-5EDC-BD47-9162-E4BF76683ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17780" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
     <sheet name="Gof" sheetId="2" r:id="rId2"/>
-    <sheet name="UK_P1" sheetId="3" r:id="rId3"/>
+    <sheet name="P1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="47">
   <si>
     <t>Description:</t>
   </si>
@@ -148,9 +148,6 @@
   </si>
   <si>
     <t>Constant</t>
-  </si>
-  <si>
-    <t/>
   </si>
   <si>
     <t xml:space="preserve">P1 - Leaving the parental home </t>
@@ -671,18 +668,18 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B5">
         <v>6.9022199015385866E-2</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F5">
         <v>684.73614386758788</v>
@@ -690,13 +687,13 @@
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B6">
         <v>24019</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F6">
         <v>-4566628.439755124</v>
@@ -709,10 +706,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AF30"/>
+  <dimension ref="A1:AE30"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -806,11 +803,8 @@
       <c r="AE1" t="s">
         <v>41</v>
       </c>
-      <c r="AF1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
@@ -905,7 +899,7 @@
         <v>1.268840887852403E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -1000,7 +994,7 @@
         <v>-1.5780736543313686E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
@@ -1095,7 +1089,7 @@
         <v>2.8828078037175422E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1190,7 +1184,7 @@
         <v>-7.8049976886715479E-3</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
@@ -1285,7 +1279,7 @@
         <v>-7.527512833879018E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -1380,7 +1374,7 @@
         <v>-8.9197156502368383E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1475,7 +1469,7 @@
         <v>-4.5251570341358141E-3</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
@@ -1570,7 +1564,7 @@
         <v>-3.93532726756886E-3</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1665,7 +1659,7 @@
         <v>-4.5922890442269965E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>22</v>
       </c>
@@ -1760,7 +1754,7 @@
         <v>-5.0173087365462787E-3</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>23</v>
       </c>
@@ -1855,7 +1849,7 @@
         <v>-7.1497321724051394E-3</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1950,7 +1944,7 @@
         <v>-7.8608146394417936E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
@@ -2045,7 +2039,7 @@
         <v>-6.8897660269216544E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
@@ -2140,7 +2134,7 @@
         <v>-7.4029150966422397E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>27</v>
       </c>

--- a/input/reg_leave_parental_home.xlsx
+++ b/input/reg_leave_parental_home.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8817BEC6-5EDC-BD47-9162-E4BF76683ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046BC585-488C-A24B-8B49-74C5E2952126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17780" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="30240" windowHeight="19540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="48">
   <si>
     <t>Description:</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Model parameters governing leaving parental home</t>
   </si>
   <si>
-    <t>Authors: Patryk Bronka, Justin van de Ven, Daria Popova</t>
+    <t>Authors: Patryk Bronka, Justin van de Ven, Daria Popova, Aleksandra Kolndrekaj</t>
   </si>
   <si>
     <t>Last edit: 19 Jan 2026 DP</t>
@@ -72,10 +72,13 @@
     <t>Dag_sq</t>
   </si>
   <si>
-    <t>Deh_c3_Medium</t>
-  </si>
-  <si>
-    <t>Deh_c3_Low</t>
+    <t>Deh_c4_Na_L1</t>
+  </si>
+  <si>
+    <t>Deh_c4_Medium_L1</t>
+  </si>
+  <si>
+    <t>Deh_c4_Low_L1</t>
   </si>
   <si>
     <t>Les_c3_Student_L1</t>
@@ -668,35 +671,35 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5">
-        <v>6.9022199015385866E-2</v>
+        <v>6.7073258632073696E-2</v>
       </c>
       <c r="E5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5">
-        <v>684.73614386758788</v>
+        <v>661.4423481868846</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6">
-        <v>24019</v>
+        <v>24022</v>
       </c>
       <c r="E6" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F6">
-        <v>-4566628.439755124</v>
+        <v>-4575490.6663713455</v>
       </c>
     </row>
   </sheetData>
@@ -706,10 +709,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AE30"/>
+  <dimension ref="A1:AF31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -803,2760 +806,2948 @@
       <c r="AE1" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.2">
+      <c r="AF1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2">
-        <v>-0.20267947067355804</v>
+        <v>-0.20758112018024577</v>
       </c>
       <c r="C2">
-        <v>1.003251197257006E-3</v>
+        <v>1.0005206591985412E-3</v>
       </c>
       <c r="D2">
-        <v>-3.988007170215416E-5</v>
+        <v>-3.5814547092007554E-5</v>
       </c>
       <c r="E2">
-        <v>4.3293677199282579E-7</v>
+        <v>3.5996480465815583E-7</v>
       </c>
       <c r="F2">
-        <v>-1.455617568321007E-4</v>
+        <v>-2.2036577315475298E-4</v>
       </c>
       <c r="G2">
-        <v>-2.5990829519184741E-4</v>
+        <v>-1.5218301699738187E-4</v>
       </c>
       <c r="H2">
-        <v>1.2803032434900507E-4</v>
+        <v>-2.7525005442595831E-4</v>
       </c>
       <c r="I2">
-        <v>6.4937865481969558E-5</v>
+        <v>1.966244507026618E-4</v>
       </c>
       <c r="J2">
-        <v>1.7311275914468738E-4</v>
+        <v>4.6776370144376223E-5</v>
       </c>
       <c r="K2">
-        <v>1.6837730078171067E-4</v>
+        <v>1.3433701185813936E-4</v>
       </c>
       <c r="L2">
-        <v>1.8307476985138661E-4</v>
+        <v>1.4362906355992955E-4</v>
       </c>
       <c r="M2">
-        <v>5.1005132907317005E-5</v>
+        <v>1.4969478050918337E-4</v>
       </c>
       <c r="N2">
-        <v>-1.6756409050416445E-4</v>
+        <v>1.9635896086423577E-5</v>
       </c>
       <c r="O2">
-        <v>1.662230055640984E-4</v>
+        <v>-1.5529268109889887E-4</v>
       </c>
       <c r="P2">
-        <v>1.6181593453577461E-5</v>
+        <v>1.6340289846084841E-4</v>
       </c>
       <c r="Q2">
-        <v>5.3356987382376689E-6</v>
+        <v>2.1289421178969284E-5</v>
       </c>
       <c r="R2">
-        <v>6.2641293248999437E-5</v>
+        <v>6.4434250311572973E-6</v>
       </c>
       <c r="S2">
-        <v>-3.2195274102895992E-5</v>
+        <v>5.9646024902017735E-5</v>
       </c>
       <c r="T2">
-        <v>-6.036192433433014E-5</v>
+        <v>-2.412411564488479E-5</v>
       </c>
       <c r="U2">
-        <v>3.3015914756626155E-5</v>
+        <v>-5.8235237810183649E-5</v>
       </c>
       <c r="V2">
-        <v>-1.3943944411035939E-5</v>
+        <v>3.8308562154541274E-5</v>
       </c>
       <c r="W2">
-        <v>-1.6967168748297916E-5</v>
+        <v>-1.2603087492062997E-5</v>
       </c>
       <c r="X2">
-        <v>6.1545927356103686E-5</v>
+        <v>-1.2415530464250412E-5</v>
       </c>
       <c r="Y2">
-        <v>2.5204466419506002E-6</v>
+        <v>6.2049055527128172E-5</v>
       </c>
       <c r="Z2">
-        <v>3.6095380948773644E-5</v>
+        <v>1.5707991150727183E-6</v>
       </c>
       <c r="AA2">
-        <v>1.8502171495594645E-5</v>
+        <v>4.4743738907690041E-5</v>
       </c>
       <c r="AB2">
-        <v>-1.0091452927714643E-5</v>
+        <v>1.9346771455097677E-5</v>
       </c>
       <c r="AC2">
-        <v>-4.8169548043188143E-4</v>
+        <v>-8.5206271170738937E-6</v>
       </c>
       <c r="AD2">
-        <v>-2.2878681587369142E-5</v>
+        <v>-4.8491751454143037E-4</v>
       </c>
       <c r="AE2">
-        <v>1.268840887852403E-4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.2">
+        <v>-1.6263788564520126E-5</v>
+      </c>
+      <c r="AF2">
+        <v>1.2366993500762848E-4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3">
-        <v>0.1749869048277522</v>
+        <v>0.1997281297465206</v>
       </c>
       <c r="C3">
-        <v>-3.988007170215416E-5</v>
+        <v>-3.5814547092007554E-5</v>
       </c>
       <c r="D3">
-        <v>1.1447850306598067E-3</v>
+        <v>1.2112041023426448E-3</v>
       </c>
       <c r="E3">
-        <v>-2.1101191708056903E-5</v>
+        <v>-2.2319934708756732E-5</v>
       </c>
       <c r="F3">
-        <v>4.6439425792957453E-4</v>
+        <v>8.0351321999211226E-4</v>
       </c>
       <c r="G3">
-        <v>5.0217367022199538E-4</v>
+        <v>4.4497146669870871E-4</v>
       </c>
       <c r="H3">
-        <v>5.040186038672255E-4</v>
+        <v>5.3704397132845415E-4</v>
       </c>
       <c r="I3">
-        <v>1.6978679481840521E-4</v>
+        <v>3.0096852119942648E-4</v>
       </c>
       <c r="J3">
-        <v>9.5698036855192256E-5</v>
+        <v>2.7006149659412296E-4</v>
       </c>
       <c r="K3">
-        <v>1.1407331867113149E-4</v>
+        <v>3.2910446154502885E-4</v>
       </c>
       <c r="L3">
-        <v>1.1819494535253818E-4</v>
+        <v>2.5996012241122335E-4</v>
       </c>
       <c r="M3">
-        <v>3.6006293135907317E-4</v>
+        <v>2.5911096908810122E-4</v>
       </c>
       <c r="N3">
-        <v>3.0751499614768566E-4</v>
+        <v>5.0582283882276489E-4</v>
       </c>
       <c r="O3">
-        <v>2.4588557925959119E-4</v>
+        <v>2.8027296158254214E-4</v>
       </c>
       <c r="P3">
-        <v>3.3599924276807725E-4</v>
+        <v>2.320916846641442E-4</v>
       </c>
       <c r="Q3">
-        <v>2.3877822860431379E-4</v>
+        <v>3.3612945322286322E-4</v>
       </c>
       <c r="R3">
-        <v>2.3623889733457313E-4</v>
+        <v>2.5331675022573767E-4</v>
       </c>
       <c r="S3">
-        <v>3.0352060479769483E-4</v>
+        <v>2.3121237053660266E-4</v>
       </c>
       <c r="T3">
-        <v>2.4231764163930823E-4</v>
+        <v>2.9508295579747427E-4</v>
       </c>
       <c r="U3">
-        <v>3.0144618337597079E-4</v>
+        <v>2.2676346763183175E-4</v>
       </c>
       <c r="V3">
-        <v>2.5226066487243882E-4</v>
+        <v>2.8705440860610242E-4</v>
       </c>
       <c r="W3">
-        <v>3.7534963407277397E-4</v>
+        <v>2.4318932414474424E-4</v>
       </c>
       <c r="X3">
-        <v>9.656539712628049E-5</v>
+        <v>3.7117580639640371E-4</v>
       </c>
       <c r="Y3">
-        <v>5.8623260199830701E-6</v>
+        <v>8.6311337591227048E-5</v>
       </c>
       <c r="Z3">
-        <v>-3.0895817672078234E-6</v>
+        <v>6.0185117747523463E-6</v>
       </c>
       <c r="AA3">
-        <v>-5.543069881322406E-5</v>
+        <v>7.7573150486439117E-6</v>
       </c>
       <c r="AB3">
-        <v>-3.6916698753138369E-5</v>
+        <v>-4.37111033549549E-5</v>
       </c>
       <c r="AC3">
-        <v>3.2376399281118691E-4</v>
+        <v>-5.7483922405465911E-5</v>
       </c>
       <c r="AD3">
-        <v>3.7598502356093371E-5</v>
+        <v>3.0594389090943946E-4</v>
       </c>
       <c r="AE3">
-        <v>-1.5780736543313686E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.2">
+        <v>4.5938859206975024E-5</v>
+      </c>
+      <c r="AF3">
+        <v>-1.6808632573797836E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4">
-        <v>-2.2636506564422975E-3</v>
+        <v>-2.6773497318359567E-3</v>
       </c>
       <c r="C4">
-        <v>4.3293677199282579E-7</v>
+        <v>3.5996480465815583E-7</v>
       </c>
       <c r="D4">
-        <v>-2.1101191708056903E-5</v>
+        <v>-2.2319934708756732E-5</v>
       </c>
       <c r="E4">
-        <v>3.9322065534350253E-7</v>
+        <v>4.1568459528178607E-7</v>
       </c>
       <c r="F4">
-        <v>-8.3700123573849207E-6</v>
+        <v>-1.4180521210316629E-5</v>
       </c>
       <c r="G4">
-        <v>-9.4801702937827906E-6</v>
+        <v>-8.0599661547113414E-6</v>
       </c>
       <c r="H4">
-        <v>-8.3759526785381493E-6</v>
+        <v>-1.0164380172712992E-5</v>
       </c>
       <c r="I4">
-        <v>-2.8255626283874143E-6</v>
+        <v>-4.8600956288020276E-6</v>
       </c>
       <c r="J4">
-        <v>-1.4135306485980572E-6</v>
+        <v>-4.661458229733817E-6</v>
       </c>
       <c r="K4">
-        <v>-1.7838292934820973E-6</v>
+        <v>-5.6048751393461587E-6</v>
       </c>
       <c r="L4">
-        <v>-2.3804769169569719E-6</v>
+        <v>-4.4428458269934562E-6</v>
       </c>
       <c r="M4">
-        <v>-6.6372830091126364E-6</v>
+        <v>-4.9496581091379433E-6</v>
       </c>
       <c r="N4">
-        <v>-5.5843662216286988E-6</v>
+        <v>-9.3088091981656037E-6</v>
       </c>
       <c r="O4">
-        <v>-4.9818823705450639E-6</v>
+        <v>-5.1601543477111712E-6</v>
       </c>
       <c r="P4">
-        <v>-6.4697383011483434E-6</v>
+        <v>-4.7744167412468636E-6</v>
       </c>
       <c r="Q4">
-        <v>-4.6239148649851091E-6</v>
+        <v>-6.4722889666835487E-6</v>
       </c>
       <c r="R4">
-        <v>-4.6719676109688849E-6</v>
+        <v>-4.8878282369641678E-6</v>
       </c>
       <c r="S4">
-        <v>-5.6410671585207429E-6</v>
+        <v>-4.601562683222023E-6</v>
       </c>
       <c r="T4">
-        <v>-4.7279293580410286E-6</v>
+        <v>-5.5307647907283899E-6</v>
       </c>
       <c r="U4">
-        <v>-5.6918833754125567E-6</v>
+        <v>-4.4725187062759166E-6</v>
       </c>
       <c r="V4">
-        <v>-5.0269393684843002E-6</v>
+        <v>-5.4622681237404913E-6</v>
       </c>
       <c r="W4">
-        <v>-6.8486974691471917E-6</v>
+        <v>-4.847160544957353E-6</v>
       </c>
       <c r="X4">
-        <v>-2.0553374108836498E-6</v>
+        <v>-6.8188063961987933E-6</v>
       </c>
       <c r="Y4">
-        <v>-1.1041643782008719E-7</v>
+        <v>-1.9027586668400809E-6</v>
       </c>
       <c r="Z4">
-        <v>3.366219190139378E-8</v>
+        <v>-1.1147281012490682E-7</v>
       </c>
       <c r="AA4">
-        <v>8.0468889660022073E-7</v>
+        <v>-1.6341386261677094E-7</v>
       </c>
       <c r="AB4">
-        <v>5.2443061451713129E-7</v>
+        <v>5.9964560833659268E-7</v>
       </c>
       <c r="AC4">
-        <v>-7.0302506220349444E-6</v>
+        <v>8.6386851775463133E-7</v>
       </c>
       <c r="AD4">
-        <v>-1.1430393126544458E-6</v>
+        <v>-6.7249685989256738E-6</v>
       </c>
       <c r="AE4">
-        <v>2.8828078037175422E-4</v>
-      </c>
-    </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.2">
+        <v>-1.3239563656416592E-6</v>
+      </c>
+      <c r="AF4">
+        <v>3.0706765633689022E-4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>-0.24712813452727792</v>
+        <v>-7.5051253269756077E-2</v>
       </c>
       <c r="C5">
-        <v>-1.455617568321007E-4</v>
+        <v>-2.2036577315475298E-4</v>
       </c>
       <c r="D5">
-        <v>4.6439425792957453E-4</v>
+        <v>8.0351321999211226E-4</v>
       </c>
       <c r="E5">
-        <v>-8.3700123573849207E-6</v>
+        <v>-1.4180521210316629E-5</v>
       </c>
       <c r="F5">
-        <v>1.393992963110869E-3</v>
+        <v>6.77613174194216E-3</v>
       </c>
       <c r="G5">
-        <v>1.0685621842281517E-3</v>
+        <v>1.6810336411684612E-3</v>
       </c>
       <c r="H5">
-        <v>1.3734984337263805E-4</v>
+        <v>1.4784298075190723E-3</v>
       </c>
       <c r="I5">
-        <v>-1.0213854480026322E-4</v>
+        <v>-3.042042530406778E-3</v>
       </c>
       <c r="J5">
-        <v>-1.9054206381681829E-5</v>
+        <v>-1.9630702327500644E-4</v>
       </c>
       <c r="K5">
-        <v>-6.7226492001986335E-5</v>
+        <v>4.6845558334803524E-5</v>
       </c>
       <c r="L5">
-        <v>1.4021060243848309E-4</v>
+        <v>-2.2933061411999881E-4</v>
       </c>
       <c r="M5">
-        <v>1.8725882435280969E-4</v>
+        <v>-3.269752371923122E-5</v>
       </c>
       <c r="N5">
-        <v>4.1979631441332725E-4</v>
+        <v>-7.8204176065001674E-5</v>
       </c>
       <c r="O5">
-        <v>3.6690318672919593E-4</v>
+        <v>1.968024775126202E-4</v>
       </c>
       <c r="P5">
-        <v>2.1112382243047509E-4</v>
+        <v>3.9191593996575503E-5</v>
       </c>
       <c r="Q5">
-        <v>1.6896290576812119E-4</v>
+        <v>1.2229678380336058E-4</v>
       </c>
       <c r="R5">
-        <v>2.2946851768483741E-4</v>
+        <v>1.8200220245876344E-4</v>
       </c>
       <c r="S5">
-        <v>1.7465178024838582E-4</v>
+        <v>-1.6945566355887082E-5</v>
       </c>
       <c r="T5">
-        <v>4.1788254493471222E-4</v>
+        <v>-9.9921214716107627E-5</v>
       </c>
       <c r="U5">
-        <v>1.5553375934152029E-4</v>
+        <v>3.1591749473021142E-4</v>
       </c>
       <c r="V5">
-        <v>2.3154841327471673E-4</v>
+        <v>-3.4902018928462055E-5</v>
       </c>
       <c r="W5">
-        <v>4.3687226972893053E-4</v>
+        <v>4.2043914335640692E-5</v>
       </c>
       <c r="X5">
-        <v>2.5135560197017768E-4</v>
+        <v>4.004151662559516E-4</v>
       </c>
       <c r="Y5">
-        <v>2.7024954846997318E-5</v>
+        <v>1.583288399686477E-5</v>
       </c>
       <c r="Z5">
-        <v>-1.2729083300184874E-4</v>
+        <v>4.7225383861884251E-5</v>
       </c>
       <c r="AA5">
-        <v>-7.9329549132553284E-5</v>
+        <v>-5.6160774035137666E-5</v>
       </c>
       <c r="AB5">
-        <v>2.8115579145155311E-4</v>
+        <v>-1.5091809039732948E-5</v>
       </c>
       <c r="AC5">
-        <v>9.3166464608707145E-4</v>
+        <v>1.5780785762827161E-5</v>
       </c>
       <c r="AD5">
-        <v>-1.0282855291970054E-4</v>
+        <v>9.6731761536263811E-4</v>
       </c>
       <c r="AE5">
-        <v>-7.8049976886715479E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.2">
+        <v>-1.5371471592788392E-4</v>
+      </c>
+      <c r="AF5">
+        <v>-1.2787263037740082E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
       <c r="B6">
-        <v>-0.41067950164364558</v>
+        <v>-0.19760244631696608</v>
       </c>
       <c r="C6">
-        <v>-2.5990829519184741E-4</v>
+        <v>-1.5218301699738187E-4</v>
       </c>
       <c r="D6">
-        <v>5.0217367022199538E-4</v>
+        <v>4.4497146669870871E-4</v>
       </c>
       <c r="E6">
-        <v>-9.4801702937827906E-6</v>
+        <v>-8.0599661547113414E-6</v>
       </c>
       <c r="F6">
-        <v>1.0685621842281517E-3</v>
+        <v>1.6810336411684612E-3</v>
       </c>
       <c r="G6">
-        <v>6.5591571209528358E-3</v>
+        <v>1.6833278170857845E-3</v>
       </c>
       <c r="H6">
-        <v>2.5739463420652501E-4</v>
+        <v>1.3547860022670674E-3</v>
       </c>
       <c r="I6">
-        <v>-6.5085424063560397E-4</v>
+        <v>-2.1201699064095077E-4</v>
       </c>
       <c r="J6">
-        <v>1.5774079840394738E-4</v>
+        <v>-6.4462147394792383E-5</v>
       </c>
       <c r="K6">
-        <v>1.7010540421167936E-4</v>
+        <v>1.7484144327233335E-5</v>
       </c>
       <c r="L6">
-        <v>4.1257565493650822E-4</v>
+        <v>-3.83540622167001E-6</v>
       </c>
       <c r="M6">
-        <v>5.2386910137350328E-4</v>
+        <v>2.7833817273945836E-4</v>
       </c>
       <c r="N6">
-        <v>4.8723691488297563E-4</v>
+        <v>3.5678371335411997E-4</v>
       </c>
       <c r="O6">
-        <v>2.6106346470773428E-4</v>
+        <v>4.3582471197963998E-4</v>
       </c>
       <c r="P6">
-        <v>2.3627509804795651E-4</v>
+        <v>3.8665993380054137E-4</v>
       </c>
       <c r="Q6">
-        <v>1.9848455177190987E-4</v>
+        <v>2.2576525796526222E-4</v>
       </c>
       <c r="R6">
-        <v>-5.6092428577259068E-5</v>
+        <v>1.9830865385825916E-4</v>
       </c>
       <c r="S6">
-        <v>-1.7238590888518464E-4</v>
+        <v>2.3841999109407435E-4</v>
       </c>
       <c r="T6">
-        <v>1.7040369713535581E-4</v>
+        <v>1.5795015446461007E-4</v>
       </c>
       <c r="U6">
-        <v>1.6156647440221194E-4</v>
+        <v>4.3242808590066419E-4</v>
       </c>
       <c r="V6">
-        <v>-2.884905730418198E-4</v>
+        <v>1.0697945405575843E-4</v>
       </c>
       <c r="W6">
-        <v>1.9333730432413352E-4</v>
+        <v>2.2606405081549487E-4</v>
       </c>
       <c r="X6">
-        <v>-1.9338845232749172E-4</v>
+        <v>4.4390586994820606E-4</v>
       </c>
       <c r="Y6">
-        <v>-2.2035683306357461E-6</v>
+        <v>2.6971178553977055E-4</v>
       </c>
       <c r="Z6">
-        <v>1.0327414611596319E-4</v>
+        <v>2.8249078510313858E-5</v>
       </c>
       <c r="AA6">
-        <v>4.3094902814287065E-5</v>
+        <v>-1.5884086586774482E-4</v>
       </c>
       <c r="AB6">
-        <v>4.4655413250984407E-4</v>
+        <v>-4.8603812532399852E-5</v>
       </c>
       <c r="AC6">
-        <v>6.1687035793088095E-4</v>
+        <v>3.1947794391678315E-4</v>
       </c>
       <c r="AD6">
-        <v>-1.6695709595049768E-5</v>
+        <v>1.0561272165055353E-3</v>
       </c>
       <c r="AE6">
-        <v>-7.527512833879018E-3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.2">
+        <v>-9.6399030472008593E-5</v>
+      </c>
+      <c r="AF6">
+        <v>-7.8759709211673103E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
       <c r="B7">
-        <v>-0.18615590720758657</v>
+        <v>-0.40171722273970079</v>
       </c>
       <c r="C7">
-        <v>1.2803032434900507E-4</v>
+        <v>-2.7525005442595831E-4</v>
       </c>
       <c r="D7">
-        <v>5.040186038672255E-4</v>
+        <v>5.3704397132845415E-4</v>
       </c>
       <c r="E7">
-        <v>-8.3759526785381493E-6</v>
+        <v>-1.0164380172712992E-5</v>
       </c>
       <c r="F7">
-        <v>1.3734984337263805E-4</v>
+        <v>1.4784298075190723E-3</v>
       </c>
       <c r="G7">
-        <v>2.5739463420652501E-4</v>
+        <v>1.3547860022670674E-3</v>
       </c>
       <c r="H7">
-        <v>2.656429233148884E-3</v>
+        <v>6.8247887400718996E-3</v>
       </c>
       <c r="I7">
-        <v>1.5007870097433185E-3</v>
+        <v>-7.7539984199314661E-5</v>
       </c>
       <c r="J7">
-        <v>1.0406888403427326E-3</v>
+        <v>-6.2537835174310188E-4</v>
       </c>
       <c r="K7">
-        <v>1.6098748218543691E-3</v>
+        <v>1.8235407865441783E-4</v>
       </c>
       <c r="L7">
-        <v>1.5259335329889823E-3</v>
+        <v>2.2437071098977649E-4</v>
       </c>
       <c r="M7">
-        <v>1.161343787269572E-3</v>
+        <v>5.3156924897645574E-4</v>
       </c>
       <c r="N7">
-        <v>-1.6627462911186644E-4</v>
+        <v>6.7200452711455071E-4</v>
       </c>
       <c r="O7">
-        <v>-7.1657018774787425E-5</v>
+        <v>5.334708496636492E-4</v>
       </c>
       <c r="P7">
-        <v>2.7186239300046149E-5</v>
+        <v>3.1577125179988027E-4</v>
       </c>
       <c r="Q7">
-        <v>2.6106875032902552E-5</v>
+        <v>2.7781265807227457E-4</v>
       </c>
       <c r="R7">
-        <v>-1.5104835718476439E-4</v>
+        <v>2.3920822292268474E-4</v>
       </c>
       <c r="S7">
-        <v>1.4747979654594287E-4</v>
+        <v>-7.3357989133670067E-5</v>
       </c>
       <c r="T7">
-        <v>-5.9136937744112177E-5</v>
+        <v>-1.7090711527230655E-4</v>
       </c>
       <c r="U7">
-        <v>2.7305043314325688E-6</v>
+        <v>2.0925376461486931E-4</v>
       </c>
       <c r="V7">
-        <v>-2.0852317552113968E-5</v>
+        <v>7.2196678534333604E-5</v>
       </c>
       <c r="W7">
-        <v>-3.1069069678916182E-4</v>
+        <v>-2.6748184923592504E-4</v>
       </c>
       <c r="X7">
-        <v>-9.0364403546973511E-5</v>
+        <v>2.0448099579843128E-4</v>
       </c>
       <c r="Y7">
-        <v>-9.3197335251311896E-6</v>
+        <v>-1.4141087857681158E-4</v>
       </c>
       <c r="Z7">
-        <v>1.2038135546313763E-4</v>
+        <v>2.7587062873393265E-6</v>
       </c>
       <c r="AA7">
-        <v>-7.135677064754617E-5</v>
+        <v>6.7696276270442392E-5</v>
       </c>
       <c r="AB7">
-        <v>7.6498904887661694E-5</v>
+        <v>-1.6483260493021059E-5</v>
       </c>
       <c r="AC7">
-        <v>-2.4870269898535566E-4</v>
+        <v>4.8536917546892675E-4</v>
       </c>
       <c r="AD7">
-        <v>-9.3727303104299627E-5</v>
+        <v>7.7981861282318612E-4</v>
       </c>
       <c r="AE7">
-        <v>-8.9197156502368383E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.2">
+        <v>-3.4721657098736841E-5</v>
+      </c>
+      <c r="AF7">
+        <v>-8.3513290753085521E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
       <c r="B8">
-        <v>-0.25624532503978709</v>
+        <v>-0.18533550293176548</v>
       </c>
       <c r="C8">
-        <v>6.4937865481969558E-5</v>
+        <v>1.966244507026618E-4</v>
       </c>
       <c r="D8">
-        <v>1.6978679481840521E-4</v>
+        <v>3.0096852119942648E-4</v>
       </c>
       <c r="E8">
-        <v>-2.8255626283874143E-6</v>
+        <v>-4.8600956288020276E-6</v>
       </c>
       <c r="F8">
-        <v>-1.0213854480026322E-4</v>
+        <v>-3.042042530406778E-3</v>
       </c>
       <c r="G8">
-        <v>-6.5085424063560397E-4</v>
+        <v>-2.1201699064095077E-4</v>
       </c>
       <c r="H8">
-        <v>1.5007870097433185E-3</v>
+        <v>-7.7539984199314661E-5</v>
       </c>
       <c r="I8">
-        <v>3.3247306170292963E-3</v>
+        <v>4.2844875985216142E-3</v>
       </c>
       <c r="J8">
-        <v>1.7285841791062663E-3</v>
+        <v>1.5759004100588572E-3</v>
       </c>
       <c r="K8">
-        <v>2.236760609438726E-3</v>
+        <v>1.0281292675592643E-3</v>
       </c>
       <c r="L8">
-        <v>2.2257994948709898E-3</v>
+        <v>1.7204766728795579E-3</v>
       </c>
       <c r="M8">
-        <v>1.6874723562210277E-3</v>
+        <v>1.6070944659217674E-3</v>
       </c>
       <c r="N8">
-        <v>-3.8518266337743076E-4</v>
+        <v>1.3044449891990305E-3</v>
       </c>
       <c r="O8">
-        <v>-1.4025417403930492E-4</v>
+        <v>-1.7272541229972885E-4</v>
       </c>
       <c r="P8">
-        <v>-5.8675835403398371E-5</v>
+        <v>1.9204317599709649E-6</v>
       </c>
       <c r="Q8">
-        <v>-2.3661412842095134E-4</v>
+        <v>4.1342716082856136E-5</v>
       </c>
       <c r="R8">
-        <v>-1.1226720564236608E-4</v>
+        <v>-6.491178353127151E-7</v>
       </c>
       <c r="S8">
-        <v>1.1462038418311708E-4</v>
+        <v>-8.6205647767372299E-5</v>
       </c>
       <c r="T8">
-        <v>1.8147505900696376E-6</v>
+        <v>2.4095064838562154E-4</v>
       </c>
       <c r="U8">
-        <v>-1.3191056217370001E-4</v>
+        <v>-1.1370387665397071E-4</v>
       </c>
       <c r="V8">
-        <v>-1.7894712276465201E-5</v>
+        <v>2.7986649151010695E-5</v>
       </c>
       <c r="W8">
-        <v>-4.5940120675852395E-4</v>
+        <v>2.1395355977187947E-5</v>
       </c>
       <c r="X8">
-        <v>-8.3370132209597582E-5</v>
+        <v>-4.0747779805873211E-4</v>
       </c>
       <c r="Y8">
-        <v>-9.1006088659880682E-6</v>
+        <v>-3.9056292400923339E-5</v>
       </c>
       <c r="Z8">
-        <v>5.0639640062871249E-5</v>
+        <v>-2.6488357675537918E-5</v>
       </c>
       <c r="AA8">
-        <v>-5.5105413464862996E-5</v>
+        <v>1.1042014054976686E-4</v>
       </c>
       <c r="AB8">
-        <v>9.0812592074561264E-5</v>
+        <v>-6.9332360169555387E-5</v>
       </c>
       <c r="AC8">
-        <v>-1.8000166222586784E-4</v>
+        <v>1.609415858674669E-4</v>
       </c>
       <c r="AD8">
-        <v>1.8986922959096978E-5</v>
+        <v>-5.0331829423211133E-4</v>
       </c>
       <c r="AE8">
-        <v>-4.5251570341358141E-3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.2">
+        <v>-5.8199699141244453E-5</v>
+      </c>
+      <c r="AF8">
+        <v>-5.7212067258735344E-3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
       <c r="B9">
-        <v>-0.12642554937614064</v>
+        <v>-0.25167997114882762</v>
       </c>
       <c r="C9">
-        <v>1.7311275914468738E-4</v>
+        <v>4.6776370144376223E-5</v>
       </c>
       <c r="D9">
-        <v>9.5698036855192256E-5</v>
+        <v>2.7006149659412296E-4</v>
       </c>
       <c r="E9">
-        <v>-1.4135306485980572E-6</v>
+        <v>-4.661458229733817E-6</v>
       </c>
       <c r="F9">
-        <v>-1.9054206381681829E-5</v>
+        <v>-1.9630702327500644E-4</v>
       </c>
       <c r="G9">
-        <v>1.5774079840394738E-4</v>
+        <v>-6.4462147394792383E-5</v>
       </c>
       <c r="H9">
-        <v>1.0406888403427326E-3</v>
+        <v>-6.2537835174310188E-4</v>
       </c>
       <c r="I9">
-        <v>1.7285841791062663E-3</v>
+        <v>1.5759004100588572E-3</v>
       </c>
       <c r="J9">
-        <v>3.2269856400346884E-3</v>
+        <v>3.2436799733072878E-3</v>
       </c>
       <c r="K9">
-        <v>2.322440557535325E-3</v>
+        <v>1.6173685000352136E-3</v>
       </c>
       <c r="L9">
-        <v>2.2904723341788582E-3</v>
+        <v>2.1371410208063917E-3</v>
       </c>
       <c r="M9">
-        <v>2.014559582588827E-3</v>
+        <v>2.1281368582487538E-3</v>
       </c>
       <c r="N9">
-        <v>2.1080620809860889E-4</v>
+        <v>1.6227764023620072E-3</v>
       </c>
       <c r="O9">
-        <v>-1.925372894737605E-4</v>
+        <v>-3.6426511240648257E-4</v>
       </c>
       <c r="P9">
-        <v>-1.4144342851001176E-4</v>
+        <v>-1.0649904882898721E-4</v>
       </c>
       <c r="Q9">
-        <v>-2.4760000721439678E-4</v>
+        <v>2.3529619841122708E-5</v>
       </c>
       <c r="R9">
-        <v>-2.1514326770911583E-4</v>
+        <v>-1.9777414909828397E-4</v>
       </c>
       <c r="S9">
-        <v>-1.1493286791516895E-4</v>
+        <v>-6.2411402324679928E-5</v>
       </c>
       <c r="T9">
-        <v>-8.8546001924674723E-5</v>
+        <v>1.3881636743120481E-4</v>
       </c>
       <c r="U9">
-        <v>-2.4214016544321247E-5</v>
+        <v>3.4149069492930102E-5</v>
       </c>
       <c r="V9">
-        <v>-2.6647471732395202E-5</v>
+        <v>-9.492733634786603E-5</v>
       </c>
       <c r="W9">
-        <v>-4.3016027738813982E-4</v>
+        <v>6.0030106901738851E-5</v>
       </c>
       <c r="X9">
-        <v>-5.9587237419699186E-5</v>
+        <v>-4.4014557325362216E-4</v>
       </c>
       <c r="Y9">
-        <v>5.2332234867601265E-6</v>
+        <v>-6.6296903178857634E-5</v>
       </c>
       <c r="Z9">
-        <v>-3.9498739419105162E-5</v>
+        <v>-1.0942222301353111E-5</v>
       </c>
       <c r="AA9">
-        <v>1.3407181033159169E-6</v>
+        <v>5.3821302802515875E-5</v>
       </c>
       <c r="AB9">
-        <v>1.8265797415208422E-4</v>
+        <v>-4.4105683785933378E-5</v>
       </c>
       <c r="AC9">
-        <v>1.9311301516016129E-4</v>
+        <v>7.777302847041586E-5</v>
       </c>
       <c r="AD9">
-        <v>2.2240361721406938E-4</v>
+        <v>-1.9751254821681347E-4</v>
       </c>
       <c r="AE9">
-        <v>-3.93532726756886E-3</v>
-      </c>
-    </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.2">
+        <v>-1.3259019736037081E-5</v>
+      </c>
+      <c r="AF9">
+        <v>-5.7682647594389045E-3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>21</v>
       </c>
       <c r="B10">
-        <v>-0.25782213871005205</v>
+        <v>-0.11101839269930437</v>
       </c>
       <c r="C10">
-        <v>1.6837730078171067E-4</v>
+        <v>1.3433701185813936E-4</v>
       </c>
       <c r="D10">
-        <v>1.1407331867113149E-4</v>
+        <v>3.2910446154502885E-4</v>
       </c>
       <c r="E10">
-        <v>-1.7838292934820973E-6</v>
+        <v>-5.6048751393461587E-6</v>
       </c>
       <c r="F10">
-        <v>-6.7226492001986335E-5</v>
+        <v>4.6845558334803524E-5</v>
       </c>
       <c r="G10">
-        <v>1.7010540421167936E-4</v>
+        <v>1.7484144327233335E-5</v>
       </c>
       <c r="H10">
-        <v>1.6098748218543691E-3</v>
+        <v>1.8235407865441783E-4</v>
       </c>
       <c r="I10">
-        <v>2.236760609438726E-3</v>
+        <v>1.0281292675592643E-3</v>
       </c>
       <c r="J10">
-        <v>2.322440557535325E-3</v>
+        <v>1.6173685000352136E-3</v>
       </c>
       <c r="K10">
-        <v>3.7086030158952304E-3</v>
+        <v>3.1686606126896202E-3</v>
       </c>
       <c r="L10">
-        <v>2.7932948388144124E-3</v>
+        <v>2.2253028858731779E-3</v>
       </c>
       <c r="M10">
-        <v>2.3474371875728223E-3</v>
+        <v>2.1801257428236578E-3</v>
       </c>
       <c r="N10">
-        <v>2.3267375902124503E-4</v>
+        <v>1.969635132958844E-3</v>
       </c>
       <c r="O10">
-        <v>-1.6859372068152041E-4</v>
+        <v>2.3397990037411971E-4</v>
       </c>
       <c r="P10">
-        <v>-1.8935514396263548E-4</v>
+        <v>-1.1536177755304129E-4</v>
       </c>
       <c r="Q10">
-        <v>-2.9089427538773972E-4</v>
+        <v>3.5844201006782444E-5</v>
       </c>
       <c r="R10">
-        <v>-2.5586089345017594E-4</v>
+        <v>-1.6006459339084836E-4</v>
       </c>
       <c r="S10">
-        <v>-7.3998415140113101E-5</v>
+        <v>-9.8557574322383256E-5</v>
       </c>
       <c r="T10">
-        <v>-1.5742041863316689E-4</v>
+        <v>-5.7193411811561637E-5</v>
       </c>
       <c r="U10">
-        <v>-2.0806817057532757E-4</v>
+        <v>-2.7086077731052881E-5</v>
       </c>
       <c r="V10">
-        <v>-1.240682438938659E-4</v>
+        <v>2.4730471848987551E-5</v>
       </c>
       <c r="W10">
-        <v>-7.0470382499248361E-4</v>
+        <v>1.8731504269444332E-4</v>
       </c>
       <c r="X10">
-        <v>-1.0864930364699963E-4</v>
+        <v>-4.0606137750241018E-4</v>
       </c>
       <c r="Y10">
-        <v>3.2911397601400856E-6</v>
+        <v>-1.800926872857567E-5</v>
       </c>
       <c r="Z10">
-        <v>9.5158029803746547E-5</v>
+        <v>3.464963209568535E-6</v>
       </c>
       <c r="AA10">
-        <v>6.7721159702267331E-5</v>
+        <v>-4.3502193654356146E-5</v>
       </c>
       <c r="AB10">
-        <v>2.9690841027047192E-4</v>
+        <v>5.5214484269356973E-6</v>
       </c>
       <c r="AC10">
-        <v>3.2829573453441695E-5</v>
+        <v>1.3798068443338866E-4</v>
       </c>
       <c r="AD10">
-        <v>1.9075533992781281E-4</v>
+        <v>1.6042587488563406E-4</v>
       </c>
       <c r="AE10">
-        <v>-4.5922890442269965E-3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.2">
+        <v>1.4390576215908237E-4</v>
+      </c>
+      <c r="AF10">
+        <v>-7.0144060457698106E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>22</v>
       </c>
       <c r="B11">
-        <v>-0.10211638883400255</v>
+        <v>-0.25718639477129263</v>
       </c>
       <c r="C11">
-        <v>1.8307476985138661E-4</v>
+        <v>1.4362906355992955E-4</v>
       </c>
       <c r="D11">
-        <v>1.1819494535253818E-4</v>
+        <v>2.5996012241122335E-4</v>
       </c>
       <c r="E11">
-        <v>-2.3804769169569719E-6</v>
+        <v>-4.4428458269934562E-6</v>
       </c>
       <c r="F11">
-        <v>1.4021060243848309E-4</v>
+        <v>-2.2933061411999881E-4</v>
       </c>
       <c r="G11">
-        <v>4.1257565493650822E-4</v>
+        <v>-3.83540622167001E-6</v>
       </c>
       <c r="H11">
-        <v>1.5259335329889823E-3</v>
+        <v>2.2437071098977649E-4</v>
       </c>
       <c r="I11">
-        <v>2.2257994948709898E-3</v>
+        <v>1.7204766728795579E-3</v>
       </c>
       <c r="J11">
-        <v>2.2904723341788582E-3</v>
+        <v>2.1371410208063917E-3</v>
       </c>
       <c r="K11">
-        <v>2.7932948388144124E-3</v>
+        <v>2.2253028858731779E-3</v>
       </c>
       <c r="L11">
-        <v>3.8842549820459309E-3</v>
+        <v>3.6021100246888395E-3</v>
       </c>
       <c r="M11">
-        <v>2.3914592793874822E-3</v>
+        <v>2.6912521058714391E-3</v>
       </c>
       <c r="N11">
-        <v>-9.72319652447443E-6</v>
+        <v>2.2895887241131977E-3</v>
       </c>
       <c r="O11">
-        <v>2.1343269416563746E-4</v>
+        <v>2.7184390920743061E-4</v>
       </c>
       <c r="P11">
-        <v>1.4123856767088308E-4</v>
+        <v>-1.0510373909602055E-4</v>
       </c>
       <c r="Q11">
-        <v>-1.417117531285988E-4</v>
+        <v>-6.1530464232545162E-5</v>
       </c>
       <c r="R11">
-        <v>-1.2373352281797858E-4</v>
+        <v>-2.3052912983246096E-4</v>
       </c>
       <c r="S11">
-        <v>-3.0438834279161226E-5</v>
+        <v>-1.8109991435215453E-4</v>
       </c>
       <c r="T11">
-        <v>2.3854383263835336E-4</v>
+        <v>-2.835031747376658E-5</v>
       </c>
       <c r="U11">
-        <v>-6.8594786761098708E-5</v>
+        <v>-9.7199705675142089E-5</v>
       </c>
       <c r="V11">
-        <v>1.6749596512831877E-4</v>
+        <v>-1.5281774963111258E-4</v>
       </c>
       <c r="W11">
-        <v>-4.6364332681867506E-4</v>
+        <v>1.1558556674471439E-5</v>
       </c>
       <c r="X11">
-        <v>9.9729058016456446E-5</v>
+        <v>-6.6425046641433848E-4</v>
       </c>
       <c r="Y11">
-        <v>2.1660693554577382E-5</v>
+        <v>-6.404096945532723E-5</v>
       </c>
       <c r="Z11">
-        <v>-9.601522902623455E-6</v>
+        <v>1.5471141574857281E-6</v>
       </c>
       <c r="AA11">
-        <v>-1.9869326021490453E-5</v>
+        <v>9.4938867879374274E-5</v>
       </c>
       <c r="AB11">
-        <v>2.8973525477011771E-4</v>
+        <v>6.7860537026259119E-5</v>
       </c>
       <c r="AC11">
-        <v>1.0710341007257808E-3</v>
+        <v>2.8999327648147801E-4</v>
       </c>
       <c r="AD11">
-        <v>3.7638181847277877E-4</v>
+        <v>4.1427333061940137E-5</v>
       </c>
       <c r="AE11">
-        <v>-5.0173087365462787E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.2">
+        <v>1.4636320971836723E-4</v>
+      </c>
+      <c r="AF11">
+        <v>-6.4809373635966987E-3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>23</v>
       </c>
       <c r="B12">
-        <v>-4.2447204812374538E-2</v>
+        <v>-0.10169372408723946</v>
       </c>
       <c r="C12">
-        <v>5.1005132907317005E-5</v>
+        <v>1.4969478050918337E-4</v>
       </c>
       <c r="D12">
-        <v>3.6006293135907317E-4</v>
+        <v>2.5911096908810122E-4</v>
       </c>
       <c r="E12">
-        <v>-6.6372830091126364E-6</v>
+        <v>-4.9496581091379433E-6</v>
       </c>
       <c r="F12">
-        <v>1.8725882435280969E-4</v>
+        <v>-3.269752371923122E-5</v>
       </c>
       <c r="G12">
-        <v>5.2386910137350328E-4</v>
+        <v>2.7833817273945836E-4</v>
       </c>
       <c r="H12">
-        <v>1.161343787269572E-3</v>
+        <v>5.3156924897645574E-4</v>
       </c>
       <c r="I12">
-        <v>1.6874723562210277E-3</v>
+        <v>1.6070944659217674E-3</v>
       </c>
       <c r="J12">
-        <v>2.014559582588827E-3</v>
+        <v>2.1281368582487538E-3</v>
       </c>
       <c r="K12">
-        <v>2.3474371875728223E-3</v>
+        <v>2.1801257428236578E-3</v>
       </c>
       <c r="L12">
-        <v>2.3914592793874822E-3</v>
+        <v>2.6912521058714391E-3</v>
       </c>
       <c r="M12">
-        <v>4.7241367224645442E-3</v>
+        <v>3.7950636466547462E-3</v>
       </c>
       <c r="N12">
-        <v>1.6639963122036332E-4</v>
+        <v>2.3604506758853226E-3</v>
       </c>
       <c r="O12">
-        <v>1.4855486046188009E-4</v>
+        <v>4.6097849759680959E-5</v>
       </c>
       <c r="P12">
-        <v>9.875668717656286E-5</v>
+        <v>2.7978522933678595E-4</v>
       </c>
       <c r="Q12">
-        <v>-1.6163878192911485E-4</v>
+        <v>2.6427746861688438E-4</v>
       </c>
       <c r="R12">
-        <v>-7.5138701609503661E-5</v>
+        <v>-8.1134669808167033E-5</v>
       </c>
       <c r="S12">
-        <v>1.2942246847655163E-4</v>
+        <v>-4.5634837406131109E-5</v>
       </c>
       <c r="T12">
-        <v>3.0175555293904515E-5</v>
+        <v>1.4013586579809332E-5</v>
       </c>
       <c r="U12">
-        <v>-6.3333323770845581E-5</v>
+        <v>2.9747401395108849E-4</v>
       </c>
       <c r="V12">
-        <v>1.2562164006015898E-4</v>
+        <v>-2.7753711846173739E-5</v>
       </c>
       <c r="W12">
-        <v>-5.0388385255079927E-4</v>
+        <v>2.9856021505670624E-4</v>
       </c>
       <c r="X12">
-        <v>8.2113781840541938E-5</v>
+        <v>-4.2062670227277136E-4</v>
       </c>
       <c r="Y12">
-        <v>-1.3649194648799701E-5</v>
+        <v>1.4844073235358891E-4</v>
       </c>
       <c r="Z12">
-        <v>1.3307300721414025E-6</v>
+        <v>1.9843368338410845E-5</v>
       </c>
       <c r="AA12">
-        <v>9.6405769183027963E-5</v>
+        <v>-1.421721672999253E-5</v>
       </c>
       <c r="AB12">
-        <v>8.7885074478018157E-5</v>
+        <v>-1.9797213126812043E-5</v>
       </c>
       <c r="AC12">
-        <v>5.0069336645541893E-4</v>
+        <v>3.0147059722249658E-4</v>
       </c>
       <c r="AD12">
-        <v>1.7276354388240416E-4</v>
+        <v>1.082859674476654E-3</v>
       </c>
       <c r="AE12">
-        <v>-7.1497321724051394E-3</v>
-      </c>
-    </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.2">
+        <v>3.3483355004522593E-4</v>
+      </c>
+      <c r="AF12">
+        <v>-6.8969492390412186E-3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>24</v>
       </c>
       <c r="B13">
-        <v>-5.3210321474670225E-2</v>
+        <v>-4.2375228765302218E-2</v>
       </c>
       <c r="C13">
-        <v>-1.6756409050416445E-4</v>
+        <v>1.9635896086423577E-5</v>
       </c>
       <c r="D13">
-        <v>3.0751499614768566E-4</v>
+        <v>5.0582283882276489E-4</v>
       </c>
       <c r="E13">
-        <v>-5.5843662216286988E-6</v>
+        <v>-9.3088091981656037E-6</v>
       </c>
       <c r="F13">
-        <v>4.1979631441332725E-4</v>
+        <v>-7.8204176065001674E-5</v>
       </c>
       <c r="G13">
-        <v>4.8723691488297563E-4</v>
+        <v>3.5678371335411997E-4</v>
       </c>
       <c r="H13">
-        <v>-1.6627462911186644E-4</v>
+        <v>6.7200452711455071E-4</v>
       </c>
       <c r="I13">
-        <v>-3.8518266337743076E-4</v>
+        <v>1.3044449891990305E-3</v>
       </c>
       <c r="J13">
-        <v>2.1080620809860889E-4</v>
+        <v>1.6227764023620072E-3</v>
       </c>
       <c r="K13">
-        <v>2.3267375902124503E-4</v>
+        <v>1.969635132958844E-3</v>
       </c>
       <c r="L13">
-        <v>-9.72319652447443E-6</v>
+        <v>2.2895887241131977E-3</v>
       </c>
       <c r="M13">
-        <v>1.6639963122036332E-4</v>
+        <v>2.3604506758853226E-3</v>
       </c>
       <c r="N13">
-        <v>1.0022320550449259E-2</v>
+        <v>4.730495849823867E-3</v>
       </c>
       <c r="O13">
-        <v>2.5121325632044421E-3</v>
+        <v>2.2693943006640046E-4</v>
       </c>
       <c r="P13">
-        <v>2.5872066002731353E-3</v>
+        <v>2.3094079260865558E-4</v>
       </c>
       <c r="Q13">
-        <v>2.5986526662081328E-3</v>
+        <v>2.2290811828302033E-4</v>
       </c>
       <c r="R13">
-        <v>2.4232564836916969E-3</v>
+        <v>-9.6690640576072354E-5</v>
       </c>
       <c r="S13">
-        <v>2.5347363690243359E-3</v>
+        <v>1.010828698106152E-5</v>
       </c>
       <c r="T13">
-        <v>2.9478230383117032E-3</v>
+        <v>1.7962528989545279E-4</v>
       </c>
       <c r="U13">
-        <v>2.6747852623793624E-3</v>
+        <v>9.8729803759006925E-5</v>
       </c>
       <c r="V13">
-        <v>2.6740025790139756E-3</v>
+        <v>-2.2595430780857962E-5</v>
       </c>
       <c r="W13">
-        <v>2.6445667520989084E-3</v>
+        <v>2.5770867538976066E-4</v>
       </c>
       <c r="X13">
-        <v>2.6755692159541409E-3</v>
+        <v>-4.5250298042239689E-4</v>
       </c>
       <c r="Y13">
-        <v>5.3050356581477035E-5</v>
+        <v>1.3714088259977886E-4</v>
       </c>
       <c r="Z13">
-        <v>-3.3061981479276016E-4</v>
+        <v>-1.3915280044423067E-5</v>
       </c>
       <c r="AA13">
-        <v>-3.5368318013078565E-4</v>
+        <v>-2.4702454943775396E-5</v>
       </c>
       <c r="AB13">
-        <v>8.640014404297571E-4</v>
+        <v>9.1966178694389005E-5</v>
       </c>
       <c r="AC13">
-        <v>4.0798763949485683E-3</v>
+        <v>1.1749946571311745E-4</v>
       </c>
       <c r="AD13">
-        <v>6.8765637421166212E-4</v>
+        <v>5.7524318997224499E-4</v>
       </c>
       <c r="AE13">
-        <v>-7.8608146394417936E-3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.2">
+        <v>1.2756104613542886E-4</v>
+      </c>
+      <c r="AF13">
+        <v>-9.1896095843771019E-3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14">
-        <v>0.18019671034921061</v>
+        <v>-6.7537800332445774E-2</v>
       </c>
       <c r="C14">
-        <v>1.662230055640984E-4</v>
+        <v>-1.5529268109889887E-4</v>
       </c>
       <c r="D14">
-        <v>2.4588557925959119E-4</v>
+        <v>2.8027296158254214E-4</v>
       </c>
       <c r="E14">
-        <v>-4.9818823705450639E-6</v>
+        <v>-5.1601543477111712E-6</v>
       </c>
       <c r="F14">
-        <v>3.6690318672919593E-4</v>
+        <v>1.968024775126202E-4</v>
       </c>
       <c r="G14">
-        <v>2.6106346470773428E-4</v>
+        <v>4.3582471197963998E-4</v>
       </c>
       <c r="H14">
-        <v>-7.1657018774787425E-5</v>
+        <v>5.334708496636492E-4</v>
       </c>
       <c r="I14">
-        <v>-1.4025417403930492E-4</v>
+        <v>-1.7272541229972885E-4</v>
       </c>
       <c r="J14">
-        <v>-1.925372894737605E-4</v>
+        <v>-3.6426511240648257E-4</v>
       </c>
       <c r="K14">
-        <v>-1.6859372068152041E-4</v>
+        <v>2.3397990037411971E-4</v>
       </c>
       <c r="L14">
-        <v>2.1343269416563746E-4</v>
+        <v>2.7184390920743061E-4</v>
       </c>
       <c r="M14">
-        <v>1.4855486046188009E-4</v>
+        <v>4.6097849759680959E-5</v>
       </c>
       <c r="N14">
-        <v>2.5121325632044421E-3</v>
+        <v>2.2693943006640046E-4</v>
       </c>
       <c r="O14">
-        <v>4.9366589501847807E-3</v>
+        <v>9.9610437127468244E-3</v>
       </c>
       <c r="P14">
-        <v>2.5341729398844983E-3</v>
+        <v>2.5437999938117558E-3</v>
       </c>
       <c r="Q14">
-        <v>2.544969480455773E-3</v>
+        <v>2.6002442177631563E-3</v>
       </c>
       <c r="R14">
-        <v>2.4184731926747464E-3</v>
+        <v>2.60250501900108E-3</v>
       </c>
       <c r="S14">
-        <v>2.4860019220449962E-3</v>
+        <v>2.4446326628455506E-3</v>
       </c>
       <c r="T14">
-        <v>2.8341902152415415E-3</v>
+        <v>2.558143057209685E-3</v>
       </c>
       <c r="U14">
-        <v>2.5797366183455774E-3</v>
+        <v>2.960361236013973E-3</v>
       </c>
       <c r="V14">
-        <v>2.6486969446011567E-3</v>
+        <v>2.690620687459002E-3</v>
       </c>
       <c r="W14">
-        <v>2.5915649745999556E-3</v>
+        <v>2.6931009418376438E-3</v>
       </c>
       <c r="X14">
-        <v>2.6051491663760242E-3</v>
+        <v>2.67150611730109E-3</v>
       </c>
       <c r="Y14">
-        <v>6.3848391747433676E-5</v>
+        <v>2.7021111428959009E-3</v>
       </c>
       <c r="Z14">
-        <v>-3.9045973402864116E-4</v>
+        <v>5.166515283836447E-5</v>
       </c>
       <c r="AA14">
-        <v>-1.939464363324544E-4</v>
+        <v>-3.5445431679852196E-4</v>
       </c>
       <c r="AB14">
-        <v>6.0224779842726298E-4</v>
+        <v>-3.5236329918160328E-4</v>
       </c>
       <c r="AC14">
-        <v>3.7283013199375342E-3</v>
+        <v>8.836250317549463E-4</v>
       </c>
       <c r="AD14">
-        <v>4.1663830078365383E-4</v>
+        <v>4.0826869466348507E-3</v>
       </c>
       <c r="AE14">
-        <v>-6.8897660269216544E-3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:31" x14ac:dyDescent="0.2">
+        <v>6.9708163366788954E-4</v>
+      </c>
+      <c r="AF14">
+        <v>-7.5071007540232692E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
       <c r="B15">
-        <v>0.17452486868536413</v>
+        <v>0.16833671737694358</v>
       </c>
       <c r="C15">
-        <v>1.6181593453577461E-5</v>
+        <v>1.6340289846084841E-4</v>
       </c>
       <c r="D15">
-        <v>3.3599924276807725E-4</v>
+        <v>2.320916846641442E-4</v>
       </c>
       <c r="E15">
-        <v>-6.4697383011483434E-6</v>
+        <v>-4.7744167412468636E-6</v>
       </c>
       <c r="F15">
-        <v>2.1112382243047509E-4</v>
+        <v>3.9191593996575503E-5</v>
       </c>
       <c r="G15">
-        <v>2.3627509804795651E-4</v>
+        <v>3.8665993380054137E-4</v>
       </c>
       <c r="H15">
-        <v>2.7186239300046149E-5</v>
+        <v>3.1577125179988027E-4</v>
       </c>
       <c r="I15">
-        <v>-5.8675835403398371E-5</v>
+        <v>1.9204317599709649E-6</v>
       </c>
       <c r="J15">
-        <v>-1.4144342851001176E-4</v>
+        <v>-1.0649904882898721E-4</v>
       </c>
       <c r="K15">
-        <v>-1.8935514396263548E-4</v>
+        <v>-1.1536177755304129E-4</v>
       </c>
       <c r="L15">
-        <v>1.4123856767088308E-4</v>
+        <v>-1.0510373909602055E-4</v>
       </c>
       <c r="M15">
-        <v>9.875668717656286E-5</v>
+        <v>2.7978522933678595E-4</v>
       </c>
       <c r="N15">
-        <v>2.5872066002731353E-3</v>
+        <v>2.3094079260865558E-4</v>
       </c>
       <c r="O15">
-        <v>2.5341729398844983E-3</v>
+        <v>2.5437999938117558E-3</v>
       </c>
       <c r="P15">
-        <v>5.0408197013070977E-3</v>
+        <v>4.9429388639092246E-3</v>
       </c>
       <c r="Q15">
-        <v>2.6064231096127504E-3</v>
+        <v>2.5442544348095392E-3</v>
       </c>
       <c r="R15">
-        <v>2.4657508774558489E-3</v>
+        <v>2.5533095278191904E-3</v>
       </c>
       <c r="S15">
-        <v>2.549288955785808E-3</v>
+        <v>2.4370313183131958E-3</v>
       </c>
       <c r="T15">
-        <v>2.8936903134150756E-3</v>
+        <v>2.5024206466494271E-3</v>
       </c>
       <c r="U15">
-        <v>2.6738850493223496E-3</v>
+        <v>2.8361268935977258E-3</v>
       </c>
       <c r="V15">
-        <v>2.7020964865515735E-3</v>
+        <v>2.593167226664353E-3</v>
       </c>
       <c r="W15">
-        <v>2.6748824615748386E-3</v>
+        <v>2.6686997482110726E-3</v>
       </c>
       <c r="X15">
-        <v>2.6207323095914581E-3</v>
+        <v>2.6117987398632673E-3</v>
       </c>
       <c r="Y15">
-        <v>2.3063138114478112E-5</v>
+        <v>2.6257306852547737E-3</v>
       </c>
       <c r="Z15">
-        <v>-2.3912498025086551E-4</v>
+        <v>6.2053314703571861E-5</v>
       </c>
       <c r="AA15">
-        <v>1.9723470932403106E-4</v>
+        <v>-4.013320078186444E-4</v>
       </c>
       <c r="AB15">
-        <v>7.7764997963329586E-4</v>
+        <v>-1.9171875709240831E-4</v>
       </c>
       <c r="AC15">
-        <v>3.7910794330858542E-3</v>
+        <v>6.2520699498085975E-4</v>
       </c>
       <c r="AD15">
-        <v>6.5801033590116246E-4</v>
+        <v>3.7233483070655462E-3</v>
       </c>
       <c r="AE15">
-        <v>-7.4029150966422397E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:31" x14ac:dyDescent="0.2">
+        <v>4.2949958651375013E-4</v>
+      </c>
+      <c r="AF15">
+        <v>-6.7386493439850507E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>27</v>
       </c>
       <c r="B16">
-        <v>7.8432395370250541E-2</v>
+        <v>0.16129324501572315</v>
       </c>
       <c r="C16">
-        <v>5.3356987382376689E-6</v>
+        <v>2.1289421178969284E-5</v>
       </c>
       <c r="D16">
-        <v>2.3877822860431379E-4</v>
+        <v>3.3612945322286322E-4</v>
       </c>
       <c r="E16">
-        <v>-4.6239148649851091E-6</v>
+        <v>-6.4722889666835487E-6</v>
       </c>
       <c r="F16">
-        <v>1.6896290576812119E-4</v>
+        <v>1.2229678380336058E-4</v>
       </c>
       <c r="G16">
-        <v>1.9848455177190987E-4</v>
+        <v>2.2576525796526222E-4</v>
       </c>
       <c r="H16">
-        <v>2.6106875032902552E-5</v>
+        <v>2.7781265807227457E-4</v>
       </c>
       <c r="I16">
-        <v>-2.3661412842095134E-4</v>
+        <v>4.1342716082856136E-5</v>
       </c>
       <c r="J16">
-        <v>-2.4760000721439678E-4</v>
+        <v>2.3529619841122708E-5</v>
       </c>
       <c r="K16">
-        <v>-2.9089427538773972E-4</v>
+        <v>3.5844201006782444E-5</v>
       </c>
       <c r="L16">
-        <v>-1.417117531285988E-4</v>
+        <v>-6.1530464232545162E-5</v>
       </c>
       <c r="M16">
-        <v>-1.6163878192911485E-4</v>
+        <v>2.6427746861688438E-4</v>
       </c>
       <c r="N16">
-        <v>2.5986526662081328E-3</v>
+        <v>2.2290811828302033E-4</v>
       </c>
       <c r="O16">
-        <v>2.544969480455773E-3</v>
+        <v>2.6002442177631563E-3</v>
       </c>
       <c r="P16">
-        <v>2.6064231096127504E-3</v>
+        <v>2.5442544348095392E-3</v>
       </c>
       <c r="Q16">
-        <v>5.1511462597021822E-3</v>
+        <v>5.0372129387980741E-3</v>
       </c>
       <c r="R16">
-        <v>2.4921675289081764E-3</v>
+        <v>2.6001298384376701E-3</v>
       </c>
       <c r="S16">
-        <v>2.5724971209959385E-3</v>
+        <v>2.4693490410888789E-3</v>
       </c>
       <c r="T16">
-        <v>2.9414095360766673E-3</v>
+        <v>2.5600242323224722E-3</v>
       </c>
       <c r="U16">
-        <v>2.7055990208078506E-3</v>
+        <v>2.8879344376244007E-3</v>
       </c>
       <c r="V16">
-        <v>2.7138451408494722E-3</v>
+        <v>2.673763104855714E-3</v>
       </c>
       <c r="W16">
-        <v>2.6702630930883968E-3</v>
+        <v>2.7009555285118763E-3</v>
       </c>
       <c r="X16">
-        <v>2.6623625659362819E-3</v>
+        <v>2.6875183056754483E-3</v>
       </c>
       <c r="Y16">
-        <v>1.55021775945218E-5</v>
+        <v>2.6317172248474779E-3</v>
       </c>
       <c r="Z16">
-        <v>-3.335063633469087E-5</v>
+        <v>2.2938560151833246E-5</v>
       </c>
       <c r="AA16">
-        <v>-7.8010941309687254E-5</v>
+        <v>-2.454278741564549E-4</v>
       </c>
       <c r="AB16">
-        <v>7.8357147469100877E-4</v>
+        <v>1.9687079064206801E-4</v>
       </c>
       <c r="AC16">
-        <v>3.8621427825652646E-3</v>
+        <v>7.9523786611517303E-4</v>
       </c>
       <c r="AD16">
-        <v>5.6077753856394858E-4</v>
+        <v>3.7674862622241877E-3</v>
       </c>
       <c r="AE16">
-        <v>-5.8583659104293577E-3</v>
-      </c>
-    </row>
-    <row r="17" spans="1:31" x14ac:dyDescent="0.2">
+        <v>6.705768760565373E-4</v>
+      </c>
+      <c r="AF16">
+        <v>-7.5447656928781604E-3</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17">
-        <v>5.9866018534232089E-2</v>
+        <v>6.8939149905630021E-2</v>
       </c>
       <c r="C17">
-        <v>6.2641293248999437E-5</v>
+        <v>6.4434250311572973E-6</v>
       </c>
       <c r="D17">
-        <v>2.3623889733457313E-4</v>
+        <v>2.5331675022573767E-4</v>
       </c>
       <c r="E17">
-        <v>-4.6719676109688849E-6</v>
+        <v>-4.8878282369641678E-6</v>
       </c>
       <c r="F17">
-        <v>2.2946851768483741E-4</v>
+        <v>1.8200220245876344E-4</v>
       </c>
       <c r="G17">
-        <v>-5.6092428577259068E-5</v>
+        <v>1.9830865385825916E-4</v>
       </c>
       <c r="H17">
-        <v>-1.5104835718476439E-4</v>
+        <v>2.3920822292268474E-4</v>
       </c>
       <c r="I17">
-        <v>-1.1226720564236608E-4</v>
+        <v>-6.491178353127151E-7</v>
       </c>
       <c r="J17">
-        <v>-2.1514326770911583E-4</v>
+        <v>-1.9777414909828397E-4</v>
       </c>
       <c r="K17">
-        <v>-2.5586089345017594E-4</v>
+        <v>-1.6006459339084836E-4</v>
       </c>
       <c r="L17">
-        <v>-1.2373352281797858E-4</v>
+        <v>-2.3052912983246096E-4</v>
       </c>
       <c r="M17">
-        <v>-7.5138701609503661E-5</v>
+        <v>-8.1134669808167033E-5</v>
       </c>
       <c r="N17">
-        <v>2.4232564836916969E-3</v>
+        <v>-9.6690640576072354E-5</v>
       </c>
       <c r="O17">
-        <v>2.4184731926747464E-3</v>
+        <v>2.60250501900108E-3</v>
       </c>
       <c r="P17">
-        <v>2.4657508774558489E-3</v>
+        <v>2.5533095278191904E-3</v>
       </c>
       <c r="Q17">
-        <v>2.4921675289081764E-3</v>
+        <v>2.6001298384376701E-3</v>
       </c>
       <c r="R17">
-        <v>5.4227986374468387E-3</v>
+        <v>5.1542562365659746E-3</v>
       </c>
       <c r="S17">
-        <v>2.4432766098324106E-3</v>
+        <v>2.4958350941403739E-3</v>
       </c>
       <c r="T17">
-        <v>2.791817385060162E-3</v>
+        <v>2.5833035732770104E-3</v>
       </c>
       <c r="U17">
-        <v>2.5345531219736453E-3</v>
+        <v>2.9336285746020319E-3</v>
       </c>
       <c r="V17">
-        <v>2.5638419159647913E-3</v>
+        <v>2.7028694385049855E-3</v>
       </c>
       <c r="W17">
-        <v>2.5143091038747965E-3</v>
+        <v>2.7133569256387463E-3</v>
       </c>
       <c r="X17">
-        <v>2.5240433015959779E-3</v>
+        <v>2.6828811327583913E-3</v>
       </c>
       <c r="Y17">
-        <v>4.8088342975039297E-5</v>
+        <v>2.6678274312721189E-3</v>
       </c>
       <c r="Z17">
-        <v>-3.5511256265554421E-4</v>
+        <v>1.6382463128005733E-5</v>
       </c>
       <c r="AA17">
-        <v>-2.7227025082740092E-4</v>
+        <v>-6.9571271212558503E-5</v>
       </c>
       <c r="AB17">
-        <v>2.2049382169779823E-4</v>
+        <v>-8.4003396433393032E-5</v>
       </c>
       <c r="AC17">
-        <v>3.7102097712881105E-3</v>
+        <v>7.9651402997497314E-4</v>
       </c>
       <c r="AD17">
-        <v>2.1534853343267108E-4</v>
+        <v>3.8274021701565058E-3</v>
       </c>
       <c r="AE17">
-        <v>-6.1966872707844636E-3</v>
-      </c>
-    </row>
-    <row r="18" spans="1:31" x14ac:dyDescent="0.2">
+        <v>5.647207535889677E-4</v>
+      </c>
+      <c r="AF17">
+        <v>-6.1490466953348505E-3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>29</v>
       </c>
       <c r="B18">
-        <v>2.6411486540465667E-2</v>
+        <v>4.894321766648832E-2</v>
       </c>
       <c r="C18">
-        <v>-3.2195274102895992E-5</v>
+        <v>5.9646024902017735E-5</v>
       </c>
       <c r="D18">
-        <v>3.0352060479769483E-4</v>
+        <v>2.3121237053660266E-4</v>
       </c>
       <c r="E18">
-        <v>-5.6410671585207429E-6</v>
+        <v>-4.601562683222023E-6</v>
       </c>
       <c r="F18">
-        <v>1.7465178024838582E-4</v>
+        <v>-1.6945566355887082E-5</v>
       </c>
       <c r="G18">
-        <v>-1.7238590888518464E-4</v>
+        <v>2.3841999109407435E-4</v>
       </c>
       <c r="H18">
-        <v>1.4747979654594287E-4</v>
+        <v>-7.3357989133670067E-5</v>
       </c>
       <c r="I18">
-        <v>1.1462038418311708E-4</v>
+        <v>-8.6205647767372299E-5</v>
       </c>
       <c r="J18">
-        <v>-1.1493286791516895E-4</v>
+        <v>-6.2411402324679928E-5</v>
       </c>
       <c r="K18">
-        <v>-7.3998415140113101E-5</v>
+        <v>-9.8557574322383256E-5</v>
       </c>
       <c r="L18">
-        <v>-3.0438834279161226E-5</v>
+        <v>-1.8109991435215453E-4</v>
       </c>
       <c r="M18">
-        <v>1.2942246847655163E-4</v>
+        <v>-4.5634837406131109E-5</v>
       </c>
       <c r="N18">
-        <v>2.5347363690243359E-3</v>
+        <v>1.010828698106152E-5</v>
       </c>
       <c r="O18">
-        <v>2.4860019220449962E-3</v>
+        <v>2.4446326628455506E-3</v>
       </c>
       <c r="P18">
-        <v>2.549288955785808E-3</v>
+        <v>2.4370313183131958E-3</v>
       </c>
       <c r="Q18">
-        <v>2.5724971209959385E-3</v>
+        <v>2.4693490410888789E-3</v>
       </c>
       <c r="R18">
-        <v>2.4432766098324106E-3</v>
+        <v>2.4958350941403739E-3</v>
       </c>
       <c r="S18">
-        <v>5.1109734336883608E-3</v>
+        <v>5.4338628043113834E-3</v>
       </c>
       <c r="T18">
-        <v>2.8605465436060233E-3</v>
+        <v>2.4593825306241206E-3</v>
       </c>
       <c r="U18">
-        <v>2.6620074476919045E-3</v>
+        <v>2.7913310608169021E-3</v>
       </c>
       <c r="V18">
-        <v>2.6777513320349637E-3</v>
+        <v>2.5418104851318243E-3</v>
       </c>
       <c r="W18">
-        <v>2.6410710079755807E-3</v>
+        <v>2.5735567501558631E-3</v>
       </c>
       <c r="X18">
-        <v>2.6259649815891812E-3</v>
+        <v>2.5372961990088537E-3</v>
       </c>
       <c r="Y18">
-        <v>1.3884871210150223E-5</v>
+        <v>2.5419697493696642E-3</v>
       </c>
       <c r="Z18">
-        <v>-3.6539529091222139E-5</v>
+        <v>4.6911315654731803E-5</v>
       </c>
       <c r="AA18">
-        <v>-7.8220337956249838E-6</v>
+        <v>-3.7060446292431072E-4</v>
       </c>
       <c r="AB18">
-        <v>8.320548858839783E-4</v>
+        <v>-2.7033595762525993E-4</v>
       </c>
       <c r="AC18">
-        <v>3.4705819706743876E-3</v>
+        <v>2.2938060598892002E-4</v>
       </c>
       <c r="AD18">
-        <v>4.5439573712119174E-4</v>
+        <v>3.6968217157761557E-3</v>
       </c>
       <c r="AE18">
-        <v>-6.9280385138953257E-3</v>
-      </c>
-    </row>
-    <row r="19" spans="1:31" x14ac:dyDescent="0.2">
+        <v>2.3555444547826711E-4</v>
+      </c>
+      <c r="AF18">
+        <v>-6.1852708304634399E-3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>30</v>
       </c>
       <c r="B19">
-        <v>4.2044019043601406E-3</v>
+        <v>1.7287555765509111E-2</v>
       </c>
       <c r="C19">
-        <v>-6.036192433433014E-5</v>
+        <v>-2.412411564488479E-5</v>
       </c>
       <c r="D19">
-        <v>2.4231764163930823E-4</v>
+        <v>2.9508295579747427E-4</v>
       </c>
       <c r="E19">
-        <v>-4.7279293580410286E-6</v>
+        <v>-5.5307647907283899E-6</v>
       </c>
       <c r="F19">
-        <v>4.1788254493471222E-4</v>
+        <v>-9.9921214716107627E-5</v>
       </c>
       <c r="G19">
-        <v>1.7040369713535581E-4</v>
+        <v>1.5795015446461007E-4</v>
       </c>
       <c r="H19">
-        <v>-5.9136937744112177E-5</v>
+        <v>-1.7090711527230655E-4</v>
       </c>
       <c r="I19">
-        <v>1.8147505900696376E-6</v>
+        <v>2.4095064838562154E-4</v>
       </c>
       <c r="J19">
-        <v>-8.8546001924674723E-5</v>
+        <v>1.3881636743120481E-4</v>
       </c>
       <c r="K19">
-        <v>-1.5742041863316689E-4</v>
+        <v>-5.7193411811561637E-5</v>
       </c>
       <c r="L19">
-        <v>2.3854383263835336E-4</v>
+        <v>-2.835031747376658E-5</v>
       </c>
       <c r="M19">
-        <v>3.0175555293904515E-5</v>
+        <v>1.4013586579809332E-5</v>
       </c>
       <c r="N19">
-        <v>2.9478230383117032E-3</v>
+        <v>1.7962528989545279E-4</v>
       </c>
       <c r="O19">
-        <v>2.8341902152415415E-3</v>
+        <v>2.558143057209685E-3</v>
       </c>
       <c r="P19">
-        <v>2.8936903134150756E-3</v>
+        <v>2.5024206466494271E-3</v>
       </c>
       <c r="Q19">
-        <v>2.9414095360766673E-3</v>
+        <v>2.5600242323224722E-3</v>
       </c>
       <c r="R19">
-        <v>2.791817385060162E-3</v>
+        <v>2.5833035732770104E-3</v>
       </c>
       <c r="S19">
-        <v>2.8605465436060233E-3</v>
+        <v>2.4593825306241206E-3</v>
       </c>
       <c r="T19">
-        <v>5.2539082579279479E-3</v>
+        <v>5.1257475673913569E-3</v>
       </c>
       <c r="U19">
-        <v>3.0206221918056761E-3</v>
+        <v>2.8636425830490457E-3</v>
       </c>
       <c r="V19">
-        <v>3.0722276804035793E-3</v>
+        <v>2.6770660248227503E-3</v>
       </c>
       <c r="W19">
-        <v>3.0476529906321159E-3</v>
+        <v>2.6948403172487347E-3</v>
       </c>
       <c r="X19">
-        <v>3.0407024435006717E-3</v>
+        <v>2.6601865048624831E-3</v>
       </c>
       <c r="Y19">
-        <v>4.1965120184968676E-5</v>
+        <v>2.6431170489514795E-3</v>
       </c>
       <c r="Z19">
-        <v>-2.9990807887933524E-4</v>
+        <v>1.3755972232894675E-5</v>
       </c>
       <c r="AA19">
-        <v>-2.5550372242020549E-4</v>
+        <v>-6.1975807112222422E-5</v>
       </c>
       <c r="AB19">
-        <v>9.9158737611014275E-4</v>
+        <v>-1.9305222792210955E-6</v>
       </c>
       <c r="AC19">
-        <v>6.2900161260970641E-3</v>
+        <v>8.5193195049797937E-4</v>
       </c>
       <c r="AD19">
-        <v>6.8588572307904945E-4</v>
+        <v>3.4698126787947644E-3</v>
       </c>
       <c r="AE19">
-        <v>-6.9917621702153075E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:31" x14ac:dyDescent="0.2">
+        <v>4.6553896826760589E-4</v>
+      </c>
+      <c r="AF19">
+        <v>-6.833533655218561E-3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>31</v>
       </c>
       <c r="B20">
-        <v>0.20275552884670275</v>
+        <v>-3.5956456862079049E-3</v>
       </c>
       <c r="C20">
-        <v>3.3015914756626155E-5</v>
+        <v>-5.8235237810183649E-5</v>
       </c>
       <c r="D20">
-        <v>3.0144618337597079E-4</v>
+        <v>2.2676346763183175E-4</v>
       </c>
       <c r="E20">
-        <v>-5.6918833754125567E-6</v>
+        <v>-4.4725187062759166E-6</v>
       </c>
       <c r="F20">
-        <v>1.5553375934152029E-4</v>
+        <v>3.1591749473021142E-4</v>
       </c>
       <c r="G20">
-        <v>1.6156647440221194E-4</v>
+        <v>4.3242808590066419E-4</v>
       </c>
       <c r="H20">
-        <v>2.7305043314325688E-6</v>
+        <v>2.0925376461486931E-4</v>
       </c>
       <c r="I20">
-        <v>-1.3191056217370001E-4</v>
+        <v>-1.1370387665397071E-4</v>
       </c>
       <c r="J20">
-        <v>-2.4214016544321247E-5</v>
+        <v>3.4149069492930102E-5</v>
       </c>
       <c r="K20">
-        <v>-2.0806817057532757E-4</v>
+        <v>-2.7086077731052881E-5</v>
       </c>
       <c r="L20">
-        <v>-6.8594786761098708E-5</v>
+        <v>-9.7199705675142089E-5</v>
       </c>
       <c r="M20">
-        <v>-6.3333323770845581E-5</v>
+        <v>2.9747401395108849E-4</v>
       </c>
       <c r="N20">
-        <v>2.6747852623793624E-3</v>
+        <v>9.8729803759006925E-5</v>
       </c>
       <c r="O20">
-        <v>2.5797366183455774E-3</v>
+        <v>2.960361236013973E-3</v>
       </c>
       <c r="P20">
-        <v>2.6738850493223496E-3</v>
+        <v>2.8361268935977258E-3</v>
       </c>
       <c r="Q20">
-        <v>2.7055990208078506E-3</v>
+        <v>2.8879344376244007E-3</v>
       </c>
       <c r="R20">
-        <v>2.5345531219736453E-3</v>
+        <v>2.9336285746020319E-3</v>
       </c>
       <c r="S20">
-        <v>2.6620074476919045E-3</v>
+        <v>2.7913310608169021E-3</v>
       </c>
       <c r="T20">
-        <v>3.0206221918056761E-3</v>
+        <v>2.8636425830490457E-3</v>
       </c>
       <c r="U20">
-        <v>5.7016314616764466E-3</v>
+        <v>5.2280089871464454E-3</v>
       </c>
       <c r="V20">
-        <v>2.7941038617208275E-3</v>
+        <v>3.0170099491313861E-3</v>
       </c>
       <c r="W20">
-        <v>2.7958562353896151E-3</v>
+        <v>3.0717484640609004E-3</v>
       </c>
       <c r="X20">
-        <v>2.7403949705875762E-3</v>
+        <v>3.0504256414284228E-3</v>
       </c>
       <c r="Y20">
-        <v>2.3553104853564196E-5</v>
+        <v>3.0431964473658854E-3</v>
       </c>
       <c r="Z20">
-        <v>-1.3742312520852203E-4</v>
+        <v>4.138284363145898E-5</v>
       </c>
       <c r="AA20">
-        <v>9.717996561565685E-5</v>
+        <v>-3.1448617303492916E-4</v>
       </c>
       <c r="AB20">
-        <v>9.555719696956145E-4</v>
+        <v>-2.5650292090165911E-4</v>
       </c>
       <c r="AC20">
-        <v>4.0893680846745368E-3</v>
+        <v>9.9765743259814339E-4</v>
       </c>
       <c r="AD20">
-        <v>8.5471673258112266E-4</v>
+        <v>6.2194003388472557E-3</v>
       </c>
       <c r="AE20">
-        <v>-7.0647692506423023E-3</v>
-      </c>
-    </row>
-    <row r="21" spans="1:31" x14ac:dyDescent="0.2">
+        <v>6.9886718084717701E-4</v>
+      </c>
+      <c r="AF20">
+        <v>-6.8252074618705685E-3</v>
+      </c>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21">
-        <v>-7.3833158871357734E-3</v>
+        <v>0.18960538583431136</v>
       </c>
       <c r="C21">
-        <v>-1.3943944411035939E-5</v>
+        <v>3.8308562154541274E-5</v>
       </c>
       <c r="D21">
-        <v>2.5226066487243882E-4</v>
+        <v>2.8705440860610242E-4</v>
       </c>
       <c r="E21">
-        <v>-5.0269393684843002E-6</v>
+        <v>-5.4622681237404913E-6</v>
       </c>
       <c r="F21">
-        <v>2.3154841327471673E-4</v>
+        <v>-3.4902018928462055E-5</v>
       </c>
       <c r="G21">
-        <v>-2.884905730418198E-4</v>
+        <v>1.0697945405575843E-4</v>
       </c>
       <c r="H21">
-        <v>-2.0852317552113968E-5</v>
+        <v>7.2196678534333604E-5</v>
       </c>
       <c r="I21">
-        <v>-1.7894712276465201E-5</v>
+        <v>2.7986649151010695E-5</v>
       </c>
       <c r="J21">
-        <v>-2.6647471732395202E-5</v>
+        <v>-9.492733634786603E-5</v>
       </c>
       <c r="K21">
-        <v>-1.240682438938659E-4</v>
+        <v>2.4730471848987551E-5</v>
       </c>
       <c r="L21">
-        <v>1.6749596512831877E-4</v>
+        <v>-1.5281774963111258E-4</v>
       </c>
       <c r="M21">
-        <v>1.2562164006015898E-4</v>
+        <v>-2.7753711846173739E-5</v>
       </c>
       <c r="N21">
-        <v>2.6740025790139756E-3</v>
+        <v>-2.2595430780857962E-5</v>
       </c>
       <c r="O21">
-        <v>2.6486969446011567E-3</v>
+        <v>2.690620687459002E-3</v>
       </c>
       <c r="P21">
-        <v>2.7020964865515735E-3</v>
+        <v>2.593167226664353E-3</v>
       </c>
       <c r="Q21">
-        <v>2.7138451408494722E-3</v>
+        <v>2.673763104855714E-3</v>
       </c>
       <c r="R21">
-        <v>2.5638419159647913E-3</v>
+        <v>2.7028694385049855E-3</v>
       </c>
       <c r="S21">
-        <v>2.6777513320349637E-3</v>
+        <v>2.5418104851318243E-3</v>
       </c>
       <c r="T21">
-        <v>3.0722276804035793E-3</v>
+        <v>2.6770660248227503E-3</v>
       </c>
       <c r="U21">
-        <v>2.7941038617208275E-3</v>
+        <v>3.0170099491313861E-3</v>
       </c>
       <c r="V21">
-        <v>6.4659029985279538E-3</v>
+        <v>5.6856952345552885E-3</v>
       </c>
       <c r="W21">
-        <v>2.7690120172499423E-3</v>
+        <v>2.7995047746552587E-3</v>
       </c>
       <c r="X21">
-        <v>2.816688492757821E-3</v>
+        <v>2.8054921538831858E-3</v>
       </c>
       <c r="Y21">
-        <v>3.6464141922585766E-5</v>
+        <v>2.7526232199681384E-3</v>
       </c>
       <c r="Z21">
-        <v>-2.3524995121688698E-4</v>
+        <v>2.2308029525381615E-5</v>
       </c>
       <c r="AA21">
-        <v>-6.0841997218795667E-5</v>
+        <v>-1.4936512243180795E-4</v>
       </c>
       <c r="AB21">
-        <v>9.7826395803863632E-4</v>
+        <v>9.0923009748039693E-5</v>
       </c>
       <c r="AC21">
-        <v>4.2565169307163019E-3</v>
+        <v>9.5626338923415831E-4</v>
       </c>
       <c r="AD21">
-        <v>7.8507040841053436E-4</v>
+        <v>4.0539456518666056E-3</v>
       </c>
       <c r="AE21">
-        <v>-6.6340885237400078E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:31" x14ac:dyDescent="0.2">
+        <v>8.540285919441603E-4</v>
+      </c>
+      <c r="AF21">
+        <v>-6.8430847914009076E-3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22">
-        <v>0.14095634302440696</v>
+        <v>-1.8134419711079774E-2</v>
       </c>
       <c r="C22">
-        <v>-1.6967168748297916E-5</v>
+        <v>-1.2603087492062997E-5</v>
       </c>
       <c r="D22">
-        <v>3.7534963407277397E-4</v>
+        <v>2.4318932414474424E-4</v>
       </c>
       <c r="E22">
-        <v>-6.8486974691471917E-6</v>
+        <v>-4.847160544957353E-6</v>
       </c>
       <c r="F22">
-        <v>4.3687226972893053E-4</v>
+        <v>4.2043914335640692E-5</v>
       </c>
       <c r="G22">
-        <v>1.9333730432413352E-4</v>
+        <v>2.2606405081549487E-4</v>
       </c>
       <c r="H22">
-        <v>-3.1069069678916182E-4</v>
+        <v>-2.6748184923592504E-4</v>
       </c>
       <c r="I22">
-        <v>-4.5940120675852395E-4</v>
+        <v>2.1395355977187947E-5</v>
       </c>
       <c r="J22">
-        <v>-4.3016027738813982E-4</v>
+        <v>6.0030106901738851E-5</v>
       </c>
       <c r="K22">
-        <v>-7.0470382499248361E-4</v>
+        <v>1.8731504269444332E-4</v>
       </c>
       <c r="L22">
-        <v>-4.6364332681867506E-4</v>
+        <v>1.1558556674471439E-5</v>
       </c>
       <c r="M22">
-        <v>-5.0388385255079927E-4</v>
+        <v>2.9856021505670624E-4</v>
       </c>
       <c r="N22">
-        <v>2.6445667520989084E-3</v>
+        <v>2.5770867538976066E-4</v>
       </c>
       <c r="O22">
-        <v>2.5915649745999556E-3</v>
+        <v>2.6931009418376438E-3</v>
       </c>
       <c r="P22">
-        <v>2.6748824615748386E-3</v>
+        <v>2.6686997482110726E-3</v>
       </c>
       <c r="Q22">
-        <v>2.6702630930883968E-3</v>
+        <v>2.7009555285118763E-3</v>
       </c>
       <c r="R22">
-        <v>2.5143091038747965E-3</v>
+        <v>2.7133569256387463E-3</v>
       </c>
       <c r="S22">
-        <v>2.6410710079755807E-3</v>
+        <v>2.5735567501558631E-3</v>
       </c>
       <c r="T22">
-        <v>3.0476529906321159E-3</v>
+        <v>2.6948403172487347E-3</v>
       </c>
       <c r="U22">
-        <v>2.7958562353896151E-3</v>
+        <v>3.0717484640609004E-3</v>
       </c>
       <c r="V22">
-        <v>2.7690120172499423E-3</v>
+        <v>2.7995047746552587E-3</v>
       </c>
       <c r="W22">
-        <v>5.7791879799845109E-3</v>
+        <v>6.4798650097036272E-3</v>
       </c>
       <c r="X22">
-        <v>2.7226402037455228E-3</v>
+        <v>2.7987200125283605E-3</v>
       </c>
       <c r="Y22">
-        <v>4.3122025931064247E-5</v>
+        <v>2.8329324296102899E-3</v>
       </c>
       <c r="Z22">
-        <v>-2.2849696480605822E-4</v>
+        <v>3.67840972096057E-5</v>
       </c>
       <c r="AA22">
-        <v>-1.7837985771582251E-4</v>
+        <v>-2.5598047167513493E-4</v>
       </c>
       <c r="AB22">
-        <v>9.1564238885748998E-4</v>
+        <v>-6.7341290994294583E-5</v>
       </c>
       <c r="AC22">
-        <v>4.0644222806185785E-3</v>
+        <v>9.9398358505750368E-4</v>
       </c>
       <c r="AD22">
-        <v>6.1026301828242147E-4</v>
+        <v>4.2351790780349313E-3</v>
       </c>
       <c r="AE22">
-        <v>-8.1672672765457661E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:31" x14ac:dyDescent="0.2">
+        <v>7.9533769129889759E-4</v>
+      </c>
+      <c r="AF22">
+        <v>-6.6672566230439817E-3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23">
-        <v>-0.12087443728595966</v>
+        <v>0.13026905603376457</v>
       </c>
       <c r="C23">
-        <v>6.1545927356103686E-5</v>
+        <v>-1.2415530464250412E-5</v>
       </c>
       <c r="D23">
-        <v>9.656539712628049E-5</v>
+        <v>3.7117580639640371E-4</v>
       </c>
       <c r="E23">
-        <v>-2.0553374108836498E-6</v>
+        <v>-6.8188063961987933E-6</v>
       </c>
       <c r="F23">
-        <v>2.5135560197017768E-4</v>
+        <v>4.004151662559516E-4</v>
       </c>
       <c r="G23">
-        <v>-1.9338845232749172E-4</v>
+        <v>4.4390586994820606E-4</v>
       </c>
       <c r="H23">
-        <v>-9.0364403546973511E-5</v>
+        <v>2.0448099579843128E-4</v>
       </c>
       <c r="I23">
-        <v>-8.3370132209597582E-5</v>
+        <v>-4.0747779805873211E-4</v>
       </c>
       <c r="J23">
-        <v>-5.9587237419699186E-5</v>
+        <v>-4.4014557325362216E-4</v>
       </c>
       <c r="K23">
-        <v>-1.0864930364699963E-4</v>
+        <v>-4.0606137750241018E-4</v>
       </c>
       <c r="L23">
-        <v>9.9729058016456446E-5</v>
+        <v>-6.6425046641433848E-4</v>
       </c>
       <c r="M23">
-        <v>8.2113781840541938E-5</v>
+        <v>-4.2062670227277136E-4</v>
       </c>
       <c r="N23">
-        <v>2.6755692159541409E-3</v>
+        <v>-4.5250298042239689E-4</v>
       </c>
       <c r="O23">
-        <v>2.6051491663760242E-3</v>
+        <v>2.67150611730109E-3</v>
       </c>
       <c r="P23">
-        <v>2.6207323095914581E-3</v>
+        <v>2.6117987398632673E-3</v>
       </c>
       <c r="Q23">
-        <v>2.6623625659362819E-3</v>
+        <v>2.6875183056754483E-3</v>
       </c>
       <c r="R23">
-        <v>2.5240433015959779E-3</v>
+        <v>2.6828811327583913E-3</v>
       </c>
       <c r="S23">
-        <v>2.6259649815891812E-3</v>
+        <v>2.5372961990088537E-3</v>
       </c>
       <c r="T23">
-        <v>3.0407024435006717E-3</v>
+        <v>2.6601865048624831E-3</v>
       </c>
       <c r="U23">
-        <v>2.7403949705875762E-3</v>
+        <v>3.0504256414284228E-3</v>
       </c>
       <c r="V23">
-        <v>2.816688492757821E-3</v>
+        <v>2.8054921538831858E-3</v>
       </c>
       <c r="W23">
-        <v>2.7226402037455228E-3</v>
+        <v>2.7987200125283605E-3</v>
       </c>
       <c r="X23">
-        <v>5.4226928192797836E-3</v>
+        <v>5.7493064685174497E-3</v>
       </c>
       <c r="Y23">
-        <v>1.7722454424726354E-5</v>
+        <v>2.7410527348470238E-3</v>
       </c>
       <c r="Z23">
-        <v>-2.333545116330749E-4</v>
+        <v>4.2078122985080696E-5</v>
       </c>
       <c r="AA23">
-        <v>-1.526032916186715E-4</v>
+        <v>-2.4129424255733928E-4</v>
       </c>
       <c r="AB23">
-        <v>1.053836214946053E-3</v>
+        <v>-1.7546927837554254E-4</v>
       </c>
       <c r="AC23">
-        <v>4.2317219962565494E-3</v>
+        <v>9.2668157156582196E-4</v>
       </c>
       <c r="AD23">
-        <v>7.3542981255237869E-4</v>
+        <v>4.056550328183816E-3</v>
       </c>
       <c r="AE23">
-        <v>-4.2998183190180173E-3</v>
-      </c>
-    </row>
-    <row r="24" spans="1:31" x14ac:dyDescent="0.2">
+        <v>6.1811414330239589E-4</v>
+      </c>
+      <c r="AF23">
+        <v>-8.1235657763158893E-3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>35</v>
       </c>
       <c r="B24">
-        <v>-1.5778697301363526E-2</v>
+        <v>-0.13172778095661891</v>
       </c>
       <c r="C24">
-        <v>2.5204466419506002E-6</v>
+        <v>6.2049055527128172E-5</v>
       </c>
       <c r="D24">
-        <v>5.8623260199830701E-6</v>
+        <v>8.6311337591227048E-5</v>
       </c>
       <c r="E24">
-        <v>-1.1041643782008719E-7</v>
+        <v>-1.9027586668400809E-6</v>
       </c>
       <c r="F24">
-        <v>2.7024954846997318E-5</v>
+        <v>1.583288399686477E-5</v>
       </c>
       <c r="G24">
-        <v>-2.2035683306357461E-6</v>
+        <v>2.6971178553977055E-4</v>
       </c>
       <c r="H24">
-        <v>-9.3197335251311896E-6</v>
+        <v>-1.4141087857681158E-4</v>
       </c>
       <c r="I24">
-        <v>-9.1006088659880682E-6</v>
+        <v>-3.9056292400923339E-5</v>
       </c>
       <c r="J24">
-        <v>5.2332234867601265E-6</v>
+        <v>-6.6296903178857634E-5</v>
       </c>
       <c r="K24">
-        <v>3.2911397601400856E-6</v>
+        <v>-1.800926872857567E-5</v>
       </c>
       <c r="L24">
-        <v>2.1660693554577382E-5</v>
+        <v>-6.404096945532723E-5</v>
       </c>
       <c r="M24">
-        <v>-1.3649194648799701E-5</v>
+        <v>1.4844073235358891E-4</v>
       </c>
       <c r="N24">
-        <v>5.3050356581477035E-5</v>
+        <v>1.3714088259977886E-4</v>
       </c>
       <c r="O24">
-        <v>6.3848391747433676E-5</v>
+        <v>2.7021111428959009E-3</v>
       </c>
       <c r="P24">
-        <v>2.3063138114478112E-5</v>
+        <v>2.6257306852547737E-3</v>
       </c>
       <c r="Q24">
-        <v>1.55021775945218E-5</v>
+        <v>2.6317172248474779E-3</v>
       </c>
       <c r="R24">
-        <v>4.8088342975039297E-5</v>
+        <v>2.6678274312721189E-3</v>
       </c>
       <c r="S24">
-        <v>1.3884871210150223E-5</v>
+        <v>2.5419697493696642E-3</v>
       </c>
       <c r="T24">
-        <v>4.1965120184968676E-5</v>
+        <v>2.6431170489514795E-3</v>
       </c>
       <c r="U24">
-        <v>2.3553104853564196E-5</v>
+        <v>3.0431964473658854E-3</v>
       </c>
       <c r="V24">
-        <v>3.6464141922585766E-5</v>
+        <v>2.7526232199681384E-3</v>
       </c>
       <c r="W24">
-        <v>4.3122025931064247E-5</v>
+        <v>2.8329324296102899E-3</v>
       </c>
       <c r="X24">
-        <v>1.7722454424726354E-5</v>
+        <v>2.7410527348470238E-3</v>
       </c>
       <c r="Y24">
-        <v>2.4409798752061451E-5</v>
+        <v>5.4200688670805672E-3</v>
       </c>
       <c r="Z24">
-        <v>-1.0720998795343764E-4</v>
+        <v>1.6997596660196524E-5</v>
       </c>
       <c r="AA24">
-        <v>-1.2828307150981861E-4</v>
+        <v>-2.4863666861131301E-4</v>
       </c>
       <c r="AB24">
-        <v>-2.2020427517849554E-5</v>
+        <v>-1.4475303038542948E-4</v>
       </c>
       <c r="AC24">
-        <v>1.6510996314368431E-4</v>
+        <v>1.0714562091791425E-3</v>
       </c>
       <c r="AD24">
-        <v>-2.9597106632200053E-5</v>
+        <v>4.2163983927284605E-3</v>
       </c>
       <c r="AE24">
-        <v>-5.109483342639182E-4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:31" x14ac:dyDescent="0.2">
+        <v>7.452836621582215E-4</v>
+      </c>
+      <c r="AF24">
+        <v>-4.1967151553959411E-3</v>
+      </c>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>36</v>
       </c>
       <c r="B25">
-        <v>0.11143107296221159</v>
+        <v>-1.5229470223584403E-2</v>
       </c>
       <c r="C25">
-        <v>3.6095380948773644E-5</v>
+        <v>1.5707991150727183E-6</v>
       </c>
       <c r="D25">
-        <v>-3.0895817672078234E-6</v>
+        <v>6.0185117747523463E-6</v>
       </c>
       <c r="E25">
-        <v>3.366219190139378E-8</v>
+        <v>-1.1147281012490682E-7</v>
       </c>
       <c r="F25">
-        <v>-1.2729083300184874E-4</v>
+        <v>4.7225383861884251E-5</v>
       </c>
       <c r="G25">
-        <v>1.0327414611596319E-4</v>
+        <v>2.8249078510313858E-5</v>
       </c>
       <c r="H25">
-        <v>1.2038135546313763E-4</v>
+        <v>2.7587062873393265E-6</v>
       </c>
       <c r="I25">
-        <v>5.0639640062871249E-5</v>
+        <v>-2.6488357675537918E-5</v>
       </c>
       <c r="J25">
-        <v>-3.9498739419105162E-5</v>
+        <v>-1.0942222301353111E-5</v>
       </c>
       <c r="K25">
-        <v>9.5158029803746547E-5</v>
+        <v>3.464963209568535E-6</v>
       </c>
       <c r="L25">
-        <v>-9.601522902623455E-6</v>
+        <v>1.5471141574857281E-6</v>
       </c>
       <c r="M25">
-        <v>1.3307300721414025E-6</v>
+        <v>1.9843368338410845E-5</v>
       </c>
       <c r="N25">
-        <v>-3.3061981479276016E-4</v>
+        <v>-1.3915280044423067E-5</v>
       </c>
       <c r="O25">
-        <v>-3.9045973402864116E-4</v>
+        <v>5.166515283836447E-5</v>
       </c>
       <c r="P25">
-        <v>-2.3912498025086551E-4</v>
+        <v>6.2053314703571861E-5</v>
       </c>
       <c r="Q25">
-        <v>-3.335063633469087E-5</v>
+        <v>2.2938560151833246E-5</v>
       </c>
       <c r="R25">
-        <v>-3.5511256265554421E-4</v>
+        <v>1.6382463128005733E-5</v>
       </c>
       <c r="S25">
-        <v>-3.6539529091222139E-5</v>
+        <v>4.6911315654731803E-5</v>
       </c>
       <c r="T25">
-        <v>-2.9990807887933524E-4</v>
+        <v>1.3755972232894675E-5</v>
       </c>
       <c r="U25">
-        <v>-1.3742312520852203E-4</v>
+        <v>4.138284363145898E-5</v>
       </c>
       <c r="V25">
-        <v>-2.3524995121688698E-4</v>
+        <v>2.2308029525381615E-5</v>
       </c>
       <c r="W25">
-        <v>-2.2849696480605822E-4</v>
+        <v>3.67840972096057E-5</v>
       </c>
       <c r="X25">
-        <v>-2.333545116330749E-4</v>
+        <v>4.2078122985080696E-5</v>
       </c>
       <c r="Y25">
-        <v>-1.0720998795343764E-4</v>
+        <v>1.6997596660196524E-5</v>
       </c>
       <c r="Z25">
-        <v>4.0766704739928321E-3</v>
+        <v>2.4226366935096994E-5</v>
       </c>
       <c r="AA25">
-        <v>7.9530304868071292E-4</v>
+        <v>-1.0604655990724388E-4</v>
       </c>
       <c r="AB25">
-        <v>1.0339785780323456E-5</v>
+        <v>-1.2701964426740123E-4</v>
       </c>
       <c r="AC25">
-        <v>-9.17069993231757E-4</v>
+        <v>-2.2404405524717008E-5</v>
       </c>
       <c r="AD25">
-        <v>7.9906720154998339E-4</v>
+        <v>1.6178544856595257E-4</v>
       </c>
       <c r="AE25">
-        <v>1.7216177399785645E-3</v>
-      </c>
-    </row>
-    <row r="26" spans="1:31" x14ac:dyDescent="0.2">
+        <v>-2.9776083124929033E-5</v>
+      </c>
+      <c r="AF25">
+        <v>-5.1025476033362508E-4</v>
+      </c>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>37</v>
       </c>
       <c r="B26">
-        <v>8.3105699222738139E-2</v>
+        <v>0.11251512566003151</v>
       </c>
       <c r="C26">
-        <v>1.8502171495594645E-5</v>
+        <v>4.4743738907690041E-5</v>
       </c>
       <c r="D26">
-        <v>-5.543069881322406E-5</v>
+        <v>7.7573150486439117E-6</v>
       </c>
       <c r="E26">
-        <v>8.0468889660022073E-7</v>
+        <v>-1.6341386261677094E-7</v>
       </c>
       <c r="F26">
-        <v>-7.9329549132553284E-5</v>
+        <v>-5.6160774035137666E-5</v>
       </c>
       <c r="G26">
-        <v>4.3094902814287065E-5</v>
+        <v>-1.5884086586774482E-4</v>
       </c>
       <c r="H26">
-        <v>-7.135677064754617E-5</v>
+        <v>6.7696276270442392E-5</v>
       </c>
       <c r="I26">
-        <v>-5.5105413464862996E-5</v>
+        <v>1.1042014054976686E-4</v>
       </c>
       <c r="J26">
-        <v>1.3407181033159169E-6</v>
+        <v>5.3821302802515875E-5</v>
       </c>
       <c r="K26">
-        <v>6.7721159702267331E-5</v>
+        <v>-4.3502193654356146E-5</v>
       </c>
       <c r="L26">
-        <v>-1.9869326021490453E-5</v>
+        <v>9.4938867879374274E-5</v>
       </c>
       <c r="M26">
-        <v>9.6405769183027963E-5</v>
+        <v>-1.421721672999253E-5</v>
       </c>
       <c r="N26">
-        <v>-3.5368318013078565E-4</v>
+        <v>-2.4702454943775396E-5</v>
       </c>
       <c r="O26">
-        <v>-1.939464363324544E-4</v>
+        <v>-3.5445431679852196E-4</v>
       </c>
       <c r="P26">
-        <v>1.9723470932403106E-4</v>
+        <v>-4.013320078186444E-4</v>
       </c>
       <c r="Q26">
-        <v>-7.8010941309687254E-5</v>
+        <v>-2.454278741564549E-4</v>
       </c>
       <c r="R26">
-        <v>-2.7227025082740092E-4</v>
+        <v>-6.9571271212558503E-5</v>
       </c>
       <c r="S26">
-        <v>-7.8220337956249838E-6</v>
+        <v>-3.7060446292431072E-4</v>
       </c>
       <c r="T26">
-        <v>-2.5550372242020549E-4</v>
+        <v>-6.1975807112222422E-5</v>
       </c>
       <c r="U26">
-        <v>9.717996561565685E-5</v>
+        <v>-3.1448617303492916E-4</v>
       </c>
       <c r="V26">
-        <v>-6.0841997218795667E-5</v>
+        <v>-1.4936512243180795E-4</v>
       </c>
       <c r="W26">
-        <v>-1.7837985771582251E-4</v>
+        <v>-2.5598047167513493E-4</v>
       </c>
       <c r="X26">
-        <v>-1.526032916186715E-4</v>
+        <v>-2.4129424255733928E-4</v>
       </c>
       <c r="Y26">
-        <v>-1.2828307150981861E-4</v>
+        <v>-2.4863666861131301E-4</v>
       </c>
       <c r="Z26">
-        <v>7.9530304868071292E-4</v>
+        <v>-1.0604655990724388E-4</v>
       </c>
       <c r="AA26">
-        <v>4.4710730767484599E-3</v>
+        <v>4.0534614110994144E-3</v>
       </c>
       <c r="AB26">
-        <v>4.3907649154365826E-5</v>
+        <v>7.906437760467857E-4</v>
       </c>
       <c r="AC26">
-        <v>-9.1086257598375128E-4</v>
+        <v>-5.8412094472513453E-6</v>
       </c>
       <c r="AD26">
-        <v>5.7107298628172545E-5</v>
+        <v>-9.096200513727139E-4</v>
       </c>
       <c r="AE26">
-        <v>2.782632183163524E-3</v>
-      </c>
-    </row>
-    <row r="27" spans="1:31" x14ac:dyDescent="0.2">
+        <v>8.1059336180796962E-4</v>
+      </c>
+      <c r="AF26">
+        <v>1.5987703405011271E-3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27">
-        <v>-0.48479716690381414</v>
+        <v>8.4215867358136673E-2</v>
       </c>
       <c r="C27">
-        <v>-1.0091452927714643E-5</v>
+        <v>1.9346771455097677E-5</v>
       </c>
       <c r="D27">
-        <v>-3.6916698753138369E-5</v>
+        <v>-4.37111033549549E-5</v>
       </c>
       <c r="E27">
-        <v>5.2443061451713129E-7</v>
+        <v>5.9964560833659268E-7</v>
       </c>
       <c r="F27">
-        <v>2.8115579145155311E-4</v>
+        <v>-1.5091809039732948E-5</v>
       </c>
       <c r="G27">
-        <v>4.4655413250984407E-4</v>
+        <v>-4.8603812532399852E-5</v>
       </c>
       <c r="H27">
-        <v>7.6498904887661694E-5</v>
+        <v>-1.6483260493021059E-5</v>
       </c>
       <c r="I27">
-        <v>9.0812592074561264E-5</v>
+        <v>-6.9332360169555387E-5</v>
       </c>
       <c r="J27">
-        <v>1.8265797415208422E-4</v>
+        <v>-4.4105683785933378E-5</v>
       </c>
       <c r="K27">
-        <v>2.9690841027047192E-4</v>
+        <v>5.5214484269356973E-6</v>
       </c>
       <c r="L27">
-        <v>2.8973525477011771E-4</v>
+        <v>6.7860537026259119E-5</v>
       </c>
       <c r="M27">
-        <v>8.7885074478018157E-5</v>
+        <v>-1.9797213126812043E-5</v>
       </c>
       <c r="N27">
-        <v>8.640014404297571E-4</v>
+        <v>9.1966178694389005E-5</v>
       </c>
       <c r="O27">
-        <v>6.0224779842726298E-4</v>
+        <v>-3.5236329918160328E-4</v>
       </c>
       <c r="P27">
-        <v>7.7764997963329586E-4</v>
+        <v>-1.9171875709240831E-4</v>
       </c>
       <c r="Q27">
-        <v>7.8357147469100877E-4</v>
+        <v>1.9687079064206801E-4</v>
       </c>
       <c r="R27">
-        <v>2.2049382169779823E-4</v>
+        <v>-8.4003396433393032E-5</v>
       </c>
       <c r="S27">
-        <v>8.320548858839783E-4</v>
+        <v>-2.7033595762525993E-4</v>
       </c>
       <c r="T27">
-        <v>9.9158737611014275E-4</v>
+        <v>-1.9305222792210955E-6</v>
       </c>
       <c r="U27">
-        <v>9.555719696956145E-4</v>
+        <v>-2.5650292090165911E-4</v>
       </c>
       <c r="V27">
-        <v>9.7826395803863632E-4</v>
+        <v>9.0923009748039693E-5</v>
       </c>
       <c r="W27">
-        <v>9.1564238885748998E-4</v>
+        <v>-6.7341290994294583E-5</v>
       </c>
       <c r="X27">
-        <v>1.053836214946053E-3</v>
+        <v>-1.7546927837554254E-4</v>
       </c>
       <c r="Y27">
-        <v>-2.2020427517849554E-5</v>
+        <v>-1.4475303038542948E-4</v>
       </c>
       <c r="Z27">
-        <v>1.0339785780323456E-5</v>
+        <v>-1.2701964426740123E-4</v>
       </c>
       <c r="AA27">
-        <v>4.3907649154365826E-5</v>
+        <v>7.906437760467857E-4</v>
       </c>
       <c r="AB27">
-        <v>3.7101545641845097E-3</v>
+        <v>4.4547470729170893E-3</v>
       </c>
       <c r="AC27">
-        <v>1.5977275058258716E-3</v>
+        <v>4.3364124045632978E-5</v>
       </c>
       <c r="AD27">
-        <v>5.7681661978063866E-4</v>
+        <v>-8.9523759819373457E-4</v>
       </c>
       <c r="AE27">
-        <v>-5.2207757882608181E-4</v>
-      </c>
-    </row>
-    <row r="28" spans="1:31" x14ac:dyDescent="0.2">
+        <v>6.1799608931991035E-5</v>
+      </c>
+      <c r="AF27">
+        <v>2.5819594381777671E-3</v>
+      </c>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28">
-        <v>-0.19046534736933973</v>
+        <v>-0.47689607236742615</v>
       </c>
       <c r="C28">
-        <v>-4.8169548043188143E-4</v>
+        <v>-8.5206271170738937E-6</v>
       </c>
       <c r="D28">
-        <v>3.2376399281118691E-4</v>
+        <v>-5.7483922405465911E-5</v>
       </c>
       <c r="E28">
-        <v>-7.0302506220349444E-6</v>
+        <v>8.6386851775463133E-7</v>
       </c>
       <c r="F28">
-        <v>9.3166464608707145E-4</v>
+        <v>1.5780785762827161E-5</v>
       </c>
       <c r="G28">
-        <v>6.1687035793088095E-4</v>
+        <v>3.1947794391678315E-4</v>
       </c>
       <c r="H28">
-        <v>-2.4870269898535566E-4</v>
+        <v>4.8536917546892675E-4</v>
       </c>
       <c r="I28">
-        <v>-1.8000166222586784E-4</v>
+        <v>1.609415858674669E-4</v>
       </c>
       <c r="J28">
-        <v>1.9311301516016129E-4</v>
+        <v>7.777302847041586E-5</v>
       </c>
       <c r="K28">
-        <v>3.2829573453441695E-5</v>
+        <v>1.3798068443338866E-4</v>
       </c>
       <c r="L28">
-        <v>1.0710341007257808E-3</v>
+        <v>2.8999327648147801E-4</v>
       </c>
       <c r="M28">
-        <v>5.0069336645541893E-4</v>
+        <v>3.0147059722249658E-4</v>
       </c>
       <c r="N28">
-        <v>4.0798763949485683E-3</v>
+        <v>1.1749946571311745E-4</v>
       </c>
       <c r="O28">
-        <v>3.7283013199375342E-3</v>
+        <v>8.836250317549463E-4</v>
       </c>
       <c r="P28">
-        <v>3.7910794330858542E-3</v>
+        <v>6.2520699498085975E-4</v>
       </c>
       <c r="Q28">
-        <v>3.8621427825652646E-3</v>
+        <v>7.9523786611517303E-4</v>
       </c>
       <c r="R28">
-        <v>3.7102097712881105E-3</v>
+        <v>7.9651402997497314E-4</v>
       </c>
       <c r="S28">
-        <v>3.4705819706743876E-3</v>
+        <v>2.2938060598892002E-4</v>
       </c>
       <c r="T28">
-        <v>6.2900161260970641E-3</v>
+        <v>8.5193195049797937E-4</v>
       </c>
       <c r="U28">
-        <v>4.0893680846745368E-3</v>
+        <v>9.9765743259814339E-4</v>
       </c>
       <c r="V28">
-        <v>4.2565169307163019E-3</v>
+        <v>9.5626338923415831E-4</v>
       </c>
       <c r="W28">
-        <v>4.0644222806185785E-3</v>
+        <v>9.9398358505750368E-4</v>
       </c>
       <c r="X28">
-        <v>4.2317219962565494E-3</v>
+        <v>9.2668157156582196E-4</v>
       </c>
       <c r="Y28">
-        <v>1.6510996314368431E-4</v>
+        <v>1.0714562091791425E-3</v>
       </c>
       <c r="Z28">
-        <v>-9.17069993231757E-4</v>
+        <v>-2.2404405524717008E-5</v>
       </c>
       <c r="AA28">
-        <v>-9.1086257598375128E-4</v>
+        <v>-5.8412094472513453E-6</v>
       </c>
       <c r="AB28">
-        <v>1.5977275058258716E-3</v>
+        <v>4.3364124045632978E-5</v>
       </c>
       <c r="AC28">
-        <v>2.2554675514069828E-2</v>
+        <v>3.7327240946998549E-3</v>
       </c>
       <c r="AD28">
-        <v>1.5332234325299298E-3</v>
+        <v>1.6012931728277824E-3</v>
       </c>
       <c r="AE28">
-        <v>-1.1206354892388748E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:31" x14ac:dyDescent="0.2">
+        <v>5.766615819541059E-4</v>
+      </c>
+      <c r="AF28">
+        <v>-2.6107629693339482E-4</v>
+      </c>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>40</v>
       </c>
       <c r="B29">
-        <v>-0.2066391002274455</v>
+        <v>-0.19765628023852819</v>
       </c>
       <c r="C29">
-        <v>-2.2878681587369142E-5</v>
+        <v>-4.8491751454143037E-4</v>
       </c>
       <c r="D29">
-        <v>3.7598502356093371E-5</v>
+        <v>3.0594389090943946E-4</v>
       </c>
       <c r="E29">
-        <v>-1.1430393126544458E-6</v>
+        <v>-6.7249685989256738E-6</v>
       </c>
       <c r="F29">
-        <v>-1.0282855291970054E-4</v>
+        <v>9.6731761536263811E-4</v>
       </c>
       <c r="G29">
-        <v>-1.6695709595049768E-5</v>
+        <v>1.0561272165055353E-3</v>
       </c>
       <c r="H29">
-        <v>-9.3727303104299627E-5</v>
+        <v>7.7981861282318612E-4</v>
       </c>
       <c r="I29">
-        <v>1.8986922959096978E-5</v>
+        <v>-5.0331829423211133E-4</v>
       </c>
       <c r="J29">
-        <v>2.2240361721406938E-4</v>
+        <v>-1.9751254821681347E-4</v>
       </c>
       <c r="K29">
-        <v>1.9075533992781281E-4</v>
+        <v>1.6042587488563406E-4</v>
       </c>
       <c r="L29">
-        <v>3.7638181847277877E-4</v>
+        <v>4.1427333061940137E-5</v>
       </c>
       <c r="M29">
-        <v>1.7276354388240416E-4</v>
+        <v>1.082859674476654E-3</v>
       </c>
       <c r="N29">
-        <v>6.8765637421166212E-4</v>
+        <v>5.7524318997224499E-4</v>
       </c>
       <c r="O29">
-        <v>4.1663830078365383E-4</v>
+        <v>4.0826869466348507E-3</v>
       </c>
       <c r="P29">
-        <v>6.5801033590116246E-4</v>
+        <v>3.7233483070655462E-3</v>
       </c>
       <c r="Q29">
-        <v>5.6077753856394858E-4</v>
+        <v>3.7674862622241877E-3</v>
       </c>
       <c r="R29">
-        <v>2.1534853343267108E-4</v>
+        <v>3.8274021701565058E-3</v>
       </c>
       <c r="S29">
-        <v>4.5439573712119174E-4</v>
+        <v>3.6968217157761557E-3</v>
       </c>
       <c r="T29">
-        <v>6.8588572307904945E-4</v>
+        <v>3.4698126787947644E-3</v>
       </c>
       <c r="U29">
-        <v>8.5471673258112266E-4</v>
+        <v>6.2194003388472557E-3</v>
       </c>
       <c r="V29">
-        <v>7.8507040841053436E-4</v>
+        <v>4.0539456518666056E-3</v>
       </c>
       <c r="W29">
-        <v>6.1026301828242147E-4</v>
+        <v>4.2351790780349313E-3</v>
       </c>
       <c r="X29">
-        <v>7.3542981255237869E-4</v>
+        <v>4.056550328183816E-3</v>
       </c>
       <c r="Y29">
-        <v>-2.9597106632200053E-5</v>
+        <v>4.2163983927284605E-3</v>
       </c>
       <c r="Z29">
-        <v>7.9906720154998339E-4</v>
+        <v>1.6178544856595257E-4</v>
       </c>
       <c r="AA29">
-        <v>5.7107298628172545E-5</v>
+        <v>-9.096200513727139E-4</v>
       </c>
       <c r="AB29">
-        <v>5.7681661978063866E-4</v>
+        <v>-8.9523759819373457E-4</v>
       </c>
       <c r="AC29">
-        <v>1.5332234325299298E-3</v>
+        <v>1.6012931728277824E-3</v>
       </c>
       <c r="AD29">
-        <v>7.5951543162253764E-3</v>
+        <v>2.225403998112464E-2</v>
       </c>
       <c r="AE29">
-        <v>-7.3358371193122686E-4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:31" x14ac:dyDescent="0.2">
+        <v>1.529557390671136E-3</v>
+      </c>
+      <c r="AF29">
+        <v>-1.0982463197712714E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>41</v>
       </c>
       <c r="B30">
-        <v>-3.479796211407622</v>
+        <v>-0.21167740125123374</v>
       </c>
       <c r="C30">
-        <v>1.268840887852403E-4</v>
+        <v>-1.6263788564520126E-5</v>
       </c>
       <c r="D30">
-        <v>-1.5780736543313686E-2</v>
+        <v>4.5938859206975024E-5</v>
       </c>
       <c r="E30">
-        <v>2.8828078037175422E-4</v>
+        <v>-1.3239563656416592E-6</v>
       </c>
       <c r="F30">
-        <v>-7.8049976886715479E-3</v>
+        <v>-1.5371471592788392E-4</v>
       </c>
       <c r="G30">
-        <v>-7.527512833879018E-3</v>
+        <v>-9.6399030472008593E-5</v>
       </c>
       <c r="H30">
-        <v>-8.9197156502368383E-3</v>
+        <v>-3.4721657098736841E-5</v>
       </c>
       <c r="I30">
-        <v>-4.5251570341358141E-3</v>
+        <v>-5.8199699141244453E-5</v>
       </c>
       <c r="J30">
-        <v>-3.93532726756886E-3</v>
+        <v>-1.3259019736037081E-5</v>
       </c>
       <c r="K30">
-        <v>-4.5922890442269965E-3</v>
+        <v>1.4390576215908237E-4</v>
       </c>
       <c r="L30">
-        <v>-5.0173087365462787E-3</v>
+        <v>1.4636320971836723E-4</v>
       </c>
       <c r="M30">
-        <v>-7.1497321724051394E-3</v>
+        <v>3.3483355004522593E-4</v>
       </c>
       <c r="N30">
-        <v>-7.8608146394417936E-3</v>
+        <v>1.2756104613542886E-4</v>
       </c>
       <c r="O30">
-        <v>-6.8897660269216544E-3</v>
+        <v>6.9708163366788954E-4</v>
       </c>
       <c r="P30">
-        <v>-7.4029150966422397E-3</v>
+        <v>4.2949958651375013E-4</v>
       </c>
       <c r="Q30">
-        <v>-5.8583659104293577E-3</v>
+        <v>6.705768760565373E-4</v>
       </c>
       <c r="R30">
-        <v>-6.1966872707844636E-3</v>
+        <v>5.647207535889677E-4</v>
       </c>
       <c r="S30">
-        <v>-6.9280385138953257E-3</v>
+        <v>2.3555444547826711E-4</v>
       </c>
       <c r="T30">
-        <v>-6.9917621702153075E-3</v>
+        <v>4.6553896826760589E-4</v>
       </c>
       <c r="U30">
-        <v>-7.0647692506423023E-3</v>
+        <v>6.9886718084717701E-4</v>
       </c>
       <c r="V30">
-        <v>-6.6340885237400078E-3</v>
+        <v>8.540285919441603E-4</v>
       </c>
       <c r="W30">
-        <v>-8.1672672765457661E-3</v>
+        <v>7.9533769129889759E-4</v>
       </c>
       <c r="X30">
-        <v>-4.2998183190180173E-3</v>
+        <v>6.1811414330239589E-4</v>
       </c>
       <c r="Y30">
-        <v>-5.109483342639182E-4</v>
+        <v>7.452836621582215E-4</v>
       </c>
       <c r="Z30">
-        <v>1.7216177399785645E-3</v>
+        <v>-2.9776083124929033E-5</v>
       </c>
       <c r="AA30">
-        <v>2.782632183163524E-3</v>
+        <v>8.1059336180796962E-4</v>
       </c>
       <c r="AB30">
-        <v>-5.2207757882608181E-4</v>
+        <v>6.1799608931991035E-5</v>
       </c>
       <c r="AC30">
-        <v>-1.1206354892388748E-2</v>
+        <v>5.766615819541059E-4</v>
       </c>
       <c r="AD30">
-        <v>-7.3358371193122686E-4</v>
+        <v>1.529557390671136E-3</v>
       </c>
       <c r="AE30">
-        <v>0.23320811686834364</v>
+        <v>7.6222554067838667E-3</v>
+      </c>
+      <c r="AF30">
+        <v>-7.879032034509223E-4</v>
+      </c>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31">
+        <v>-3.8644909703584878</v>
+      </c>
+      <c r="C31">
+        <v>1.2366993500762848E-4</v>
+      </c>
+      <c r="D31">
+        <v>-1.6808632573797836E-2</v>
+      </c>
+      <c r="E31">
+        <v>3.0706765633689022E-4</v>
+      </c>
+      <c r="F31">
+        <v>-1.2787263037740082E-2</v>
+      </c>
+      <c r="G31">
+        <v>-7.8759709211673103E-3</v>
+      </c>
+      <c r="H31">
+        <v>-8.3513290753085521E-3</v>
+      </c>
+      <c r="I31">
+        <v>-5.7212067258735344E-3</v>
+      </c>
+      <c r="J31">
+        <v>-5.7682647594389045E-3</v>
+      </c>
+      <c r="K31">
+        <v>-7.0144060457698106E-3</v>
+      </c>
+      <c r="L31">
+        <v>-6.4809373635966987E-3</v>
+      </c>
+      <c r="M31">
+        <v>-6.8969492390412186E-3</v>
+      </c>
+      <c r="N31">
+        <v>-9.1896095843771019E-3</v>
+      </c>
+      <c r="O31">
+        <v>-7.5071007540232692E-3</v>
+      </c>
+      <c r="P31">
+        <v>-6.7386493439850507E-3</v>
+      </c>
+      <c r="Q31">
+        <v>-7.5447656928781604E-3</v>
+      </c>
+      <c r="R31">
+        <v>-6.1490466953348505E-3</v>
+      </c>
+      <c r="S31">
+        <v>-6.1852708304634399E-3</v>
+      </c>
+      <c r="T31">
+        <v>-6.833533655218561E-3</v>
+      </c>
+      <c r="U31">
+        <v>-6.8252074618705685E-3</v>
+      </c>
+      <c r="V31">
+        <v>-6.8430847914009076E-3</v>
+      </c>
+      <c r="W31">
+        <v>-6.6672566230439817E-3</v>
+      </c>
+      <c r="X31">
+        <v>-8.1235657763158893E-3</v>
+      </c>
+      <c r="Y31">
+        <v>-4.1967151553959411E-3</v>
+      </c>
+      <c r="Z31">
+        <v>-5.1025476033362508E-4</v>
+      </c>
+      <c r="AA31">
+        <v>1.5987703405011271E-3</v>
+      </c>
+      <c r="AB31">
+        <v>2.5819594381777671E-3</v>
+      </c>
+      <c r="AC31">
+        <v>-2.6107629693339482E-4</v>
+      </c>
+      <c r="AD31">
+        <v>-1.0982463197712714E-2</v>
+      </c>
+      <c r="AE31">
+        <v>-7.879032034509223E-4</v>
+      </c>
+      <c r="AF31">
+        <v>0.24905340225726197</v>
       </c>
     </row>
   </sheetData>

--- a/input/reg_leave_parental_home.xlsx
+++ b/input/reg_leave_parental_home.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10215"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Sonnewald/GitHub/SimPaths/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{046BC585-488C-A24B-8B49-74C5E2952126}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAAB8760-E1DA-1549-87BB-E77BE0482110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="30240" windowHeight="19540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30240" yWindow="600" windowWidth="38400" windowHeight="19440" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="58">
   <si>
     <t>Description:</t>
   </si>
@@ -132,7 +132,37 @@
     <t>UKN</t>
   </si>
   <si>
-    <t>Year_transformed</t>
+    <t>Ethn_Asian</t>
+  </si>
+  <si>
+    <t>Ethn_Black</t>
+  </si>
+  <si>
+    <t>Ethn_Other</t>
+  </si>
+  <si>
+    <t>Y2012</t>
+  </si>
+  <si>
+    <t>Y2013</t>
+  </si>
+  <si>
+    <t>Y2014</t>
+  </si>
+  <si>
+    <t>Y2015</t>
+  </si>
+  <si>
+    <t>Y2016</t>
+  </si>
+  <si>
+    <t>Y2017</t>
+  </si>
+  <si>
+    <t>Y2018</t>
+  </si>
+  <si>
+    <t>Y2019</t>
   </si>
   <si>
     <t>Y2020</t>
@@ -141,13 +171,13 @@
     <t>Y2021</t>
   </si>
   <si>
-    <t>Ethn_Asian</t>
+    <t>Y2022</t>
   </si>
   <si>
-    <t>Ethn_Black</t>
+    <t>Y2023</t>
   </si>
   <si>
-    <t>Ethn_Other</t>
+    <t>Y2024</t>
   </si>
   <si>
     <t>Constant</t>
@@ -671,35 +701,35 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A3" s="5" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B5">
-        <v>6.7073258632073696E-2</v>
+        <v>6.9393275653428899E-2</v>
       </c>
       <c r="E5" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="F5">
-        <v>661.4423481868846</v>
+        <v>710.89898169733476</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B6">
-        <v>24022</v>
+        <v>24036</v>
       </c>
       <c r="E6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="F6">
-        <v>-4575490.6663713455</v>
+        <v>-4568246.9117872091</v>
       </c>
     </row>
   </sheetData>
@@ -709,10 +739,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AF31"/>
+  <dimension ref="A1:AP41"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>11</v>
       </c>
@@ -809,2945 +839,5155 @@
       <c r="AF1" t="s">
         <v>42</v>
       </c>
+      <c r="AG1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>51</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>52</v>
+      </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>13</v>
       </c>
       <c r="B2">
-        <v>-0.20758112018024577</v>
+        <v>-0.20326063677298981</v>
       </c>
       <c r="C2">
-        <v>1.0005206591985412E-3</v>
+        <v>9.9704837736721468E-4</v>
       </c>
       <c r="D2">
-        <v>-3.5814547092007554E-5</v>
+        <v>-4.4173914881917063E-5</v>
       </c>
       <c r="E2">
-        <v>3.5996480465815583E-7</v>
+        <v>4.7994632503089972E-7</v>
       </c>
       <c r="F2">
-        <v>-2.2036577315475298E-4</v>
+        <v>-2.1042432642059085E-4</v>
       </c>
       <c r="G2">
-        <v>-1.5218301699738187E-4</v>
+        <v>-1.4228753409179545E-4</v>
       </c>
       <c r="H2">
-        <v>-2.7525005442595831E-4</v>
+        <v>-3.0449904660383707E-4</v>
       </c>
       <c r="I2">
-        <v>1.966244507026618E-4</v>
+        <v>1.0516331586592209E-4</v>
       </c>
       <c r="J2">
-        <v>4.6776370144376223E-5</v>
+        <v>-8.4569240187362495E-5</v>
       </c>
       <c r="K2">
-        <v>1.3433701185813936E-4</v>
+        <v>-2.8820999913428178E-5</v>
       </c>
       <c r="L2">
-        <v>1.4362906355992955E-4</v>
+        <v>-4.4275838381619857E-5</v>
       </c>
       <c r="M2">
-        <v>1.4969478050918337E-4</v>
+        <v>-2.9617050084873746E-5</v>
       </c>
       <c r="N2">
-        <v>1.9635896086423577E-5</v>
+        <v>-8.406784863992055E-5</v>
       </c>
       <c r="O2">
-        <v>-1.5529268109889887E-4</v>
+        <v>-1.9572763911258748E-4</v>
       </c>
       <c r="P2">
-        <v>1.6340289846084841E-4</v>
+        <v>1.5980925330027053E-4</v>
       </c>
       <c r="Q2">
-        <v>2.1289421178969284E-5</v>
+        <v>-7.8817826446984132E-6</v>
       </c>
       <c r="R2">
-        <v>6.4434250311572973E-6</v>
+        <v>-5.9965109671731291E-6</v>
       </c>
       <c r="S2">
-        <v>5.9646024902017735E-5</v>
+        <v>4.3065328651705516E-5</v>
       </c>
       <c r="T2">
-        <v>-2.412411564488479E-5</v>
+        <v>-4.160425112065179E-5</v>
       </c>
       <c r="U2">
-        <v>-5.8235237810183649E-5</v>
+        <v>-7.7336011912995051E-5</v>
       </c>
       <c r="V2">
-        <v>3.8308562154541274E-5</v>
+        <v>3.0047282918194743E-5</v>
       </c>
       <c r="W2">
-        <v>-1.2603087492062997E-5</v>
+        <v>-2.4096929068681967E-5</v>
       </c>
       <c r="X2">
-        <v>-1.2415530464250412E-5</v>
+        <v>-7.849435184905814E-6</v>
       </c>
       <c r="Y2">
-        <v>6.2049055527128172E-5</v>
+        <v>5.1487735226655074E-5</v>
       </c>
       <c r="Z2">
-        <v>1.5707991150727183E-6</v>
+        <v>-1.5876900891577438E-5</v>
       </c>
       <c r="AA2">
-        <v>4.4743738907690041E-5</v>
+        <v>-5.7409016532948489E-4</v>
       </c>
       <c r="AB2">
-        <v>1.9346771455097677E-5</v>
+        <v>-2.7027227406896798E-5</v>
       </c>
       <c r="AC2">
-        <v>-8.5206271170738937E-6</v>
+        <v>7.4784670202262093E-6</v>
       </c>
       <c r="AD2">
-        <v>-4.8491751454143037E-4</v>
+        <v>-5.9860052688067599E-6</v>
       </c>
       <c r="AE2">
-        <v>-1.6263788564520126E-5</v>
+        <v>-3.4440625634049764E-5</v>
       </c>
       <c r="AF2">
-        <v>1.2366993500762848E-4</v>
+        <v>-6.6903555485593632E-6</v>
+      </c>
+      <c r="AG2">
+        <v>2.0004222741746143E-5</v>
+      </c>
+      <c r="AH2">
+        <v>1.4649876089515727E-5</v>
+      </c>
+      <c r="AI2">
+        <v>3.8804370643321105E-5</v>
+      </c>
+      <c r="AJ2">
+        <v>8.783647549707519E-5</v>
+      </c>
+      <c r="AK2">
+        <v>4.7995511203565377E-5</v>
+      </c>
+      <c r="AL2">
+        <v>2.5863602629088659E-5</v>
+      </c>
+      <c r="AM2">
+        <v>-1.2376637487951109E-4</v>
+      </c>
+      <c r="AN2">
+        <v>-3.5963592568216901E-6</v>
+      </c>
+      <c r="AO2">
+        <v>1.3509571378930317E-4</v>
+      </c>
+      <c r="AP2">
+        <v>4.5561383890587847E-4</v>
       </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3">
-        <v>0.1997281297465206</v>
+        <v>0.19661820638317479</v>
       </c>
       <c r="C3">
-        <v>-3.5814547092007554E-5</v>
+        <v>-4.4173914881917063E-5</v>
       </c>
       <c r="D3">
-        <v>1.2112041023426448E-3</v>
+        <v>1.3056276923265164E-3</v>
       </c>
       <c r="E3">
-        <v>-2.2319934708756732E-5</v>
+        <v>-2.4015129291367468E-5</v>
       </c>
       <c r="F3">
-        <v>8.0351321999211226E-4</v>
+        <v>7.8941750058599165E-4</v>
       </c>
       <c r="G3">
-        <v>4.4497146669870871E-4</v>
+        <v>4.9442357924594062E-4</v>
       </c>
       <c r="H3">
-        <v>5.3704397132845415E-4</v>
+        <v>6.4344731555613516E-4</v>
       </c>
       <c r="I3">
-        <v>3.0096852119942648E-4</v>
+        <v>6.5663635797929719E-4</v>
       </c>
       <c r="J3">
-        <v>2.7006149659412296E-4</v>
+        <v>5.3263933432045533E-4</v>
       </c>
       <c r="K3">
-        <v>3.2910446154502885E-4</v>
+        <v>6.4997659698641606E-4</v>
       </c>
       <c r="L3">
-        <v>2.5996012241122335E-4</v>
+        <v>6.0399023573341759E-4</v>
       </c>
       <c r="M3">
-        <v>2.5911096908810122E-4</v>
+        <v>5.9540372223328001E-4</v>
       </c>
       <c r="N3">
-        <v>5.0582283882276489E-4</v>
+        <v>8.0011656375668155E-4</v>
       </c>
       <c r="O3">
-        <v>2.8027296158254214E-4</v>
+        <v>3.4786848931778278E-4</v>
       </c>
       <c r="P3">
-        <v>2.320916846641442E-4</v>
+        <v>2.8884004910859941E-4</v>
       </c>
       <c r="Q3">
-        <v>3.3612945322286322E-4</v>
+        <v>3.8809193031468891E-4</v>
       </c>
       <c r="R3">
-        <v>2.5331675022573767E-4</v>
+        <v>2.984059307919721E-4</v>
       </c>
       <c r="S3">
-        <v>2.3121237053660266E-4</v>
+        <v>2.6612113875851577E-4</v>
       </c>
       <c r="T3">
-        <v>2.9508295579747427E-4</v>
+        <v>3.3651281784985757E-4</v>
       </c>
       <c r="U3">
-        <v>2.2676346763183175E-4</v>
+        <v>2.7941384014819153E-4</v>
       </c>
       <c r="V3">
-        <v>2.8705440860610242E-4</v>
+        <v>3.3721121530420179E-4</v>
       </c>
       <c r="W3">
-        <v>2.4318932414474424E-4</v>
+        <v>2.649294187907728E-4</v>
       </c>
       <c r="X3">
-        <v>3.7117580639640371E-4</v>
+        <v>4.3744291936165876E-4</v>
       </c>
       <c r="Y3">
-        <v>8.6311337591227048E-5</v>
+        <v>1.3424030484546386E-4</v>
       </c>
       <c r="Z3">
-        <v>6.0185117747523463E-6</v>
+        <v>-3.1330126577712274E-5</v>
       </c>
       <c r="AA3">
-        <v>7.7573150486439117E-6</v>
+        <v>3.8080296473268736E-4</v>
       </c>
       <c r="AB3">
-        <v>-4.37111033549549E-5</v>
+        <v>3.9857353105700842E-5</v>
       </c>
       <c r="AC3">
-        <v>-5.7483922405465911E-5</v>
+        <v>-5.4665700489507022E-5</v>
       </c>
       <c r="AD3">
-        <v>3.0594389090943946E-4</v>
+        <v>-4.7464121990653139E-5</v>
       </c>
       <c r="AE3">
-        <v>4.5938859206975024E-5</v>
+        <v>1.1316046713941022E-5</v>
       </c>
       <c r="AF3">
-        <v>-1.6808632573797836E-2</v>
+        <v>7.14974823305594E-7</v>
+      </c>
+      <c r="AG3">
+        <v>-1.4995529296624177E-5</v>
+      </c>
+      <c r="AH3">
+        <v>-5.5909991886769587E-5</v>
+      </c>
+      <c r="AI3">
+        <v>-3.6563505017555425E-5</v>
+      </c>
+      <c r="AJ3">
+        <v>1.5202161530642778E-5</v>
+      </c>
+      <c r="AK3">
+        <v>1.0934904013128882E-5</v>
+      </c>
+      <c r="AL3">
+        <v>-2.8845380680408636E-5</v>
+      </c>
+      <c r="AM3">
+        <v>1.3893432878530655E-4</v>
+      </c>
+      <c r="AN3">
+        <v>-5.3416192538011283E-5</v>
+      </c>
+      <c r="AO3">
+        <v>8.0277675077015248E-5</v>
+      </c>
+      <c r="AP3">
+        <v>-1.8380139386570998E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4">
-        <v>-2.6773497318359567E-3</v>
+        <v>-2.6322446526901144E-3</v>
       </c>
       <c r="C4">
-        <v>3.5996480465815583E-7</v>
+        <v>4.7994632503089972E-7</v>
       </c>
       <c r="D4">
-        <v>-2.2319934708756732E-5</v>
+        <v>-2.4015129291367468E-5</v>
       </c>
       <c r="E4">
-        <v>4.1568459528178607E-7</v>
+        <v>4.4625452164940095E-7</v>
       </c>
       <c r="F4">
-        <v>-1.4180521210316629E-5</v>
+        <v>-1.3981571027355304E-5</v>
       </c>
       <c r="G4">
-        <v>-8.0599661547113414E-6</v>
+        <v>-8.9507388640175497E-6</v>
       </c>
       <c r="H4">
-        <v>-1.0164380172712992E-5</v>
+        <v>-1.1967039340186793E-5</v>
       </c>
       <c r="I4">
-        <v>-4.8600956288020276E-6</v>
+        <v>-1.0858368440379934E-5</v>
       </c>
       <c r="J4">
-        <v>-4.661458229733817E-6</v>
+        <v>-9.020763542303299E-6</v>
       </c>
       <c r="K4">
-        <v>-5.6048751393461587E-6</v>
+        <v>-1.0866629508134241E-5</v>
       </c>
       <c r="L4">
-        <v>-4.4428458269934562E-6</v>
+        <v>-1.0176081865245247E-5</v>
       </c>
       <c r="M4">
-        <v>-4.9496581091379433E-6</v>
+        <v>-1.0540649356896324E-5</v>
       </c>
       <c r="N4">
-        <v>-9.3088091981656037E-6</v>
+        <v>-1.42890125614471E-5</v>
       </c>
       <c r="O4">
-        <v>-5.1601543477111712E-6</v>
+        <v>-6.3447370974616251E-6</v>
       </c>
       <c r="P4">
-        <v>-4.7744167412468636E-6</v>
+        <v>-5.861031852039998E-6</v>
       </c>
       <c r="Q4">
-        <v>-6.4722889666835487E-6</v>
+        <v>-7.4401517611559254E-6</v>
       </c>
       <c r="R4">
-        <v>-4.8878282369641678E-6</v>
+        <v>-5.7475404668365057E-6</v>
       </c>
       <c r="S4">
-        <v>-4.601562683222023E-6</v>
+        <v>-5.2706840217776844E-6</v>
       </c>
       <c r="T4">
-        <v>-5.5307647907283899E-6</v>
+        <v>-6.3320781985083339E-6</v>
       </c>
       <c r="U4">
-        <v>-4.4725187062759166E-6</v>
+        <v>-5.4638105352337708E-6</v>
       </c>
       <c r="V4">
-        <v>-5.4622681237404913E-6</v>
+        <v>-6.3992496100736968E-6</v>
       </c>
       <c r="W4">
-        <v>-4.847160544957353E-6</v>
+        <v>-5.3645852991998655E-6</v>
       </c>
       <c r="X4">
-        <v>-6.8188063961987933E-6</v>
+        <v>-8.0043737470209231E-6</v>
       </c>
       <c r="Y4">
-        <v>-1.9027586668400809E-6</v>
+        <v>-2.7837049819938063E-6</v>
       </c>
       <c r="Z4">
-        <v>-1.1147281012490682E-7</v>
+        <v>3.9456668226590106E-7</v>
       </c>
       <c r="AA4">
-        <v>-1.6341386261677094E-7</v>
+        <v>-8.0987779329726812E-6</v>
       </c>
       <c r="AB4">
-        <v>5.9964560833659268E-7</v>
+        <v>-1.2520889908363005E-6</v>
       </c>
       <c r="AC4">
-        <v>8.6386851775463133E-7</v>
+        <v>9.7447617253322515E-7</v>
       </c>
       <c r="AD4">
-        <v>-6.7249685989256738E-6</v>
+        <v>8.7283678387166684E-7</v>
       </c>
       <c r="AE4">
-        <v>-1.3239563656416592E-6</v>
+        <v>-1.008928501183113E-7</v>
       </c>
       <c r="AF4">
-        <v>3.0706765633689022E-4</v>
+        <v>5.4569807281148585E-8</v>
+      </c>
+      <c r="AG4">
+        <v>2.5505135890218776E-7</v>
+      </c>
+      <c r="AH4">
+        <v>9.4372926843673001E-7</v>
+      </c>
+      <c r="AI4">
+        <v>6.3413159001905403E-7</v>
+      </c>
+      <c r="AJ4">
+        <v>-3.9019777466520363E-7</v>
+      </c>
+      <c r="AK4">
+        <v>-2.4995715028938281E-7</v>
+      </c>
+      <c r="AL4">
+        <v>3.1910575266509678E-7</v>
+      </c>
+      <c r="AM4">
+        <v>-2.265882714184075E-6</v>
+      </c>
+      <c r="AN4">
+        <v>8.1361826427441952E-7</v>
+      </c>
+      <c r="AO4">
+        <v>-1.5675230351619549E-6</v>
+      </c>
+      <c r="AP4">
+        <v>3.3475279048161117E-4</v>
       </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>16</v>
       </c>
       <c r="B5">
-        <v>-7.5051253269756077E-2</v>
+        <v>-4.0692152807306238E-2</v>
       </c>
       <c r="C5">
-        <v>-2.2036577315475298E-4</v>
+        <v>-2.1042432642059085E-4</v>
       </c>
       <c r="D5">
-        <v>8.0351321999211226E-4</v>
+        <v>7.8941750058599165E-4</v>
       </c>
       <c r="E5">
-        <v>-1.4180521210316629E-5</v>
+        <v>-1.3981571027355304E-5</v>
       </c>
       <c r="F5">
-        <v>6.77613174194216E-3</v>
+        <v>6.7718235200703563E-3</v>
       </c>
       <c r="G5">
-        <v>1.6810336411684612E-3</v>
+        <v>1.6713093658011395E-3</v>
       </c>
       <c r="H5">
-        <v>1.4784298075190723E-3</v>
+        <v>1.4290778639007122E-3</v>
       </c>
       <c r="I5">
-        <v>-3.042042530406778E-3</v>
+        <v>-3.276031471167392E-3</v>
       </c>
       <c r="J5">
-        <v>-1.9630702327500644E-4</v>
+        <v>-4.6563613374951403E-4</v>
       </c>
       <c r="K5">
-        <v>4.6845558334803524E-5</v>
+        <v>-2.2120828958631248E-4</v>
       </c>
       <c r="L5">
-        <v>-2.2933061411999881E-4</v>
+        <v>-5.4121750353762184E-4</v>
       </c>
       <c r="M5">
-        <v>-3.269752371923122E-5</v>
+        <v>-3.859299226464798E-4</v>
       </c>
       <c r="N5">
-        <v>-7.8204176065001674E-5</v>
+        <v>-3.6637403028690887E-4</v>
       </c>
       <c r="O5">
-        <v>1.968024775126202E-4</v>
+        <v>1.6800494291322691E-4</v>
       </c>
       <c r="P5">
-        <v>3.9191593996575503E-5</v>
+        <v>8.9285974995166779E-5</v>
       </c>
       <c r="Q5">
-        <v>1.2229678380336058E-4</v>
+        <v>1.4543060339891048E-4</v>
       </c>
       <c r="R5">
-        <v>1.8200220245876344E-4</v>
+        <v>2.3263863128959307E-4</v>
       </c>
       <c r="S5">
-        <v>-1.6945566355887082E-5</v>
+        <v>1.2368263278105278E-5</v>
       </c>
       <c r="T5">
-        <v>-9.9921214716107627E-5</v>
+        <v>-5.2186343191129993E-5</v>
       </c>
       <c r="U5">
-        <v>3.1591749473021142E-4</v>
+        <v>3.5976489490857307E-4</v>
       </c>
       <c r="V5">
-        <v>-3.4902018928462055E-5</v>
+        <v>-2.3728772881969999E-6</v>
       </c>
       <c r="W5">
-        <v>4.2043914335640692E-5</v>
+        <v>7.3155472425723419E-5</v>
       </c>
       <c r="X5">
-        <v>4.004151662559516E-4</v>
+        <v>4.7911234846116798E-4</v>
       </c>
       <c r="Y5">
-        <v>1.583288399686477E-5</v>
+        <v>5.5201431054995032E-5</v>
       </c>
       <c r="Z5">
-        <v>4.7225383861884251E-5</v>
+        <v>4.8224373789462847E-5</v>
       </c>
       <c r="AA5">
-        <v>-5.6160774035137666E-5</v>
+        <v>9.9289398882804452E-4</v>
       </c>
       <c r="AB5">
-        <v>-1.5091809039732948E-5</v>
+        <v>-1.6280678759891354E-4</v>
       </c>
       <c r="AC5">
-        <v>1.5780785762827161E-5</v>
+        <v>4.3968781107485303E-5</v>
       </c>
       <c r="AD5">
-        <v>9.6731761536263811E-4</v>
+        <v>-5.2876722559791391E-5</v>
       </c>
       <c r="AE5">
-        <v>-1.5371471592788392E-4</v>
+        <v>1.0265418675298394E-4</v>
       </c>
       <c r="AF5">
-        <v>-1.2787263037740082E-2</v>
+        <v>1.0435313997194631E-4</v>
+      </c>
+      <c r="AG5">
+        <v>1.8140607605269957E-4</v>
+      </c>
+      <c r="AH5">
+        <v>-9.2841039450234936E-5</v>
+      </c>
+      <c r="AI5">
+        <v>3.3204683387832177E-4</v>
+      </c>
+      <c r="AJ5">
+        <v>2.723793467413263E-4</v>
+      </c>
+      <c r="AK5">
+        <v>3.4019014235276129E-4</v>
+      </c>
+      <c r="AL5">
+        <v>3.6075602653079953E-4</v>
+      </c>
+      <c r="AM5">
+        <v>6.8543040571977278E-4</v>
+      </c>
+      <c r="AN5">
+        <v>1.3790508204609107E-4</v>
+      </c>
+      <c r="AO5">
+        <v>8.5273610688927845E-4</v>
+      </c>
+      <c r="AP5">
+        <v>-1.1668539620610523E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>17</v>
       </c>
       <c r="B6">
-        <v>-0.19760244631696608</v>
+        <v>-0.19989589236944563</v>
       </c>
       <c r="C6">
-        <v>-1.5218301699738187E-4</v>
+        <v>-1.4228753409179545E-4</v>
       </c>
       <c r="D6">
-        <v>4.4497146669870871E-4</v>
+        <v>4.9442357924594062E-4</v>
       </c>
       <c r="E6">
-        <v>-8.0599661547113414E-6</v>
+        <v>-8.9507388640175497E-6</v>
       </c>
       <c r="F6">
-        <v>1.6810336411684612E-3</v>
+        <v>1.6713093658011395E-3</v>
       </c>
       <c r="G6">
-        <v>1.6833278170857845E-3</v>
+        <v>1.6897020629405078E-3</v>
       </c>
       <c r="H6">
-        <v>1.3547860022670674E-3</v>
+        <v>1.3485970634110008E-3</v>
       </c>
       <c r="I6">
-        <v>-2.1201699064095077E-4</v>
+        <v>-1.8066006112108283E-4</v>
       </c>
       <c r="J6">
-        <v>-6.4462147394792383E-5</v>
+        <v>-6.7676398302700955E-5</v>
       </c>
       <c r="K6">
-        <v>1.7484144327233335E-5</v>
+        <v>6.3316555738092699E-5</v>
       </c>
       <c r="L6">
-        <v>-3.83540622167001E-6</v>
+        <v>1.7770964507714433E-5</v>
       </c>
       <c r="M6">
-        <v>2.7833817273945836E-4</v>
+        <v>2.3712215162435173E-4</v>
       </c>
       <c r="N6">
-        <v>3.5678371335411997E-4</v>
+        <v>3.2935369073708179E-4</v>
       </c>
       <c r="O6">
-        <v>4.3582471197963998E-4</v>
+        <v>4.5994261950243814E-4</v>
       </c>
       <c r="P6">
-        <v>3.8665993380054137E-4</v>
+        <v>4.1301142227544553E-4</v>
       </c>
       <c r="Q6">
-        <v>2.2576525796526222E-4</v>
+        <v>2.6337782792521409E-4</v>
       </c>
       <c r="R6">
-        <v>1.9830865385825916E-4</v>
+        <v>2.2231123827409541E-4</v>
       </c>
       <c r="S6">
-        <v>2.3841999109407435E-4</v>
+        <v>2.5209907698232588E-4</v>
       </c>
       <c r="T6">
-        <v>1.5795015446461007E-4</v>
+        <v>1.8588758779373036E-4</v>
       </c>
       <c r="U6">
-        <v>4.3242808590066419E-4</v>
+        <v>4.7103117547288189E-4</v>
       </c>
       <c r="V6">
-        <v>1.0697945405575843E-4</v>
+        <v>1.3729069205695334E-4</v>
       </c>
       <c r="W6">
-        <v>2.2606405081549487E-4</v>
+        <v>2.6112558970635739E-4</v>
       </c>
       <c r="X6">
-        <v>4.4390586994820606E-4</v>
+        <v>4.5561566345628387E-4</v>
       </c>
       <c r="Y6">
-        <v>2.6971178553977055E-4</v>
+        <v>3.2535158069503653E-4</v>
       </c>
       <c r="Z6">
-        <v>2.8249078510313858E-5</v>
+        <v>3.3930429597814208E-4</v>
       </c>
       <c r="AA6">
-        <v>-1.5884086586774482E-4</v>
+        <v>1.0977626702368599E-3</v>
       </c>
       <c r="AB6">
-        <v>-4.8603812532399852E-5</v>
+        <v>-9.7380284950361097E-5</v>
       </c>
       <c r="AC6">
-        <v>3.1947794391678315E-4</v>
+        <v>2.2835823655353009E-5</v>
       </c>
       <c r="AD6">
-        <v>1.0561272165055353E-3</v>
+        <v>-5.1390189181962258E-5</v>
       </c>
       <c r="AE6">
-        <v>-9.6399030472008593E-5</v>
+        <v>4.9621277999441844E-5</v>
       </c>
       <c r="AF6">
-        <v>-7.8759709211673103E-3</v>
+        <v>2.7235759662248707E-5</v>
+      </c>
+      <c r="AG6">
+        <v>9.3173130435845498E-7</v>
+      </c>
+      <c r="AH6">
+        <v>-7.3161646185764158E-6</v>
+      </c>
+      <c r="AI6">
+        <v>4.0122703423495741E-5</v>
+      </c>
+      <c r="AJ6">
+        <v>8.0121728651233806E-5</v>
+      </c>
+      <c r="AK6">
+        <v>1.9453057665350798E-5</v>
+      </c>
+      <c r="AL6">
+        <v>1.471616493165487E-4</v>
+      </c>
+      <c r="AM6">
+        <v>2.0533844589095459E-4</v>
+      </c>
+      <c r="AN6">
+        <v>1.3532117857273547E-6</v>
+      </c>
+      <c r="AO6">
+        <v>8.5425961333449214E-4</v>
+      </c>
+      <c r="AP6">
+        <v>-8.1730895959561175E-3</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>18</v>
       </c>
       <c r="B7">
-        <v>-0.40171722273970079</v>
+        <v>-0.3983759506058358</v>
       </c>
       <c r="C7">
-        <v>-2.7525005442595831E-4</v>
+        <v>-3.0449904660383707E-4</v>
       </c>
       <c r="D7">
-        <v>5.3704397132845415E-4</v>
+        <v>6.4344731555613516E-4</v>
       </c>
       <c r="E7">
-        <v>-1.0164380172712992E-5</v>
+        <v>-1.1967039340186793E-5</v>
       </c>
       <c r="F7">
-        <v>1.4784298075190723E-3</v>
+        <v>1.4290778639007122E-3</v>
       </c>
       <c r="G7">
-        <v>1.3547860022670674E-3</v>
+        <v>1.3485970634110008E-3</v>
       </c>
       <c r="H7">
-        <v>6.8247887400718996E-3</v>
+        <v>6.9949874492937821E-3</v>
       </c>
       <c r="I7">
-        <v>-7.7539984199314661E-5</v>
+        <v>3.4546942355673379E-4</v>
       </c>
       <c r="J7">
-        <v>-6.2537835174310188E-4</v>
+        <v>-2.5975205144695144E-4</v>
       </c>
       <c r="K7">
-        <v>1.8235407865441783E-4</v>
+        <v>7.7812805419780044E-4</v>
       </c>
       <c r="L7">
-        <v>2.2437071098977649E-4</v>
+        <v>6.1700225140653769E-4</v>
       </c>
       <c r="M7">
-        <v>5.3156924897645574E-4</v>
+        <v>8.8176773985379204E-4</v>
       </c>
       <c r="N7">
-        <v>6.7200452711455071E-4</v>
+        <v>1.0303938087590943E-3</v>
       </c>
       <c r="O7">
-        <v>5.334708496636492E-4</v>
+        <v>4.8118847374349031E-4</v>
       </c>
       <c r="P7">
-        <v>3.1577125179988027E-4</v>
+        <v>3.0191083619731393E-4</v>
       </c>
       <c r="Q7">
-        <v>2.7781265807227457E-4</v>
+        <v>3.8841340353002412E-4</v>
       </c>
       <c r="R7">
-        <v>2.3920822292268474E-4</v>
+        <v>2.6398467343196171E-4</v>
       </c>
       <c r="S7">
-        <v>-7.3357989133670067E-5</v>
+        <v>-9.3110350593150412E-5</v>
       </c>
       <c r="T7">
-        <v>-1.7090711527230655E-4</v>
+        <v>-1.5019922600451721E-4</v>
       </c>
       <c r="U7">
-        <v>2.0925376461486931E-4</v>
+        <v>1.9470520323450831E-4</v>
       </c>
       <c r="V7">
-        <v>7.2196678534333604E-5</v>
+        <v>9.812631938772295E-5</v>
       </c>
       <c r="W7">
-        <v>-2.6748184923592504E-4</v>
+        <v>-2.5356353638289507E-4</v>
       </c>
       <c r="X7">
-        <v>2.0448099579843128E-4</v>
+        <v>2.7234439124504704E-4</v>
       </c>
       <c r="Y7">
-        <v>-1.4141087857681158E-4</v>
+        <v>-1.4888379230037401E-4</v>
       </c>
       <c r="Z7">
-        <v>2.7587062873393265E-6</v>
+        <v>5.1859267960335754E-4</v>
       </c>
       <c r="AA7">
-        <v>6.7696276270442392E-5</v>
+        <v>6.4906242733550482E-4</v>
       </c>
       <c r="AB7">
-        <v>-1.6483260493021059E-5</v>
+        <v>-5.6858170959505684E-5</v>
       </c>
       <c r="AC7">
-        <v>4.8536917546892675E-4</v>
+        <v>4.8434330924966362E-5</v>
       </c>
       <c r="AD7">
-        <v>7.7981861282318612E-4</v>
+        <v>8.3822554608010719E-5</v>
       </c>
       <c r="AE7">
-        <v>-3.4721657098736841E-5</v>
+        <v>2.0352282851995472E-5</v>
       </c>
       <c r="AF7">
-        <v>-8.3513290753085521E-3</v>
+        <v>2.1017427230243379E-4</v>
+      </c>
+      <c r="AG7">
+        <v>1.8430231044319059E-4</v>
+      </c>
+      <c r="AH7">
+        <v>1.3903663627384062E-4</v>
+      </c>
+      <c r="AI7">
+        <v>-1.3912756673658015E-5</v>
+      </c>
+      <c r="AJ7">
+        <v>3.0000546713841725E-4</v>
+      </c>
+      <c r="AK7">
+        <v>1.880965996353557E-4</v>
+      </c>
+      <c r="AL7">
+        <v>8.6816632504247305E-5</v>
+      </c>
+      <c r="AM7">
+        <v>1.6031937910752133E-4</v>
+      </c>
+      <c r="AN7">
+        <v>-2.3696677730575657E-4</v>
+      </c>
+      <c r="AO7">
+        <v>1.2524687784377236E-4</v>
+      </c>
+      <c r="AP7">
+        <v>-1.0324638928380625E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>19</v>
       </c>
       <c r="B8">
-        <v>-0.18533550293176548</v>
+        <v>-0.29331006354875272</v>
       </c>
       <c r="C8">
-        <v>1.966244507026618E-4</v>
+        <v>1.0516331586592209E-4</v>
       </c>
       <c r="D8">
-        <v>3.0096852119942648E-4</v>
+        <v>6.5663635797929719E-4</v>
       </c>
       <c r="E8">
-        <v>-4.8600956288020276E-6</v>
+        <v>-1.0858368440379934E-5</v>
       </c>
       <c r="F8">
-        <v>-3.042042530406778E-3</v>
+        <v>-3.276031471167392E-3</v>
       </c>
       <c r="G8">
-        <v>-2.1201699064095077E-4</v>
+        <v>-1.8066006112108283E-4</v>
       </c>
       <c r="H8">
-        <v>-7.7539984199314661E-5</v>
+        <v>3.4546942355673379E-4</v>
       </c>
       <c r="I8">
-        <v>4.2844875985216142E-3</v>
+        <v>6.0051233345080387E-3</v>
       </c>
       <c r="J8">
-        <v>1.5759004100588572E-3</v>
+        <v>2.8424688165048758E-3</v>
       </c>
       <c r="K8">
-        <v>1.0281292675592643E-3</v>
+        <v>2.6594987327506533E-3</v>
       </c>
       <c r="L8">
-        <v>1.7204766728795579E-3</v>
+        <v>3.4016907303035544E-3</v>
       </c>
       <c r="M8">
-        <v>1.6070944659217674E-3</v>
+        <v>3.1271906930517529E-3</v>
       </c>
       <c r="N8">
-        <v>1.3044449891990305E-3</v>
+        <v>2.5517254987284595E-3</v>
       </c>
       <c r="O8">
-        <v>-1.7272541229972885E-4</v>
+        <v>-1.2161124602095338E-4</v>
       </c>
       <c r="P8">
-        <v>1.9204317599709649E-6</v>
+        <v>-9.4836699514650249E-5</v>
       </c>
       <c r="Q8">
-        <v>4.1342716082856136E-5</v>
+        <v>1.2048877062741353E-4</v>
       </c>
       <c r="R8">
-        <v>-6.491178353127151E-7</v>
+        <v>-6.099036628503553E-5</v>
       </c>
       <c r="S8">
-        <v>-8.6205647767372299E-5</v>
+        <v>-1.4910516011271439E-4</v>
       </c>
       <c r="T8">
-        <v>2.4095064838562154E-4</v>
+        <v>1.5530730650522911E-4</v>
       </c>
       <c r="U8">
-        <v>-1.1370387665397071E-4</v>
+        <v>-1.687749203797286E-4</v>
       </c>
       <c r="V8">
-        <v>2.7986649151010695E-5</v>
+        <v>1.1367478037511113E-4</v>
       </c>
       <c r="W8">
-        <v>2.1395355977187947E-5</v>
+        <v>-1.0165002897182408E-5</v>
       </c>
       <c r="X8">
-        <v>-4.0747779805873211E-4</v>
+        <v>-3.9196291533570468E-4</v>
       </c>
       <c r="Y8">
-        <v>-3.9056292400923339E-5</v>
+        <v>-2.0824147670606662E-5</v>
       </c>
       <c r="Z8">
-        <v>-2.6488357675537918E-5</v>
+        <v>2.2405605565185838E-4</v>
       </c>
       <c r="AA8">
-        <v>1.1042014054976686E-4</v>
+        <v>-5.7471330329144504E-4</v>
       </c>
       <c r="AB8">
-        <v>-6.9332360169555387E-5</v>
+        <v>-5.9019406989655517E-5</v>
       </c>
       <c r="AC8">
-        <v>1.609415858674669E-4</v>
+        <v>-6.2878773545956012E-5</v>
       </c>
       <c r="AD8">
-        <v>-5.0331829423211133E-4</v>
+        <v>3.0044011387992883E-5</v>
       </c>
       <c r="AE8">
-        <v>-5.8199699141244453E-5</v>
+        <v>2.0333155571847054E-5</v>
       </c>
       <c r="AF8">
-        <v>-5.7212067258735344E-3</v>
+        <v>-1.8080654508568182E-5</v>
+      </c>
+      <c r="AG8">
+        <v>-1.4884399641707565E-4</v>
+      </c>
+      <c r="AH8">
+        <v>1.0436353515452541E-4</v>
+      </c>
+      <c r="AI8">
+        <v>-1.6112883930819322E-4</v>
+      </c>
+      <c r="AJ8">
+        <v>-2.665490913543022E-4</v>
+      </c>
+      <c r="AK8">
+        <v>-3.2665423607252525E-4</v>
+      </c>
+      <c r="AL8">
+        <v>-2.5722103043426467E-4</v>
+      </c>
+      <c r="AM8">
+        <v>-4.9771116396402429E-4</v>
+      </c>
+      <c r="AN8">
+        <v>-2.6837823075678922E-4</v>
+      </c>
+      <c r="AO8">
+        <v>-3.9039734697497372E-4</v>
+      </c>
+      <c r="AP8">
+        <v>-1.2642002368749055E-2</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>20</v>
       </c>
       <c r="B9">
-        <v>-0.25167997114882762</v>
+        <v>-0.31439800405492929</v>
       </c>
       <c r="C9">
-        <v>4.6776370144376223E-5</v>
+        <v>-8.4569240187362495E-5</v>
       </c>
       <c r="D9">
-        <v>2.7006149659412296E-4</v>
+        <v>5.3263933432045533E-4</v>
       </c>
       <c r="E9">
-        <v>-4.661458229733817E-6</v>
+        <v>-9.020763542303299E-6</v>
       </c>
       <c r="F9">
-        <v>-1.9630702327500644E-4</v>
+        <v>-4.6563613374951403E-4</v>
       </c>
       <c r="G9">
-        <v>-6.4462147394792383E-5</v>
+        <v>-6.7676398302700955E-5</v>
       </c>
       <c r="H9">
-        <v>-6.2537835174310188E-4</v>
+        <v>-2.5975205144695144E-4</v>
       </c>
       <c r="I9">
-        <v>1.5759004100588572E-3</v>
+        <v>2.8424688165048758E-3</v>
       </c>
       <c r="J9">
-        <v>3.2436799733072878E-3</v>
+        <v>3.8906988723211387E-3</v>
       </c>
       <c r="K9">
-        <v>1.6173685000352136E-3</v>
+        <v>2.3504713405834471E-3</v>
       </c>
       <c r="L9">
-        <v>2.1371410208063917E-3</v>
+        <v>3.0037640840158827E-3</v>
       </c>
       <c r="M9">
-        <v>2.1281368582487538E-3</v>
+        <v>2.8108475336687082E-3</v>
       </c>
       <c r="N9">
-        <v>1.6227764023620072E-3</v>
+        <v>2.1636501786146938E-3</v>
       </c>
       <c r="O9">
-        <v>-3.6426511240648257E-4</v>
+        <v>-4.276768403060475E-4</v>
       </c>
       <c r="P9">
-        <v>-1.0649904882898721E-4</v>
+        <v>-1.840075526855613E-4</v>
       </c>
       <c r="Q9">
-        <v>2.3529619841122708E-5</v>
+        <v>9.3469866740401018E-5</v>
       </c>
       <c r="R9">
-        <v>-1.9777414909828397E-4</v>
+        <v>-2.1878240517719821E-4</v>
       </c>
       <c r="S9">
-        <v>-6.2411402324679928E-5</v>
+        <v>-1.0197111397685483E-4</v>
       </c>
       <c r="T9">
-        <v>1.3881636743120481E-4</v>
+        <v>8.7240043180704277E-5</v>
       </c>
       <c r="U9">
-        <v>3.4149069492930102E-5</v>
+        <v>-9.3191404206718724E-6</v>
       </c>
       <c r="V9">
-        <v>-9.492733634786603E-5</v>
+        <v>-1.7693537704697223E-6</v>
       </c>
       <c r="W9">
-        <v>6.0030106901738851E-5</v>
+        <v>-2.0527851590402798E-5</v>
       </c>
       <c r="X9">
-        <v>-4.4014557325362216E-4</v>
+        <v>-2.5876484092957785E-4</v>
       </c>
       <c r="Y9">
-        <v>-6.6296903178857634E-5</v>
+        <v>-4.6037001286206893E-5</v>
       </c>
       <c r="Z9">
-        <v>-1.0942222301353111E-5</v>
+        <v>1.1727582890683989E-4</v>
       </c>
       <c r="AA9">
-        <v>5.3821302802515875E-5</v>
+        <v>-3.747937841465385E-4</v>
       </c>
       <c r="AB9">
-        <v>-4.4105683785933378E-5</v>
+        <v>-3.3482622108227714E-5</v>
       </c>
       <c r="AC9">
-        <v>7.777302847041586E-5</v>
+        <v>-6.1859437384845185E-6</v>
       </c>
       <c r="AD9">
-        <v>-1.9751254821681347E-4</v>
+        <v>5.6484891149170607E-5</v>
       </c>
       <c r="AE9">
-        <v>-1.3259019736037081E-5</v>
+        <v>1.87603462226136E-4</v>
       </c>
       <c r="AF9">
-        <v>-5.7682647594389045E-3</v>
+        <v>9.1277848479440205E-5</v>
+      </c>
+      <c r="AG9">
+        <v>1.5445587154096175E-4</v>
+      </c>
+      <c r="AH9">
+        <v>3.1072551629293937E-5</v>
+      </c>
+      <c r="AI9">
+        <v>1.725537363159689E-5</v>
+      </c>
+      <c r="AJ9">
+        <v>1.7380397806892808E-4</v>
+      </c>
+      <c r="AK9">
+        <v>-1.8628384327871225E-4</v>
+      </c>
+      <c r="AL9">
+        <v>-4.7792762222859976E-5</v>
+      </c>
+      <c r="AM9">
+        <v>-3.420883685228901E-4</v>
+      </c>
+      <c r="AN9">
+        <v>6.5534582542681533E-6</v>
+      </c>
+      <c r="AO9">
+        <v>-3.6729874495605372E-4</v>
+      </c>
+      <c r="AP9">
+        <v>-1.0449555467615017E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>21</v>
       </c>
       <c r="B10">
-        <v>-0.11101839269930437</v>
+        <v>-0.14161592855770111</v>
       </c>
       <c r="C10">
-        <v>1.3433701185813936E-4</v>
+        <v>-2.8820999913428178E-5</v>
       </c>
       <c r="D10">
-        <v>3.2910446154502885E-4</v>
+        <v>6.4997659698641606E-4</v>
       </c>
       <c r="E10">
-        <v>-5.6048751393461587E-6</v>
+        <v>-1.0866629508134241E-5</v>
       </c>
       <c r="F10">
-        <v>4.6845558334803524E-5</v>
+        <v>-2.2120828958631248E-4</v>
       </c>
       <c r="G10">
-        <v>1.7484144327233335E-5</v>
+        <v>6.3316555738092699E-5</v>
       </c>
       <c r="H10">
-        <v>1.8235407865441783E-4</v>
+        <v>7.7812805419780044E-4</v>
       </c>
       <c r="I10">
-        <v>1.0281292675592643E-3</v>
+        <v>2.6594987327506533E-3</v>
       </c>
       <c r="J10">
-        <v>1.6173685000352136E-3</v>
+        <v>2.3504713405834471E-3</v>
       </c>
       <c r="K10">
-        <v>3.1686606126896202E-3</v>
+        <v>4.2099757554453507E-3</v>
       </c>
       <c r="L10">
-        <v>2.2253028858731779E-3</v>
+        <v>3.1346754598403671E-3</v>
       </c>
       <c r="M10">
-        <v>2.1801257428236578E-3</v>
+        <v>2.9542396101599265E-3</v>
       </c>
       <c r="N10">
-        <v>1.969635132958844E-3</v>
+        <v>2.5365184959194086E-3</v>
       </c>
       <c r="O10">
-        <v>2.3397990037411971E-4</v>
+        <v>1.2610376826330933E-4</v>
       </c>
       <c r="P10">
-        <v>-1.1536177755304129E-4</v>
+        <v>-2.8747906287254852E-4</v>
       </c>
       <c r="Q10">
-        <v>3.5844201006782444E-5</v>
+        <v>9.0597709211005014E-5</v>
       </c>
       <c r="R10">
-        <v>-1.6006459339084836E-4</v>
+        <v>-2.3754011413917663E-4</v>
       </c>
       <c r="S10">
-        <v>-9.8557574322383256E-5</v>
+        <v>-2.7085002533855569E-4</v>
       </c>
       <c r="T10">
-        <v>-5.7193411811561637E-5</v>
+        <v>-2.5488250911355438E-5</v>
       </c>
       <c r="U10">
-        <v>-2.7086077731052881E-5</v>
+        <v>-6.7724740632105684E-5</v>
       </c>
       <c r="V10">
-        <v>2.4730471848987551E-5</v>
+        <v>1.270440266677072E-4</v>
       </c>
       <c r="W10">
-        <v>1.8731504269444332E-4</v>
+        <v>-2.4072347394485296E-4</v>
       </c>
       <c r="X10">
-        <v>-4.0606137750241018E-4</v>
+        <v>1.0041377358829763E-4</v>
       </c>
       <c r="Y10">
-        <v>-1.800926872857567E-5</v>
+        <v>-1.3580965001416031E-5</v>
       </c>
       <c r="Z10">
-        <v>3.464963209568535E-6</v>
+        <v>1.9541102074537324E-4</v>
       </c>
       <c r="AA10">
-        <v>-4.3502193654356146E-5</v>
+        <v>-6.9441542209894985E-5</v>
       </c>
       <c r="AB10">
-        <v>5.5214484269356973E-6</v>
+        <v>-1.7531601378694773E-5</v>
       </c>
       <c r="AC10">
-        <v>1.3798068443338866E-4</v>
+        <v>1.7858657583539207E-6</v>
       </c>
       <c r="AD10">
-        <v>1.6042587488563406E-4</v>
+        <v>-5.8389396325273543E-5</v>
       </c>
       <c r="AE10">
-        <v>1.4390576215908237E-4</v>
+        <v>8.8222964537976178E-5</v>
       </c>
       <c r="AF10">
-        <v>-7.0144060457698106E-3</v>
+        <v>1.3190545015576453E-4</v>
+      </c>
+      <c r="AG10">
+        <v>-3.8258627026767095E-5</v>
+      </c>
+      <c r="AH10">
+        <v>1.5296807243682636E-5</v>
+      </c>
+      <c r="AI10">
+        <v>-3.2175113224578757E-5</v>
+      </c>
+      <c r="AJ10">
+        <v>1.6763358653464934E-4</v>
+      </c>
+      <c r="AK10">
+        <v>-1.4550526727856884E-4</v>
+      </c>
+      <c r="AL10">
+        <v>-1.5534491934933968E-5</v>
+      </c>
+      <c r="AM10">
+        <v>1.3323231265487036E-4</v>
+      </c>
+      <c r="AN10">
+        <v>-1.8202646069953761E-5</v>
+      </c>
+      <c r="AO10">
+        <v>-3.1383857833337803E-4</v>
+      </c>
+      <c r="AP10">
+        <v>-1.2429016341074498E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>22</v>
       </c>
       <c r="B11">
-        <v>-0.25718639477129263</v>
+        <v>-0.30457298559866613</v>
       </c>
       <c r="C11">
-        <v>1.4362906355992955E-4</v>
+        <v>-4.4275838381619857E-5</v>
       </c>
       <c r="D11">
-        <v>2.5996012241122335E-4</v>
+        <v>6.0399023573341759E-4</v>
       </c>
       <c r="E11">
-        <v>-4.4428458269934562E-6</v>
+        <v>-1.0176081865245247E-5</v>
       </c>
       <c r="F11">
-        <v>-2.2933061411999881E-4</v>
+        <v>-5.4121750353762184E-4</v>
       </c>
       <c r="G11">
-        <v>-3.83540622167001E-6</v>
+        <v>1.7770964507714433E-5</v>
       </c>
       <c r="H11">
-        <v>2.2437071098977649E-4</v>
+        <v>6.1700225140653769E-4</v>
       </c>
       <c r="I11">
-        <v>1.7204766728795579E-3</v>
+        <v>3.4016907303035544E-3</v>
       </c>
       <c r="J11">
-        <v>2.1371410208063917E-3</v>
+        <v>3.0037640840158827E-3</v>
       </c>
       <c r="K11">
-        <v>2.2253028858731779E-3</v>
+        <v>3.1346754598403671E-3</v>
       </c>
       <c r="L11">
-        <v>3.6021100246888395E-3</v>
+        <v>4.6444423653974765E-3</v>
       </c>
       <c r="M11">
-        <v>2.6912521058714391E-3</v>
+        <v>3.5323166397745985E-3</v>
       </c>
       <c r="N11">
-        <v>2.2895887241131977E-3</v>
+        <v>2.9169730998016368E-3</v>
       </c>
       <c r="O11">
-        <v>2.7184390920743061E-4</v>
+        <v>1.8989818611982135E-4</v>
       </c>
       <c r="P11">
-        <v>-1.0510373909602055E-4</v>
+        <v>-2.4745435335628676E-4</v>
       </c>
       <c r="Q11">
-        <v>-6.1530464232545162E-5</v>
+        <v>-4.9838079133757021E-6</v>
       </c>
       <c r="R11">
-        <v>-2.3052912983246096E-4</v>
+        <v>-2.4804126477982654E-4</v>
       </c>
       <c r="S11">
-        <v>-1.8109991435215453E-4</v>
+        <v>-2.1558244093333755E-4</v>
       </c>
       <c r="T11">
-        <v>-2.835031747376658E-5</v>
+        <v>-1.2127932115484378E-4</v>
       </c>
       <c r="U11">
-        <v>-9.7199705675142089E-5</v>
+        <v>-1.8060969912904326E-4</v>
       </c>
       <c r="V11">
-        <v>-1.5281774963111258E-4</v>
+        <v>-4.0953933097034791E-5</v>
       </c>
       <c r="W11">
-        <v>1.1558556674471439E-5</v>
+        <v>-1.3910515004404559E-4</v>
       </c>
       <c r="X11">
-        <v>-6.6425046641433848E-4</v>
+        <v>-3.8047684327997496E-4</v>
       </c>
       <c r="Y11">
-        <v>-6.404096945532723E-5</v>
+        <v>-5.1337837126167254E-5</v>
       </c>
       <c r="Z11">
-        <v>1.5471141574857281E-6</v>
+        <v>2.8519470912943996E-4</v>
       </c>
       <c r="AA11">
-        <v>9.4938867879374274E-5</v>
+        <v>-3.2260230766959549E-4</v>
       </c>
       <c r="AB11">
-        <v>6.7860537026259119E-5</v>
+        <v>7.4233047102914714E-5</v>
       </c>
       <c r="AC11">
-        <v>2.8999327648147801E-4</v>
+        <v>3.860255248659206E-5</v>
       </c>
       <c r="AD11">
-        <v>4.1427333061940137E-5</v>
+        <v>7.6833970969237306E-5</v>
       </c>
       <c r="AE11">
-        <v>1.4636320971836723E-4</v>
+        <v>1.5457398178008439E-4</v>
       </c>
       <c r="AF11">
-        <v>-6.4809373635966987E-3</v>
+        <v>1.5001854905039589E-4</v>
+      </c>
+      <c r="AG11">
+        <v>3.1563677486416437E-5</v>
+      </c>
+      <c r="AH11">
+        <v>4.2685896266316144E-5</v>
+      </c>
+      <c r="AI11">
+        <v>-1.259806917185656E-5</v>
+      </c>
+      <c r="AJ11">
+        <v>-8.4165941093897884E-5</v>
+      </c>
+      <c r="AK11">
+        <v>-1.6535094387331358E-4</v>
+      </c>
+      <c r="AL11">
+        <v>1.1756830425562609E-4</v>
+      </c>
+      <c r="AM11">
+        <v>-7.0886701697830089E-5</v>
+      </c>
+      <c r="AN11">
+        <v>-8.5091522172746695E-5</v>
+      </c>
+      <c r="AO11">
+        <v>-2.138436910267133E-6</v>
+      </c>
+      <c r="AP11">
+        <v>-1.227583196286604E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>23</v>
       </c>
       <c r="B12">
-        <v>-0.10169372408723946</v>
+        <v>-0.16166360182913134</v>
       </c>
       <c r="C12">
-        <v>1.4969478050918337E-4</v>
+        <v>-2.9617050084873746E-5</v>
       </c>
       <c r="D12">
-        <v>2.5911096908810122E-4</v>
+        <v>5.9540372223328001E-4</v>
       </c>
       <c r="E12">
-        <v>-4.9496581091379433E-6</v>
+        <v>-1.0540649356896324E-5</v>
       </c>
       <c r="F12">
-        <v>-3.269752371923122E-5</v>
+        <v>-3.859299226464798E-4</v>
       </c>
       <c r="G12">
-        <v>2.7833817273945836E-4</v>
+        <v>2.3712215162435173E-4</v>
       </c>
       <c r="H12">
-        <v>5.3156924897645574E-4</v>
+        <v>8.8176773985379204E-4</v>
       </c>
       <c r="I12">
-        <v>1.6070944659217674E-3</v>
+        <v>3.1271906930517529E-3</v>
       </c>
       <c r="J12">
-        <v>2.1281368582487538E-3</v>
+        <v>2.8108475336687082E-3</v>
       </c>
       <c r="K12">
-        <v>2.1801257428236578E-3</v>
+        <v>2.9542396101599265E-3</v>
       </c>
       <c r="L12">
-        <v>2.6912521058714391E-3</v>
+        <v>3.5323166397745985E-3</v>
       </c>
       <c r="M12">
-        <v>3.7950636466547462E-3</v>
+        <v>4.4384046359513055E-3</v>
       </c>
       <c r="N12">
-        <v>2.3604506758853226E-3</v>
+        <v>2.8108859983039833E-3</v>
       </c>
       <c r="O12">
-        <v>4.6097849759680959E-5</v>
+        <v>-9.2196655361993091E-5</v>
       </c>
       <c r="P12">
-        <v>2.7978522933678595E-4</v>
+        <v>1.6469036248606319E-4</v>
       </c>
       <c r="Q12">
-        <v>2.6427746861688438E-4</v>
+        <v>3.5789650164082352E-4</v>
       </c>
       <c r="R12">
-        <v>-8.1134669808167033E-5</v>
+        <v>-9.5610154566706318E-5</v>
       </c>
       <c r="S12">
-        <v>-4.5634837406131109E-5</v>
+        <v>-1.3795749379832381E-4</v>
       </c>
       <c r="T12">
-        <v>1.4013586579809332E-5</v>
+        <v>-6.6608996220079097E-5</v>
       </c>
       <c r="U12">
-        <v>2.9747401395108849E-4</v>
+        <v>2.0067831477274989E-4</v>
       </c>
       <c r="V12">
-        <v>-2.7753711846173739E-5</v>
+        <v>9.3375615364991093E-5</v>
       </c>
       <c r="W12">
-        <v>2.9856021505670624E-4</v>
+        <v>1.995753768051574E-4</v>
       </c>
       <c r="X12">
-        <v>-4.2062670227277136E-4</v>
+        <v>-1.437839419822109E-4</v>
       </c>
       <c r="Y12">
-        <v>1.4844073235358891E-4</v>
+        <v>1.9773047327624905E-4</v>
       </c>
       <c r="Z12">
-        <v>1.9843368338410845E-5</v>
+        <v>3.5584913574248029E-4</v>
       </c>
       <c r="AA12">
-        <v>-1.421721672999253E-5</v>
+        <v>9.2592718334757323E-4</v>
       </c>
       <c r="AB12">
-        <v>-1.9797213126812043E-5</v>
+        <v>2.8460218057013405E-4</v>
       </c>
       <c r="AC12">
-        <v>3.0147059722249658E-4</v>
+        <v>7.6415206701586978E-5</v>
       </c>
       <c r="AD12">
-        <v>1.082859674476654E-3</v>
+        <v>6.7395160468889195E-5</v>
       </c>
       <c r="AE12">
-        <v>3.3483355004522593E-4</v>
+        <v>2.4916420691754437E-4</v>
       </c>
       <c r="AF12">
-        <v>-6.8969492390412186E-3</v>
+        <v>2.0779822521699537E-4</v>
+      </c>
+      <c r="AG12">
+        <v>8.8427619594778559E-5</v>
+      </c>
+      <c r="AH12">
+        <v>9.8256598358846536E-5</v>
+      </c>
+      <c r="AI12">
+        <v>2.0744591881098444E-5</v>
+      </c>
+      <c r="AJ12">
+        <v>-2.064096736118827E-5</v>
+      </c>
+      <c r="AK12">
+        <v>-8.8043006408054098E-5</v>
+      </c>
+      <c r="AL12">
+        <v>1.9737493857880338E-4</v>
+      </c>
+      <c r="AM12">
+        <v>-2.7130259746770396E-4</v>
+      </c>
+      <c r="AN12">
+        <v>-4.7014219085509019E-5</v>
+      </c>
+      <c r="AO12">
+        <v>8.0999524739723203E-4</v>
+      </c>
+      <c r="AP12">
+        <v>-1.2135560927561734E-2</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>24</v>
       </c>
       <c r="B13">
-        <v>-4.2375228765302218E-2</v>
+        <v>-7.0866672213248674E-2</v>
       </c>
       <c r="C13">
-        <v>1.9635896086423577E-5</v>
+        <v>-8.406784863992055E-5</v>
       </c>
       <c r="D13">
-        <v>5.0582283882276489E-4</v>
+        <v>8.0011656375668155E-4</v>
       </c>
       <c r="E13">
-        <v>-9.3088091981656037E-6</v>
+        <v>-1.42890125614471E-5</v>
       </c>
       <c r="F13">
-        <v>-7.8204176065001674E-5</v>
+        <v>-3.6637403028690887E-4</v>
       </c>
       <c r="G13">
-        <v>3.5678371335411997E-4</v>
+        <v>3.2935369073708179E-4</v>
       </c>
       <c r="H13">
-        <v>6.7200452711455071E-4</v>
+        <v>1.0303938087590943E-3</v>
       </c>
       <c r="I13">
-        <v>1.3044449891990305E-3</v>
+        <v>2.5517254987284595E-3</v>
       </c>
       <c r="J13">
-        <v>1.6227764023620072E-3</v>
+        <v>2.1636501786146938E-3</v>
       </c>
       <c r="K13">
-        <v>1.969635132958844E-3</v>
+        <v>2.5365184959194086E-3</v>
       </c>
       <c r="L13">
-        <v>2.2895887241131977E-3</v>
+        <v>2.9169730998016368E-3</v>
       </c>
       <c r="M13">
-        <v>2.3604506758853226E-3</v>
+        <v>2.8108859983039833E-3</v>
       </c>
       <c r="N13">
-        <v>4.730495849823867E-3</v>
+        <v>4.9767491835600395E-3</v>
       </c>
       <c r="O13">
-        <v>2.2693943006640046E-4</v>
+        <v>1.2542114861689149E-4</v>
       </c>
       <c r="P13">
-        <v>2.3094079260865558E-4</v>
+        <v>1.5256273494738178E-4</v>
       </c>
       <c r="Q13">
-        <v>2.2290811828302033E-4</v>
+        <v>3.5090348575121601E-4</v>
       </c>
       <c r="R13">
-        <v>-9.6690640576072354E-5</v>
+        <v>-5.8352188495363483E-5</v>
       </c>
       <c r="S13">
-        <v>1.010828698106152E-5</v>
+        <v>1.2437595698256039E-6</v>
       </c>
       <c r="T13">
-        <v>1.7962528989545279E-4</v>
+        <v>2.6929653282534854E-4</v>
       </c>
       <c r="U13">
-        <v>9.8729803759006925E-5</v>
+        <v>5.6539762962540784E-5</v>
       </c>
       <c r="V13">
-        <v>-2.2595430780857962E-5</v>
+        <v>1.5165314124169224E-4</v>
       </c>
       <c r="W13">
-        <v>2.5770867538976066E-4</v>
+        <v>1.9098881914078017E-4</v>
       </c>
       <c r="X13">
-        <v>-4.5250298042239689E-4</v>
+        <v>-1.2307390190378675E-4</v>
       </c>
       <c r="Y13">
-        <v>1.3714088259977886E-4</v>
+        <v>2.0223714684205769E-4</v>
       </c>
       <c r="Z13">
-        <v>-1.3915280044423067E-5</v>
+        <v>8.2745024440187241E-5</v>
       </c>
       <c r="AA13">
-        <v>-2.4702454943775396E-5</v>
+        <v>-1.8371514161033033E-4</v>
       </c>
       <c r="AB13">
-        <v>9.1966178694389005E-5</v>
+        <v>1.0618924550838003E-4</v>
       </c>
       <c r="AC13">
-        <v>1.1749946571311745E-4</v>
+        <v>3.1046720655801378E-6</v>
       </c>
       <c r="AD13">
-        <v>5.7524318997224499E-4</v>
+        <v>7.5862598318748604E-5</v>
       </c>
       <c r="AE13">
-        <v>1.2756104613542886E-4</v>
+        <v>1.9107427119520806E-4</v>
       </c>
       <c r="AF13">
-        <v>-9.1896095843771019E-3</v>
+        <v>1.7188203949332955E-4</v>
+      </c>
+      <c r="AG13">
+        <v>2.2553842389188596E-5</v>
+      </c>
+      <c r="AH13">
+        <v>6.4287552542194835E-5</v>
+      </c>
+      <c r="AI13">
+        <v>1.5310477926092081E-6</v>
+      </c>
+      <c r="AJ13">
+        <v>-6.960616684839778E-5</v>
+      </c>
+      <c r="AK13">
+        <v>-2.9315875440666037E-4</v>
+      </c>
+      <c r="AL13">
+        <v>5.2927891228261685E-5</v>
+      </c>
+      <c r="AM13">
+        <v>-2.6580397456910099E-4</v>
+      </c>
+      <c r="AN13">
+        <v>-1.1245674836937811E-4</v>
+      </c>
+      <c r="AO13">
+        <v>-4.18941376147626E-4</v>
+      </c>
+      <c r="AP13">
+        <v>-1.4122897017889163E-2</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>25</v>
       </c>
       <c r="B14">
-        <v>-6.7537800332445774E-2</v>
+        <v>-5.84804932006667E-2</v>
       </c>
       <c r="C14">
-        <v>-1.5529268109889887E-4</v>
+        <v>-1.9572763911258748E-4</v>
       </c>
       <c r="D14">
-        <v>2.8027296158254214E-4</v>
+        <v>3.4786848931778278E-4</v>
       </c>
       <c r="E14">
-        <v>-5.1601543477111712E-6</v>
+        <v>-6.3447370974616251E-6</v>
       </c>
       <c r="F14">
-        <v>1.968024775126202E-4</v>
+        <v>1.6800494291322691E-4</v>
       </c>
       <c r="G14">
-        <v>4.3582471197963998E-4</v>
+        <v>4.5994261950243814E-4</v>
       </c>
       <c r="H14">
-        <v>5.334708496636492E-4</v>
+        <v>4.8118847374349031E-4</v>
       </c>
       <c r="I14">
-        <v>-1.7272541229972885E-4</v>
+        <v>-1.2161124602095338E-4</v>
       </c>
       <c r="J14">
-        <v>-3.6426511240648257E-4</v>
+        <v>-4.276768403060475E-4</v>
       </c>
       <c r="K14">
-        <v>2.3397990037411971E-4</v>
+        <v>1.2610376826330933E-4</v>
       </c>
       <c r="L14">
-        <v>2.7184390920743061E-4</v>
+        <v>1.8989818611982135E-4</v>
       </c>
       <c r="M14">
-        <v>4.6097849759680959E-5</v>
+        <v>-9.2196655361993091E-5</v>
       </c>
       <c r="N14">
-        <v>2.2693943006640046E-4</v>
+        <v>1.2542114861689149E-4</v>
       </c>
       <c r="O14">
-        <v>9.9610437127468244E-3</v>
+        <v>1.0098320584709863E-2</v>
       </c>
       <c r="P14">
-        <v>2.5437999938117558E-3</v>
+        <v>2.475440394750852E-3</v>
       </c>
       <c r="Q14">
-        <v>2.6002442177631563E-3</v>
+        <v>2.6210658175517625E-3</v>
       </c>
       <c r="R14">
-        <v>2.60250501900108E-3</v>
+        <v>2.5999574124228948E-3</v>
       </c>
       <c r="S14">
-        <v>2.4446326628455506E-3</v>
+        <v>2.4194329923345713E-3</v>
       </c>
       <c r="T14">
-        <v>2.558143057209685E-3</v>
+        <v>2.5548191203801874E-3</v>
       </c>
       <c r="U14">
-        <v>2.960361236013973E-3</v>
+        <v>2.9888985661968913E-3</v>
       </c>
       <c r="V14">
-        <v>2.690620687459002E-3</v>
+        <v>2.699874551112519E-3</v>
       </c>
       <c r="W14">
-        <v>2.6931009418376438E-3</v>
+        <v>2.6999741795281861E-3</v>
       </c>
       <c r="X14">
-        <v>2.67150611730109E-3</v>
+        <v>2.6655404841802381E-3</v>
       </c>
       <c r="Y14">
-        <v>2.7021111428959009E-3</v>
+        <v>2.7717043433295252E-3</v>
       </c>
       <c r="Z14">
-        <v>5.166515283836447E-5</v>
+        <v>9.464773918418601E-4</v>
       </c>
       <c r="AA14">
-        <v>-3.5445431679852196E-4</v>
+        <v>4.0801005309275412E-3</v>
       </c>
       <c r="AB14">
-        <v>-3.5236329918160328E-4</v>
+        <v>6.8225948247787249E-4</v>
       </c>
       <c r="AC14">
-        <v>8.836250317549463E-4</v>
+        <v>3.6383399894679389E-5</v>
       </c>
       <c r="AD14">
-        <v>4.0826869466348507E-3</v>
+        <v>-1.0350351886452737E-5</v>
       </c>
       <c r="AE14">
-        <v>6.9708163366788954E-4</v>
+        <v>-5.5908665382212592E-5</v>
       </c>
       <c r="AF14">
-        <v>-7.5071007540232692E-3</v>
+        <v>1.0982039910966931E-5</v>
+      </c>
+      <c r="AG14">
+        <v>5.7407714437415357E-5</v>
+      </c>
+      <c r="AH14">
+        <v>-1.2616885342125366E-5</v>
+      </c>
+      <c r="AI14">
+        <v>3.0369908489851719E-4</v>
+      </c>
+      <c r="AJ14">
+        <v>2.1505759542186746E-4</v>
+      </c>
+      <c r="AK14">
+        <v>-6.4940322376040452E-5</v>
+      </c>
+      <c r="AL14">
+        <v>-3.4097706900666769E-6</v>
+      </c>
+      <c r="AM14">
+        <v>-1.6657577601283252E-4</v>
+      </c>
+      <c r="AN14">
+        <v>-3.1483677810228853E-5</v>
+      </c>
+      <c r="AO14">
+        <v>1.8906649392489445E-3</v>
+      </c>
+      <c r="AP14">
+        <v>-7.5941362888467812E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>26</v>
       </c>
       <c r="B15">
-        <v>0.16833671737694358</v>
+        <v>0.17957633380331728</v>
       </c>
       <c r="C15">
-        <v>1.6340289846084841E-4</v>
+        <v>1.5980925330027053E-4</v>
       </c>
       <c r="D15">
-        <v>2.320916846641442E-4</v>
+        <v>2.8884004910859941E-4</v>
       </c>
       <c r="E15">
-        <v>-4.7744167412468636E-6</v>
+        <v>-5.861031852039998E-6</v>
       </c>
       <c r="F15">
-        <v>3.9191593996575503E-5</v>
+        <v>8.9285974995166779E-5</v>
       </c>
       <c r="G15">
-        <v>3.8665993380054137E-4</v>
+        <v>4.1301142227544553E-4</v>
       </c>
       <c r="H15">
-        <v>3.1577125179988027E-4</v>
+        <v>3.0191083619731393E-4</v>
       </c>
       <c r="I15">
-        <v>1.9204317599709649E-6</v>
+        <v>-9.4836699514650249E-5</v>
       </c>
       <c r="J15">
-        <v>-1.0649904882898721E-4</v>
+        <v>-1.840075526855613E-4</v>
       </c>
       <c r="K15">
-        <v>-1.1536177755304129E-4</v>
+        <v>-2.8747906287254852E-4</v>
       </c>
       <c r="L15">
-        <v>-1.0510373909602055E-4</v>
+        <v>-2.4745435335628676E-4</v>
       </c>
       <c r="M15">
-        <v>2.7978522933678595E-4</v>
+        <v>1.6469036248606319E-4</v>
       </c>
       <c r="N15">
-        <v>2.3094079260865558E-4</v>
+        <v>1.5256273494738178E-4</v>
       </c>
       <c r="O15">
-        <v>2.5437999938117558E-3</v>
+        <v>2.475440394750852E-3</v>
       </c>
       <c r="P15">
-        <v>4.9429388639092246E-3</v>
+        <v>4.9020636302678205E-3</v>
       </c>
       <c r="Q15">
-        <v>2.5442544348095392E-3</v>
+        <v>2.5620964088732675E-3</v>
       </c>
       <c r="R15">
-        <v>2.5533095278191904E-3</v>
+        <v>2.5513489927050325E-3</v>
       </c>
       <c r="S15">
-        <v>2.4370313183131958E-3</v>
+        <v>2.4172422196755109E-3</v>
       </c>
       <c r="T15">
-        <v>2.5024206466494271E-3</v>
+        <v>2.4980214341467559E-3</v>
       </c>
       <c r="U15">
-        <v>2.8361268935977258E-3</v>
+        <v>2.8481363968684186E-3</v>
       </c>
       <c r="V15">
-        <v>2.593167226664353E-3</v>
+        <v>2.5939712572031854E-3</v>
       </c>
       <c r="W15">
-        <v>2.6686997482110726E-3</v>
+        <v>2.6636027760937936E-3</v>
       </c>
       <c r="X15">
-        <v>2.6117987398632673E-3</v>
+        <v>2.6058610490000862E-3</v>
       </c>
       <c r="Y15">
-        <v>2.6257306852547737E-3</v>
+        <v>2.6788798706361191E-3</v>
       </c>
       <c r="Z15">
-        <v>6.2053314703571861E-5</v>
+        <v>6.5252130916728832E-4</v>
       </c>
       <c r="AA15">
-        <v>-4.013320078186444E-4</v>
+        <v>3.6480077635146942E-3</v>
       </c>
       <c r="AB15">
-        <v>-1.9171875709240831E-4</v>
+        <v>3.7381468572869928E-4</v>
       </c>
       <c r="AC15">
-        <v>6.2520699498085975E-4</v>
+        <v>3.8401810266868195E-5</v>
       </c>
       <c r="AD15">
-        <v>3.7233483070655462E-3</v>
+        <v>1.796077361887569E-5</v>
       </c>
       <c r="AE15">
-        <v>4.2949958651375013E-4</v>
+        <v>-3.0957818563876805E-6</v>
       </c>
       <c r="AF15">
-        <v>-6.7386493439850507E-3</v>
+        <v>-3.2746874619239393E-5</v>
+      </c>
+      <c r="AG15">
+        <v>1.5888366228743612E-4</v>
+      </c>
+      <c r="AH15">
+        <v>1.6095695695878464E-4</v>
+      </c>
+      <c r="AI15">
+        <v>1.624958308977804E-4</v>
+      </c>
+      <c r="AJ15">
+        <v>5.867348019234029E-5</v>
+      </c>
+      <c r="AK15">
+        <v>-5.3963370825540168E-5</v>
+      </c>
+      <c r="AL15">
+        <v>2.4130729278264065E-4</v>
+      </c>
+      <c r="AM15">
+        <v>8.4483162783728985E-5</v>
+      </c>
+      <c r="AN15">
+        <v>1.3479951180683466E-4</v>
+      </c>
+      <c r="AO15">
+        <v>1.9807767901645641E-3</v>
+      </c>
+      <c r="AP15">
+        <v>-6.474054926744922E-3</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>27</v>
       </c>
       <c r="B16">
-        <v>0.16129324501572315</v>
+        <v>0.16392685210545144</v>
       </c>
       <c r="C16">
-        <v>2.1289421178969284E-5</v>
+        <v>-7.8817826446984132E-6</v>
       </c>
       <c r="D16">
-        <v>3.3612945322286322E-4</v>
+        <v>3.8809193031468891E-4</v>
       </c>
       <c r="E16">
-        <v>-6.4722889666835487E-6</v>
+        <v>-7.4401517611559254E-6</v>
       </c>
       <c r="F16">
-        <v>1.2229678380336058E-4</v>
+        <v>1.4543060339891048E-4</v>
       </c>
       <c r="G16">
-        <v>2.2576525796526222E-4</v>
+        <v>2.6337782792521409E-4</v>
       </c>
       <c r="H16">
-        <v>2.7781265807227457E-4</v>
+        <v>3.8841340353002412E-4</v>
       </c>
       <c r="I16">
-        <v>4.1342716082856136E-5</v>
+        <v>1.2048877062741353E-4</v>
       </c>
       <c r="J16">
-        <v>2.3529619841122708E-5</v>
+        <v>9.3469866740401018E-5</v>
       </c>
       <c r="K16">
-        <v>3.5844201006782444E-5</v>
+        <v>9.0597709211005014E-5</v>
       </c>
       <c r="L16">
-        <v>-6.1530464232545162E-5</v>
+        <v>-4.9838079133757021E-6</v>
       </c>
       <c r="M16">
-        <v>2.6427746861688438E-4</v>
+        <v>3.5789650164082352E-4</v>
       </c>
       <c r="N16">
-        <v>2.2290811828302033E-4</v>
+        <v>3.5090348575121601E-4</v>
       </c>
       <c r="O16">
-        <v>2.6002442177631563E-3</v>
+        <v>2.6210658175517625E-3</v>
       </c>
       <c r="P16">
-        <v>2.5442544348095392E-3</v>
+        <v>2.5620964088732675E-3</v>
       </c>
       <c r="Q16">
-        <v>5.0372129387980741E-3</v>
+        <v>5.1175200821101923E-3</v>
       </c>
       <c r="R16">
-        <v>2.6001298384376701E-3</v>
+        <v>2.64114682326743E-3</v>
       </c>
       <c r="S16">
-        <v>2.4693490410888789E-3</v>
+        <v>2.4931512452897892E-3</v>
       </c>
       <c r="T16">
-        <v>2.5600242323224722E-3</v>
+        <v>2.6042446505563088E-3</v>
       </c>
       <c r="U16">
-        <v>2.8879344376244007E-3</v>
+        <v>2.9648150834426889E-3</v>
       </c>
       <c r="V16">
-        <v>2.673763104855714E-3</v>
+        <v>2.7135908303054608E-3</v>
       </c>
       <c r="W16">
-        <v>2.7009555285118763E-3</v>
+        <v>2.7496790287707051E-3</v>
       </c>
       <c r="X16">
-        <v>2.6875183056754483E-3</v>
+        <v>2.7310739415100714E-3</v>
       </c>
       <c r="Y16">
-        <v>2.6317172248474779E-3</v>
+        <v>2.6785300310321679E-3</v>
       </c>
       <c r="Z16">
-        <v>2.2938560151833246E-5</v>
+        <v>8.5185315207795436E-4</v>
       </c>
       <c r="AA16">
-        <v>-2.454278741564549E-4</v>
+        <v>3.899620661009066E-3</v>
       </c>
       <c r="AB16">
-        <v>1.9687079064206801E-4</v>
+        <v>6.5069366495756203E-4</v>
       </c>
       <c r="AC16">
-        <v>7.9523786611517303E-4</v>
+        <v>4.7132749667803172E-5</v>
       </c>
       <c r="AD16">
-        <v>3.7674862622241877E-3</v>
+        <v>4.3185787827978149E-5</v>
       </c>
       <c r="AE16">
-        <v>6.705768760565373E-4</v>
+        <v>1.3595470718979021E-5</v>
       </c>
       <c r="AF16">
-        <v>-7.5447656928781604E-3</v>
+        <v>-3.0583766077687115E-5</v>
+      </c>
+      <c r="AG16">
+        <v>8.7438116574985354E-5</v>
+      </c>
+      <c r="AH16">
+        <v>9.9632230893494751E-5</v>
+      </c>
+      <c r="AI16">
+        <v>7.6933662023978338E-5</v>
+      </c>
+      <c r="AJ16">
+        <v>3.9460230495682669E-4</v>
+      </c>
+      <c r="AK16">
+        <v>-7.4057170780641134E-5</v>
+      </c>
+      <c r="AL16">
+        <v>4.014360613573552E-4</v>
+      </c>
+      <c r="AM16">
+        <v>-5.0510647529924783E-5</v>
+      </c>
+      <c r="AN16">
+        <v>1.6353820279961908E-4</v>
+      </c>
+      <c r="AO16">
+        <v>6.0398932375780277E-4</v>
+      </c>
+      <c r="AP16">
+        <v>-8.0770417159786098E-3</v>
       </c>
     </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>28</v>
       </c>
       <c r="B17">
-        <v>6.8939149905630021E-2</v>
+        <v>7.4173286283390802E-2</v>
       </c>
       <c r="C17">
-        <v>6.4434250311572973E-6</v>
+        <v>-5.9965109671731291E-6</v>
       </c>
       <c r="D17">
-        <v>2.5331675022573767E-4</v>
+        <v>2.984059307919721E-4</v>
       </c>
       <c r="E17">
-        <v>-4.8878282369641678E-6</v>
+        <v>-5.7475404668365057E-6</v>
       </c>
       <c r="F17">
-        <v>1.8200220245876344E-4</v>
+        <v>2.3263863128959307E-4</v>
       </c>
       <c r="G17">
-        <v>1.9830865385825916E-4</v>
+        <v>2.2231123827409541E-4</v>
       </c>
       <c r="H17">
-        <v>2.3920822292268474E-4</v>
+        <v>2.6398467343196171E-4</v>
       </c>
       <c r="I17">
-        <v>-6.491178353127151E-7</v>
+        <v>-6.099036628503553E-5</v>
       </c>
       <c r="J17">
-        <v>-1.9777414909828397E-4</v>
+        <v>-2.1878240517719821E-4</v>
       </c>
       <c r="K17">
-        <v>-1.6006459339084836E-4</v>
+        <v>-2.3754011413917663E-4</v>
       </c>
       <c r="L17">
-        <v>-2.3052912983246096E-4</v>
+        <v>-2.4804126477982654E-4</v>
       </c>
       <c r="M17">
-        <v>-8.1134669808167033E-5</v>
+        <v>-9.5610154566706318E-5</v>
       </c>
       <c r="N17">
-        <v>-9.6690640576072354E-5</v>
+        <v>-5.8352188495363483E-5</v>
       </c>
       <c r="O17">
-        <v>2.60250501900108E-3</v>
+        <v>2.5999574124228948E-3</v>
       </c>
       <c r="P17">
-        <v>2.5533095278191904E-3</v>
+        <v>2.5513489927050325E-3</v>
       </c>
       <c r="Q17">
-        <v>2.6001298384376701E-3</v>
+        <v>2.64114682326743E-3</v>
       </c>
       <c r="R17">
-        <v>5.1542562365659746E-3</v>
+        <v>5.1839718683793093E-3</v>
       </c>
       <c r="S17">
-        <v>2.4958350941403739E-3</v>
+        <v>2.5170528700671773E-3</v>
       </c>
       <c r="T17">
-        <v>2.5833035732770104E-3</v>
+        <v>2.6147118051993443E-3</v>
       </c>
       <c r="U17">
-        <v>2.9336285746020319E-3</v>
+        <v>2.9928512081283621E-3</v>
       </c>
       <c r="V17">
-        <v>2.7028694385049855E-3</v>
+        <v>2.7369804167919291E-3</v>
       </c>
       <c r="W17">
-        <v>2.7133569256387463E-3</v>
+        <v>2.7633174487011313E-3</v>
       </c>
       <c r="X17">
-        <v>2.6828811327583913E-3</v>
+        <v>2.7182030396487649E-3</v>
       </c>
       <c r="Y17">
-        <v>2.6678274312721189E-3</v>
+        <v>2.7021672019574266E-3</v>
       </c>
       <c r="Z17">
-        <v>1.6382463128005733E-5</v>
+        <v>8.5023299658758972E-4</v>
       </c>
       <c r="AA17">
-        <v>-6.9571271212558503E-5</v>
+        <v>3.9379019639069045E-3</v>
       </c>
       <c r="AB17">
-        <v>-8.4003396433393032E-5</v>
+        <v>5.4858269430288313E-4</v>
       </c>
       <c r="AC17">
-        <v>7.9651402997497314E-4</v>
+        <v>5.1881788722194584E-5</v>
       </c>
       <c r="AD17">
-        <v>3.8274021701565058E-3</v>
+        <v>4.8457227515339698E-5</v>
       </c>
       <c r="AE17">
-        <v>5.647207535889677E-4</v>
+        <v>-1.6489966512436393E-5</v>
       </c>
       <c r="AF17">
-        <v>-6.1490466953348505E-3</v>
+        <v>-4.5143872800999536E-5</v>
+      </c>
+      <c r="AG17">
+        <v>6.4144129479145858E-5</v>
+      </c>
+      <c r="AH17">
+        <v>1.2751112905863798E-4</v>
+      </c>
+      <c r="AI17">
+        <v>2.1614045157685E-4</v>
+      </c>
+      <c r="AJ17">
+        <v>1.0637346683165807E-4</v>
+      </c>
+      <c r="AK17">
+        <v>5.6130672978440491E-5</v>
+      </c>
+      <c r="AL17">
+        <v>6.7617957688943624E-5</v>
+      </c>
+      <c r="AM17">
+        <v>1.3852603806465726E-5</v>
+      </c>
+      <c r="AN17">
+        <v>7.5757804317568792E-5</v>
+      </c>
+      <c r="AO17">
+        <v>4.4231807610293963E-4</v>
+      </c>
+      <c r="AP17">
+        <v>-6.5461510893532471E-3</v>
       </c>
     </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>29</v>
       </c>
       <c r="B18">
-        <v>4.894321766648832E-2</v>
+        <v>5.9951592838936731E-2</v>
       </c>
       <c r="C18">
-        <v>5.9646024902017735E-5</v>
+        <v>4.3065328651705516E-5</v>
       </c>
       <c r="D18">
-        <v>2.3121237053660266E-4</v>
+        <v>2.6612113875851577E-4</v>
       </c>
       <c r="E18">
-        <v>-4.601562683222023E-6</v>
+        <v>-5.2706840217776844E-6</v>
       </c>
       <c r="F18">
-        <v>-1.6945566355887082E-5</v>
+        <v>1.2368263278105278E-5</v>
       </c>
       <c r="G18">
-        <v>2.3841999109407435E-4</v>
+        <v>2.5209907698232588E-4</v>
       </c>
       <c r="H18">
-        <v>-7.3357989133670067E-5</v>
+        <v>-9.3110350593150412E-5</v>
       </c>
       <c r="I18">
-        <v>-8.6205647767372299E-5</v>
+        <v>-1.4910516011271439E-4</v>
       </c>
       <c r="J18">
-        <v>-6.2411402324679928E-5</v>
+        <v>-1.0197111397685483E-4</v>
       </c>
       <c r="K18">
-        <v>-9.8557574322383256E-5</v>
+        <v>-2.7085002533855569E-4</v>
       </c>
       <c r="L18">
-        <v>-1.8109991435215453E-4</v>
+        <v>-2.1558244093333755E-4</v>
       </c>
       <c r="M18">
-        <v>-4.5634837406131109E-5</v>
+        <v>-1.3795749379832381E-4</v>
       </c>
       <c r="N18">
-        <v>1.010828698106152E-5</v>
+        <v>1.2437595698256039E-6</v>
       </c>
       <c r="O18">
-        <v>2.4446326628455506E-3</v>
+        <v>2.4194329923345713E-3</v>
       </c>
       <c r="P18">
-        <v>2.4370313183131958E-3</v>
+        <v>2.4172422196755109E-3</v>
       </c>
       <c r="Q18">
-        <v>2.4693490410888789E-3</v>
+        <v>2.4931512452897892E-3</v>
       </c>
       <c r="R18">
-        <v>2.4958350941403739E-3</v>
+        <v>2.5170528700671773E-3</v>
       </c>
       <c r="S18">
-        <v>5.4338628043113834E-3</v>
+        <v>5.4556688119356163E-3</v>
       </c>
       <c r="T18">
-        <v>2.4593825306241206E-3</v>
+        <v>2.484338540387892E-3</v>
       </c>
       <c r="U18">
-        <v>2.7913310608169021E-3</v>
+        <v>2.8387394169739418E-3</v>
       </c>
       <c r="V18">
-        <v>2.5418104851318243E-3</v>
+        <v>2.561919449660866E-3</v>
       </c>
       <c r="W18">
-        <v>2.5735567501558631E-3</v>
+        <v>2.6151550468867571E-3</v>
       </c>
       <c r="X18">
-        <v>2.5372961990088537E-3</v>
+        <v>2.5578719783937182E-3</v>
       </c>
       <c r="Y18">
-        <v>2.5419697493696642E-3</v>
+        <v>2.5774336135951912E-3</v>
       </c>
       <c r="Z18">
-        <v>4.6911315654731803E-5</v>
+        <v>2.5593379697982466E-4</v>
       </c>
       <c r="AA18">
-        <v>-3.7060446292431072E-4</v>
+        <v>3.7506768743641762E-3</v>
       </c>
       <c r="AB18">
-        <v>-2.7033595762525993E-4</v>
+        <v>2.1419746983587554E-4</v>
       </c>
       <c r="AC18">
-        <v>2.2938060598892002E-4</v>
+        <v>2.4502872166657855E-5</v>
       </c>
       <c r="AD18">
-        <v>3.6968217157761557E-3</v>
+        <v>4.0783914542143776E-5</v>
       </c>
       <c r="AE18">
-        <v>2.3555444547826711E-4</v>
+        <v>1.7370945709111775E-5</v>
       </c>
       <c r="AF18">
-        <v>-6.1852708304634399E-3</v>
+        <v>-4.09725545687064E-5</v>
+      </c>
+      <c r="AG18">
+        <v>1.8535986158098989E-4</v>
+      </c>
+      <c r="AH18">
+        <v>8.3691610920700742E-5</v>
+      </c>
+      <c r="AI18">
+        <v>1.0224178545349704E-4</v>
+      </c>
+      <c r="AJ18">
+        <v>3.3526067415163554E-4</v>
+      </c>
+      <c r="AK18">
+        <v>-6.9398955693350008E-5</v>
+      </c>
+      <c r="AL18">
+        <v>9.5371269915595861E-5</v>
+      </c>
+      <c r="AM18">
+        <v>2.1248648945708924E-4</v>
+      </c>
+      <c r="AN18">
+        <v>4.0420432253620978E-4</v>
+      </c>
+      <c r="AO18">
+        <v>8.9499919287356917E-4</v>
+      </c>
+      <c r="AP18">
+        <v>-5.947665373213824E-3</v>
       </c>
     </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>30</v>
       </c>
       <c r="B19">
-        <v>1.7287555765509111E-2</v>
+        <v>2.5546802551051469E-2</v>
       </c>
       <c r="C19">
-        <v>-2.412411564488479E-5</v>
+        <v>-4.160425112065179E-5</v>
       </c>
       <c r="D19">
-        <v>2.9508295579747427E-4</v>
+        <v>3.3651281784985757E-4</v>
       </c>
       <c r="E19">
-        <v>-5.5307647907283899E-6</v>
+        <v>-6.3320781985083339E-6</v>
       </c>
       <c r="F19">
-        <v>-9.9921214716107627E-5</v>
+        <v>-5.2186343191129993E-5</v>
       </c>
       <c r="G19">
-        <v>1.5795015446461007E-4</v>
+        <v>1.8588758779373036E-4</v>
       </c>
       <c r="H19">
-        <v>-1.7090711527230655E-4</v>
+        <v>-1.5019922600451721E-4</v>
       </c>
       <c r="I19">
-        <v>2.4095064838562154E-4</v>
+        <v>1.5530730650522911E-4</v>
       </c>
       <c r="J19">
-        <v>1.3881636743120481E-4</v>
+        <v>8.7240043180704277E-5</v>
       </c>
       <c r="K19">
-        <v>-5.7193411811561637E-5</v>
+        <v>-2.5488250911355438E-5</v>
       </c>
       <c r="L19">
-        <v>-2.835031747376658E-5</v>
+        <v>-1.2127932115484378E-4</v>
       </c>
       <c r="M19">
-        <v>1.4013586579809332E-5</v>
+        <v>-6.6608996220079097E-5</v>
       </c>
       <c r="N19">
-        <v>1.7962528989545279E-4</v>
+        <v>2.6929653282534854E-4</v>
       </c>
       <c r="O19">
-        <v>2.558143057209685E-3</v>
+        <v>2.5548191203801874E-3</v>
       </c>
       <c r="P19">
-        <v>2.5024206466494271E-3</v>
+        <v>2.4980214341467559E-3</v>
       </c>
       <c r="Q19">
-        <v>2.5600242323224722E-3</v>
+        <v>2.6042446505563088E-3</v>
       </c>
       <c r="R19">
-        <v>2.5833035732770104E-3</v>
+        <v>2.6147118051993443E-3</v>
       </c>
       <c r="S19">
-        <v>2.4593825306241206E-3</v>
+        <v>2.484338540387892E-3</v>
       </c>
       <c r="T19">
-        <v>5.1257475673913569E-3</v>
+        <v>5.1605636538585757E-3</v>
       </c>
       <c r="U19">
-        <v>2.8636425830490457E-3</v>
+        <v>2.932751714747983E-3</v>
       </c>
       <c r="V19">
-        <v>2.6770660248227503E-3</v>
+        <v>2.7200193559688683E-3</v>
       </c>
       <c r="W19">
-        <v>2.6948403172487347E-3</v>
+        <v>2.7391782953354632E-3</v>
       </c>
       <c r="X19">
-        <v>2.6601865048624831E-3</v>
+        <v>2.7031581453199633E-3</v>
       </c>
       <c r="Y19">
-        <v>2.6431170489514795E-3</v>
+        <v>2.6917669764101293E-3</v>
       </c>
       <c r="Z19">
-        <v>1.3755972232894675E-5</v>
+        <v>8.7919636762020007E-4</v>
       </c>
       <c r="AA19">
-        <v>-6.1975807112222422E-5</v>
+        <v>3.5538676803986932E-3</v>
       </c>
       <c r="AB19">
-        <v>-1.9305222792210955E-6</v>
+        <v>4.6106910329600666E-4</v>
       </c>
       <c r="AC19">
-        <v>8.5193195049797937E-4</v>
+        <v>2.8426102905114052E-5</v>
       </c>
       <c r="AD19">
-        <v>3.4698126787947644E-3</v>
+        <v>-8.8277763434726239E-6</v>
       </c>
       <c r="AE19">
-        <v>4.6553896826760589E-4</v>
+        <v>3.8163882471270287E-5</v>
       </c>
       <c r="AF19">
-        <v>-6.833533655218561E-3</v>
+        <v>-7.049010263927727E-5</v>
+      </c>
+      <c r="AG19">
+        <v>1.733331154990731E-5</v>
+      </c>
+      <c r="AH19">
+        <v>-5.9298160870827022E-5</v>
+      </c>
+      <c r="AI19">
+        <v>1.9815304664909557E-4</v>
+      </c>
+      <c r="AJ19">
+        <v>7.6405101634254924E-5</v>
+      </c>
+      <c r="AK19">
+        <v>-1.078488017600002E-5</v>
+      </c>
+      <c r="AL19">
+        <v>1.0121783690703046E-4</v>
+      </c>
+      <c r="AM19">
+        <v>-1.0675186839905577E-4</v>
+      </c>
+      <c r="AN19">
+        <v>1.136351337243035E-4</v>
+      </c>
+      <c r="AO19">
+        <v>3.7944698820241429E-4</v>
+      </c>
+      <c r="AP19">
+        <v>-7.1529429852400118E-3</v>
       </c>
     </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>31</v>
       </c>
       <c r="B20">
-        <v>-3.5956456862079049E-3</v>
+        <v>-3.4245081456325436E-4</v>
       </c>
       <c r="C20">
-        <v>-5.8235237810183649E-5</v>
+        <v>-7.7336011912995051E-5</v>
       </c>
       <c r="D20">
-        <v>2.2676346763183175E-4</v>
+        <v>2.7941384014819153E-4</v>
       </c>
       <c r="E20">
-        <v>-4.4725187062759166E-6</v>
+        <v>-5.4638105352337708E-6</v>
       </c>
       <c r="F20">
-        <v>3.1591749473021142E-4</v>
+        <v>3.5976489490857307E-4</v>
       </c>
       <c r="G20">
-        <v>4.3242808590066419E-4</v>
+        <v>4.7103117547288189E-4</v>
       </c>
       <c r="H20">
-        <v>2.0925376461486931E-4</v>
+        <v>1.9470520323450831E-4</v>
       </c>
       <c r="I20">
-        <v>-1.1370387665397071E-4</v>
+        <v>-1.687749203797286E-4</v>
       </c>
       <c r="J20">
-        <v>3.4149069492930102E-5</v>
+        <v>-9.3191404206718724E-6</v>
       </c>
       <c r="K20">
-        <v>-2.7086077731052881E-5</v>
+        <v>-6.7724740632105684E-5</v>
       </c>
       <c r="L20">
-        <v>-9.7199705675142089E-5</v>
+        <v>-1.8060969912904326E-4</v>
       </c>
       <c r="M20">
-        <v>2.9747401395108849E-4</v>
+        <v>2.0067831477274989E-4</v>
       </c>
       <c r="N20">
-        <v>9.8729803759006925E-5</v>
+        <v>5.6539762962540784E-5</v>
       </c>
       <c r="O20">
-        <v>2.960361236013973E-3</v>
+        <v>2.9888985661968913E-3</v>
       </c>
       <c r="P20">
-        <v>2.8361268935977258E-3</v>
+        <v>2.8481363968684186E-3</v>
       </c>
       <c r="Q20">
-        <v>2.8879344376244007E-3</v>
+        <v>2.9648150834426889E-3</v>
       </c>
       <c r="R20">
-        <v>2.9336285746020319E-3</v>
+        <v>2.9928512081283621E-3</v>
       </c>
       <c r="S20">
-        <v>2.7913310608169021E-3</v>
+        <v>2.8387394169739418E-3</v>
       </c>
       <c r="T20">
-        <v>2.8636425830490457E-3</v>
+        <v>2.932751714747983E-3</v>
       </c>
       <c r="U20">
-        <v>5.2280089871464454E-3</v>
+        <v>5.3655563745153619E-3</v>
       </c>
       <c r="V20">
-        <v>3.0170099491313861E-3</v>
+        <v>3.0855966227140053E-3</v>
       </c>
       <c r="W20">
-        <v>3.0717484640609004E-3</v>
+        <v>3.1333032657373345E-3</v>
       </c>
       <c r="X20">
-        <v>3.0504256414284228E-3</v>
+        <v>3.0992083077400487E-3</v>
       </c>
       <c r="Y20">
-        <v>3.0431964473658854E-3</v>
+        <v>3.1483278195714565E-3</v>
       </c>
       <c r="Z20">
-        <v>4.138284363145898E-5</v>
+        <v>1.0547056929718968E-3</v>
       </c>
       <c r="AA20">
-        <v>-3.1448617303492916E-4</v>
+        <v>6.5457510085627623E-3</v>
       </c>
       <c r="AB20">
-        <v>-2.5650292090165911E-4</v>
+        <v>6.8731260979232377E-4</v>
       </c>
       <c r="AC20">
-        <v>9.9765743259814339E-4</v>
+        <v>9.6556733151582455E-5</v>
       </c>
       <c r="AD20">
-        <v>6.2194003388472557E-3</v>
+        <v>3.5404624202797959E-5</v>
       </c>
       <c r="AE20">
-        <v>6.9886718084717701E-4</v>
+        <v>-3.6528879631264448E-5</v>
       </c>
       <c r="AF20">
-        <v>-6.8252074618705685E-3</v>
+        <v>2.3026649255446707E-5</v>
+      </c>
+      <c r="AG20">
+        <v>1.6981086772963581E-4</v>
+      </c>
+      <c r="AH20">
+        <v>1.1883749501080871E-4</v>
+      </c>
+      <c r="AI20">
+        <v>1.6537411036645364E-4</v>
+      </c>
+      <c r="AJ20">
+        <v>8.2377089879363081E-5</v>
+      </c>
+      <c r="AK20">
+        <v>-3.6219508769482801E-5</v>
+      </c>
+      <c r="AL20">
+        <v>7.5382926559541038E-5</v>
+      </c>
+      <c r="AM20">
+        <v>2.1497535242427732E-5</v>
+      </c>
+      <c r="AN20">
+        <v>1.4277880949873961E-4</v>
+      </c>
+      <c r="AO20">
+        <v>1.3971079436535926E-3</v>
+      </c>
+      <c r="AP20">
+        <v>-6.9663188088251804E-3</v>
       </c>
     </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>32</v>
       </c>
       <c r="B21">
-        <v>0.18960538583431136</v>
+        <v>0.19576192855084637</v>
       </c>
       <c r="C21">
-        <v>3.8308562154541274E-5</v>
+        <v>3.0047282918194743E-5</v>
       </c>
       <c r="D21">
-        <v>2.8705440860610242E-4</v>
+        <v>3.3721121530420179E-4</v>
       </c>
       <c r="E21">
-        <v>-5.4622681237404913E-6</v>
+        <v>-6.3992496100736968E-6</v>
       </c>
       <c r="F21">
-        <v>-3.4902018928462055E-5</v>
+        <v>-2.3728772881969999E-6</v>
       </c>
       <c r="G21">
-        <v>1.0697945405575843E-4</v>
+        <v>1.3729069205695334E-4</v>
       </c>
       <c r="H21">
-        <v>7.2196678534333604E-5</v>
+        <v>9.812631938772295E-5</v>
       </c>
       <c r="I21">
-        <v>2.7986649151010695E-5</v>
+        <v>1.1367478037511113E-4</v>
       </c>
       <c r="J21">
-        <v>-9.492733634786603E-5</v>
+        <v>-1.7693537704697223E-6</v>
       </c>
       <c r="K21">
-        <v>2.4730471848987551E-5</v>
+        <v>1.270440266677072E-4</v>
       </c>
       <c r="L21">
-        <v>-1.5281774963111258E-4</v>
+        <v>-4.0953933097034791E-5</v>
       </c>
       <c r="M21">
-        <v>-2.7753711846173739E-5</v>
+        <v>9.3375615364991093E-5</v>
       </c>
       <c r="N21">
-        <v>-2.2595430780857962E-5</v>
+        <v>1.5165314124169224E-4</v>
       </c>
       <c r="O21">
-        <v>2.690620687459002E-3</v>
+        <v>2.699874551112519E-3</v>
       </c>
       <c r="P21">
-        <v>2.593167226664353E-3</v>
+        <v>2.5939712572031854E-3</v>
       </c>
       <c r="Q21">
-        <v>2.673763104855714E-3</v>
+        <v>2.7135908303054608E-3</v>
       </c>
       <c r="R21">
-        <v>2.7028694385049855E-3</v>
+        <v>2.7369804167919291E-3</v>
       </c>
       <c r="S21">
-        <v>2.5418104851318243E-3</v>
+        <v>2.561919449660866E-3</v>
       </c>
       <c r="T21">
-        <v>2.6770660248227503E-3</v>
+        <v>2.7200193559688683E-3</v>
       </c>
       <c r="U21">
-        <v>3.0170099491313861E-3</v>
+        <v>3.0855966227140053E-3</v>
       </c>
       <c r="V21">
-        <v>5.6856952345552885E-3</v>
+        <v>5.7392165810793106E-3</v>
       </c>
       <c r="W21">
-        <v>2.7995047746552587E-3</v>
+        <v>2.8525485902664519E-3</v>
       </c>
       <c r="X21">
-        <v>2.8054921538831858E-3</v>
+        <v>2.8443378998077216E-3</v>
       </c>
       <c r="Y21">
-        <v>2.7526232199681384E-3</v>
+        <v>2.7936202899409165E-3</v>
       </c>
       <c r="Z21">
-        <v>2.2308029525381615E-5</v>
+        <v>1.0142160742365287E-3</v>
       </c>
       <c r="AA21">
-        <v>-1.4936512243180795E-4</v>
+        <v>4.1618808185465844E-3</v>
       </c>
       <c r="AB21">
-        <v>9.0923009748039693E-5</v>
+        <v>8.5054765331505949E-4</v>
       </c>
       <c r="AC21">
-        <v>9.5626338923415831E-4</v>
+        <v>3.1414973637600591E-5</v>
       </c>
       <c r="AD21">
-        <v>4.0539456518666056E-3</v>
+        <v>6.6797044915135146E-5</v>
       </c>
       <c r="AE21">
-        <v>8.540285919441603E-4</v>
+        <v>-1.144355416136467E-5</v>
       </c>
       <c r="AF21">
-        <v>-6.8430847914009076E-3</v>
+        <v>7.7074272780367414E-5</v>
+      </c>
+      <c r="AG21">
+        <v>9.0949698897917512E-5</v>
+      </c>
+      <c r="AH21">
+        <v>8.0479858898312769E-5</v>
+      </c>
+      <c r="AI21">
+        <v>2.010058464021287E-4</v>
+      </c>
+      <c r="AJ21">
+        <v>3.1381260212924719E-4</v>
+      </c>
+      <c r="AK21">
+        <v>4.7694319335384126E-5</v>
+      </c>
+      <c r="AL21">
+        <v>3.0464728641229396E-4</v>
+      </c>
+      <c r="AM21">
+        <v>1.1760027042182061E-4</v>
+      </c>
+      <c r="AN21">
+        <v>1.6631779816697568E-4</v>
+      </c>
+      <c r="AO21">
+        <v>3.7247775096117298E-4</v>
+      </c>
+      <c r="AP21">
+        <v>-7.4122159488518059E-3</v>
       </c>
     </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>33</v>
       </c>
       <c r="B22">
-        <v>-1.8134419711079774E-2</v>
+        <v>-5.844099379730891E-3</v>
       </c>
       <c r="C22">
-        <v>-1.2603087492062997E-5</v>
+        <v>-2.4096929068681967E-5</v>
       </c>
       <c r="D22">
-        <v>2.4318932414474424E-4</v>
+        <v>2.649294187907728E-4</v>
       </c>
       <c r="E22">
-        <v>-4.847160544957353E-6</v>
+        <v>-5.3645852991998655E-6</v>
       </c>
       <c r="F22">
-        <v>4.2043914335640692E-5</v>
+        <v>7.3155472425723419E-5</v>
       </c>
       <c r="G22">
-        <v>2.2606405081549487E-4</v>
+        <v>2.6112558970635739E-4</v>
       </c>
       <c r="H22">
-        <v>-2.6748184923592504E-4</v>
+        <v>-2.5356353638289507E-4</v>
       </c>
       <c r="I22">
-        <v>2.1395355977187947E-5</v>
+        <v>-1.0165002897182408E-5</v>
       </c>
       <c r="J22">
-        <v>6.0030106901738851E-5</v>
+        <v>-2.0527851590402798E-5</v>
       </c>
       <c r="K22">
-        <v>1.8731504269444332E-4</v>
+        <v>-2.4072347394485296E-4</v>
       </c>
       <c r="L22">
-        <v>1.1558556674471439E-5</v>
+        <v>-1.3910515004404559E-4</v>
       </c>
       <c r="M22">
-        <v>2.9856021505670624E-4</v>
+        <v>1.995753768051574E-4</v>
       </c>
       <c r="N22">
-        <v>2.5770867538976066E-4</v>
+        <v>1.9098881914078017E-4</v>
       </c>
       <c r="O22">
-        <v>2.6931009418376438E-3</v>
+        <v>2.6999741795281861E-3</v>
       </c>
       <c r="P22">
-        <v>2.6686997482110726E-3</v>
+        <v>2.6636027760937936E-3</v>
       </c>
       <c r="Q22">
-        <v>2.7009555285118763E-3</v>
+        <v>2.7496790287707051E-3</v>
       </c>
       <c r="R22">
-        <v>2.7133569256387463E-3</v>
+        <v>2.7633174487011313E-3</v>
       </c>
       <c r="S22">
-        <v>2.5735567501558631E-3</v>
+        <v>2.6151550468867571E-3</v>
       </c>
       <c r="T22">
-        <v>2.6948403172487347E-3</v>
+        <v>2.7391782953354632E-3</v>
       </c>
       <c r="U22">
-        <v>3.0717484640609004E-3</v>
+        <v>3.1333032657373345E-3</v>
       </c>
       <c r="V22">
-        <v>2.7995047746552587E-3</v>
+        <v>2.8525485902664519E-3</v>
       </c>
       <c r="W22">
-        <v>6.4798650097036272E-3</v>
+        <v>6.3869819447334233E-3</v>
       </c>
       <c r="X22">
-        <v>2.7987200125283605E-3</v>
+        <v>2.8401982395330071E-3</v>
       </c>
       <c r="Y22">
-        <v>2.8329324296102899E-3</v>
+        <v>2.864958277354163E-3</v>
       </c>
       <c r="Z22">
-        <v>3.67840972096057E-5</v>
+        <v>1.0343553774806514E-3</v>
       </c>
       <c r="AA22">
-        <v>-2.5598047167513493E-4</v>
+        <v>4.2896306068334411E-3</v>
       </c>
       <c r="AB22">
-        <v>-6.7341290994294583E-5</v>
+        <v>7.835467944381885E-4</v>
       </c>
       <c r="AC22">
-        <v>9.9398358505750368E-4</v>
+        <v>1.11314512355422E-4</v>
       </c>
       <c r="AD22">
-        <v>4.2351790780349313E-3</v>
+        <v>1.0664485783086068E-4</v>
       </c>
       <c r="AE22">
-        <v>7.9533769129889759E-4</v>
+        <v>6.2374502017648124E-5</v>
       </c>
       <c r="AF22">
-        <v>-6.6672566230439817E-3</v>
+        <v>4.4927216154986649E-5</v>
+      </c>
+      <c r="AG22">
+        <v>2.0306690885231449E-4</v>
+      </c>
+      <c r="AH22">
+        <v>9.7790367365283752E-5</v>
+      </c>
+      <c r="AI22">
+        <v>2.322419260665082E-4</v>
+      </c>
+      <c r="AJ22">
+        <v>1.3299822163657547E-4</v>
+      </c>
+      <c r="AK22">
+        <v>2.6142780263536339E-5</v>
+      </c>
+      <c r="AL22">
+        <v>2.6518210579589644E-4</v>
+      </c>
+      <c r="AM22">
+        <v>2.5758220921477323E-4</v>
+      </c>
+      <c r="AN22">
+        <v>4.4105673409162278E-4</v>
+      </c>
+      <c r="AO22">
+        <v>4.1579308905015031E-4</v>
+      </c>
+      <c r="AP22">
+        <v>-6.3353044574033669E-3</v>
       </c>
     </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>34</v>
       </c>
       <c r="B23">
-        <v>0.13026905603376457</v>
+        <v>0.13108302945428535</v>
       </c>
       <c r="C23">
-        <v>-1.2415530464250412E-5</v>
+        <v>-7.849435184905814E-6</v>
       </c>
       <c r="D23">
-        <v>3.7117580639640371E-4</v>
+        <v>4.3744291936165876E-4</v>
       </c>
       <c r="E23">
-        <v>-6.8188063961987933E-6</v>
+        <v>-8.0043737470209231E-6</v>
       </c>
       <c r="F23">
-        <v>4.004151662559516E-4</v>
+        <v>4.7911234846116798E-4</v>
       </c>
       <c r="G23">
-        <v>4.4390586994820606E-4</v>
+        <v>4.5561566345628387E-4</v>
       </c>
       <c r="H23">
-        <v>2.0448099579843128E-4</v>
+        <v>2.7234439124504704E-4</v>
       </c>
       <c r="I23">
-        <v>-4.0747779805873211E-4</v>
+        <v>-3.9196291533570468E-4</v>
       </c>
       <c r="J23">
-        <v>-4.4014557325362216E-4</v>
+        <v>-2.5876484092957785E-4</v>
       </c>
       <c r="K23">
-        <v>-4.0606137750241018E-4</v>
+        <v>1.0041377358829763E-4</v>
       </c>
       <c r="L23">
-        <v>-6.6425046641433848E-4</v>
+        <v>-3.8047684327997496E-4</v>
       </c>
       <c r="M23">
-        <v>-4.2062670227277136E-4</v>
+        <v>-1.437839419822109E-4</v>
       </c>
       <c r="N23">
-        <v>-4.5250298042239689E-4</v>
+        <v>-1.2307390190378675E-4</v>
       </c>
       <c r="O23">
-        <v>2.67150611730109E-3</v>
+        <v>2.6655404841802381E-3</v>
       </c>
       <c r="P23">
-        <v>2.6117987398632673E-3</v>
+        <v>2.6058610490000862E-3</v>
       </c>
       <c r="Q23">
-        <v>2.6875183056754483E-3</v>
+        <v>2.7310739415100714E-3</v>
       </c>
       <c r="R23">
-        <v>2.6828811327583913E-3</v>
+        <v>2.7182030396487649E-3</v>
       </c>
       <c r="S23">
-        <v>2.5372961990088537E-3</v>
+        <v>2.5578719783937182E-3</v>
       </c>
       <c r="T23">
-        <v>2.6601865048624831E-3</v>
+        <v>2.7031581453199633E-3</v>
       </c>
       <c r="U23">
-        <v>3.0504256414284228E-3</v>
+        <v>3.0992083077400487E-3</v>
       </c>
       <c r="V23">
-        <v>2.8054921538831858E-3</v>
+        <v>2.8443378998077216E-3</v>
       </c>
       <c r="W23">
-        <v>2.7987200125283605E-3</v>
+        <v>2.8401982395330071E-3</v>
       </c>
       <c r="X23">
-        <v>5.7493064685174497E-3</v>
+        <v>5.7794490671659931E-3</v>
       </c>
       <c r="Y23">
-        <v>2.7410527348470238E-3</v>
+        <v>2.7776822366332009E-3</v>
       </c>
       <c r="Z23">
-        <v>4.2078122985080696E-5</v>
+        <v>1.0263225136128132E-3</v>
       </c>
       <c r="AA23">
-        <v>-2.4129424255733928E-4</v>
+        <v>4.1485892398685411E-3</v>
       </c>
       <c r="AB23">
-        <v>-1.7546927837554254E-4</v>
+        <v>6.3174760861943913E-4</v>
       </c>
       <c r="AC23">
-        <v>9.2668157156582196E-4</v>
+        <v>1.7245075275301592E-4</v>
       </c>
       <c r="AD23">
-        <v>4.056550328183816E-3</v>
+        <v>1.0520961430668857E-4</v>
       </c>
       <c r="AE23">
-        <v>6.1811414330239589E-4</v>
+        <v>7.6535642257911213E-5</v>
       </c>
       <c r="AF23">
-        <v>-8.1235657763158893E-3</v>
+        <v>1.2215194341674504E-4</v>
+      </c>
+      <c r="AG23">
+        <v>2.2512109619011555E-4</v>
+      </c>
+      <c r="AH23">
+        <v>1.8785836796904798E-4</v>
+      </c>
+      <c r="AI23">
+        <v>4.3959020936331565E-4</v>
+      </c>
+      <c r="AJ23">
+        <v>3.2698336473956655E-4</v>
+      </c>
+      <c r="AK23">
+        <v>1.3697271737599798E-4</v>
+      </c>
+      <c r="AL23">
+        <v>2.7365750791416652E-4</v>
+      </c>
+      <c r="AM23">
+        <v>7.854314535588494E-4</v>
+      </c>
+      <c r="AN23">
+        <v>2.7528335927253953E-4</v>
+      </c>
+      <c r="AO23">
+        <v>3.7985727573123899E-4</v>
+      </c>
+      <c r="AP23">
+        <v>-8.9143066260666572E-3</v>
       </c>
     </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>35</v>
       </c>
       <c r="B24">
-        <v>-0.13172778095661891</v>
+        <v>-0.13472011693213851</v>
       </c>
       <c r="C24">
-        <v>6.2049055527128172E-5</v>
+        <v>5.1487735226655074E-5</v>
       </c>
       <c r="D24">
-        <v>8.6311337591227048E-5</v>
+        <v>1.3424030484546386E-4</v>
       </c>
       <c r="E24">
-        <v>-1.9027586668400809E-6</v>
+        <v>-2.7837049819938063E-6</v>
       </c>
       <c r="F24">
-        <v>1.583288399686477E-5</v>
+        <v>5.5201431054995032E-5</v>
       </c>
       <c r="G24">
-        <v>2.6971178553977055E-4</v>
+        <v>3.2535158069503653E-4</v>
       </c>
       <c r="H24">
-        <v>-1.4141087857681158E-4</v>
+        <v>-1.4888379230037401E-4</v>
       </c>
       <c r="I24">
-        <v>-3.9056292400923339E-5</v>
+        <v>-2.0824147670606662E-5</v>
       </c>
       <c r="J24">
-        <v>-6.6296903178857634E-5</v>
+        <v>-4.6037001286206893E-5</v>
       </c>
       <c r="K24">
-        <v>-1.800926872857567E-5</v>
+        <v>-1.3580965001416031E-5</v>
       </c>
       <c r="L24">
-        <v>-6.404096945532723E-5</v>
+        <v>-5.1337837126167254E-5</v>
       </c>
       <c r="M24">
-        <v>1.4844073235358891E-4</v>
+        <v>1.9773047327624905E-4</v>
       </c>
       <c r="N24">
-        <v>1.3714088259977886E-4</v>
+        <v>2.0223714684205769E-4</v>
       </c>
       <c r="O24">
-        <v>2.7021111428959009E-3</v>
+        <v>2.7717043433295252E-3</v>
       </c>
       <c r="P24">
-        <v>2.6257306852547737E-3</v>
+        <v>2.6788798706361191E-3</v>
       </c>
       <c r="Q24">
-        <v>2.6317172248474779E-3</v>
+        <v>2.6785300310321679E-3</v>
       </c>
       <c r="R24">
-        <v>2.6678274312721189E-3</v>
+        <v>2.7021672019574266E-3</v>
       </c>
       <c r="S24">
-        <v>2.5419697493696642E-3</v>
+        <v>2.5774336135951912E-3</v>
       </c>
       <c r="T24">
-        <v>2.6431170489514795E-3</v>
+        <v>2.6917669764101293E-3</v>
       </c>
       <c r="U24">
-        <v>3.0431964473658854E-3</v>
+        <v>3.1483278195714565E-3</v>
       </c>
       <c r="V24">
-        <v>2.7526232199681384E-3</v>
+        <v>2.7936202899409165E-3</v>
       </c>
       <c r="W24">
-        <v>2.8329324296102899E-3</v>
+        <v>2.864958277354163E-3</v>
       </c>
       <c r="X24">
-        <v>2.7410527348470238E-3</v>
+        <v>2.7776822366332009E-3</v>
       </c>
       <c r="Y24">
-        <v>5.4200688670805672E-3</v>
+        <v>5.5668702465927486E-3</v>
       </c>
       <c r="Z24">
-        <v>1.6997596660196524E-5</v>
+        <v>1.084000432767135E-3</v>
       </c>
       <c r="AA24">
-        <v>-2.4863666861131301E-4</v>
+        <v>4.5067796378181028E-3</v>
       </c>
       <c r="AB24">
-        <v>-1.4475303038542948E-4</v>
+        <v>6.908244200843134E-4</v>
       </c>
       <c r="AC24">
-        <v>1.0714562091791425E-3</v>
+        <v>1.7514571422318079E-4</v>
       </c>
       <c r="AD24">
-        <v>4.2163983927284605E-3</v>
+        <v>1.5254935321406632E-4</v>
       </c>
       <c r="AE24">
-        <v>7.452836621582215E-4</v>
+        <v>1.2885266391750067E-4</v>
       </c>
       <c r="AF24">
-        <v>-4.1967151553959411E-3</v>
+        <v>8.3843002373435111E-5</v>
+      </c>
+      <c r="AG24">
+        <v>1.4180528153370689E-4</v>
+      </c>
+      <c r="AH24">
+        <v>7.8670555083259499E-5</v>
+      </c>
+      <c r="AI24">
+        <v>2.3438448419749354E-4</v>
+      </c>
+      <c r="AJ24">
+        <v>7.2498158909919995E-5</v>
+      </c>
+      <c r="AK24">
+        <v>-4.9212304672168437E-5</v>
+      </c>
+      <c r="AL24">
+        <v>8.5715926743694252E-5</v>
+      </c>
+      <c r="AM24">
+        <v>-8.3712329792238766E-5</v>
+      </c>
+      <c r="AN24">
+        <v>9.3380854805229317E-5</v>
+      </c>
+      <c r="AO24">
+        <v>1.2002889366924379E-3</v>
+      </c>
+      <c r="AP24">
+        <v>-4.8076095563179032E-3</v>
       </c>
     </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>36</v>
       </c>
       <c r="B25">
-        <v>-1.5229470223584403E-2</v>
+        <v>-0.48835347754042741</v>
       </c>
       <c r="C25">
-        <v>1.5707991150727183E-6</v>
+        <v>-1.5876900891577438E-5</v>
       </c>
       <c r="D25">
-        <v>6.0185117747523463E-6</v>
+        <v>-3.1330126577712274E-5</v>
       </c>
       <c r="E25">
-        <v>-1.1147281012490682E-7</v>
+        <v>3.9456668226590106E-7</v>
       </c>
       <c r="F25">
-        <v>4.7225383861884251E-5</v>
+        <v>4.8224373789462847E-5</v>
       </c>
       <c r="G25">
-        <v>2.8249078510313858E-5</v>
+        <v>3.3930429597814208E-4</v>
       </c>
       <c r="H25">
-        <v>2.7587062873393265E-6</v>
+        <v>5.1859267960335754E-4</v>
       </c>
       <c r="I25">
-        <v>-2.6488357675537918E-5</v>
+        <v>2.2405605565185838E-4</v>
       </c>
       <c r="J25">
-        <v>-1.0942222301353111E-5</v>
+        <v>1.1727582890683989E-4</v>
       </c>
       <c r="K25">
-        <v>3.464963209568535E-6</v>
+        <v>1.9541102074537324E-4</v>
       </c>
       <c r="L25">
-        <v>1.5471141574857281E-6</v>
+        <v>2.8519470912943996E-4</v>
       </c>
       <c r="M25">
-        <v>1.9843368338410845E-5</v>
+        <v>3.5584913574248029E-4</v>
       </c>
       <c r="N25">
-        <v>-1.3915280044423067E-5</v>
+        <v>8.2745024440187241E-5</v>
       </c>
       <c r="O25">
-        <v>5.166515283836447E-5</v>
+        <v>9.464773918418601E-4</v>
       </c>
       <c r="P25">
-        <v>6.2053314703571861E-5</v>
+        <v>6.5252130916728832E-4</v>
       </c>
       <c r="Q25">
-        <v>2.2938560151833246E-5</v>
+        <v>8.5185315207795436E-4</v>
       </c>
       <c r="R25">
-        <v>1.6382463128005733E-5</v>
+        <v>8.5023299658758972E-4</v>
       </c>
       <c r="S25">
-        <v>4.6911315654731803E-5</v>
+        <v>2.5593379697982466E-4</v>
       </c>
       <c r="T25">
-        <v>1.3755972232894675E-5</v>
+        <v>8.7919636762020007E-4</v>
       </c>
       <c r="U25">
-        <v>4.138284363145898E-5</v>
+        <v>1.0547056929718968E-3</v>
       </c>
       <c r="V25">
-        <v>2.2308029525381615E-5</v>
+        <v>1.0142160742365287E-3</v>
       </c>
       <c r="W25">
-        <v>3.67840972096057E-5</v>
+        <v>1.0343553774806514E-3</v>
       </c>
       <c r="X25">
-        <v>4.2078122985080696E-5</v>
+        <v>1.0263225136128132E-3</v>
       </c>
       <c r="Y25">
-        <v>1.6997596660196524E-5</v>
+        <v>1.084000432767135E-3</v>
       </c>
       <c r="Z25">
-        <v>2.4226366935096994E-5</v>
+        <v>3.7787034307713852E-3</v>
       </c>
       <c r="AA25">
-        <v>-1.0604655990724388E-4</v>
+        <v>1.6826897430707907E-3</v>
       </c>
       <c r="AB25">
-        <v>-1.2701964426740123E-4</v>
+        <v>5.6084740014147709E-4</v>
       </c>
       <c r="AC25">
-        <v>-2.2404405524717008E-5</v>
+        <v>2.4316950526984368E-5</v>
       </c>
       <c r="AD25">
-        <v>1.6178544856595257E-4</v>
+        <v>-5.9313884211468224E-5</v>
       </c>
       <c r="AE25">
-        <v>-2.9776083124929033E-5</v>
+        <v>-6.5765981379933513E-6</v>
       </c>
       <c r="AF25">
-        <v>-5.1025476033362508E-4</v>
+        <v>-1.1386214138434004E-5</v>
+      </c>
+      <c r="AG25">
+        <v>-1.7982595831144804E-5</v>
+      </c>
+      <c r="AH25">
+        <v>-9.8054533502596138E-6</v>
+      </c>
+      <c r="AI25">
+        <v>6.2954379101127058E-6</v>
+      </c>
+      <c r="AJ25">
+        <v>1.1694831471503484E-4</v>
+      </c>
+      <c r="AK25">
+        <v>-1.453065995145351E-4</v>
+      </c>
+      <c r="AL25">
+        <v>-1.1636752989817589E-4</v>
+      </c>
+      <c r="AM25">
+        <v>-3.5705730854794987E-4</v>
+      </c>
+      <c r="AN25">
+        <v>5.7797568376490488E-5</v>
+      </c>
+      <c r="AO25">
+        <v>-6.9522810621687903E-4</v>
+      </c>
+      <c r="AP25">
+        <v>-1.0085313309827234E-3</v>
       </c>
     </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>37</v>
       </c>
       <c r="B26">
-        <v>0.11251512566003151</v>
+        <v>-0.2023127666908747</v>
       </c>
       <c r="C26">
-        <v>4.4743738907690041E-5</v>
+        <v>-5.7409016532948489E-4</v>
       </c>
       <c r="D26">
-        <v>7.7573150486439117E-6</v>
+        <v>3.8080296473268736E-4</v>
       </c>
       <c r="E26">
-        <v>-1.6341386261677094E-7</v>
+        <v>-8.0987779329726812E-6</v>
       </c>
       <c r="F26">
-        <v>-5.6160774035137666E-5</v>
+        <v>9.9289398882804452E-4</v>
       </c>
       <c r="G26">
-        <v>-1.5884086586774482E-4</v>
+        <v>1.0977626702368599E-3</v>
       </c>
       <c r="H26">
-        <v>6.7696276270442392E-5</v>
+        <v>6.4906242733550482E-4</v>
       </c>
       <c r="I26">
-        <v>1.1042014054976686E-4</v>
+        <v>-5.7471330329144504E-4</v>
       </c>
       <c r="J26">
-        <v>5.3821302802515875E-5</v>
+        <v>-3.747937841465385E-4</v>
       </c>
       <c r="K26">
-        <v>-4.3502193654356146E-5</v>
+        <v>-6.9441542209894985E-5</v>
       </c>
       <c r="L26">
-        <v>9.4938867879374274E-5</v>
+        <v>-3.2260230766959549E-4</v>
       </c>
       <c r="M26">
-        <v>-1.421721672999253E-5</v>
+        <v>9.2592718334757323E-4</v>
       </c>
       <c r="N26">
-        <v>-2.4702454943775396E-5</v>
+        <v>-1.8371514161033033E-4</v>
       </c>
       <c r="O26">
-        <v>-3.5445431679852196E-4</v>
+        <v>4.0801005309275412E-3</v>
       </c>
       <c r="P26">
-        <v>-4.013320078186444E-4</v>
+        <v>3.6480077635146942E-3</v>
       </c>
       <c r="Q26">
-        <v>-2.454278741564549E-4</v>
+        <v>3.899620661009066E-3</v>
       </c>
       <c r="R26">
-        <v>-6.9571271212558503E-5</v>
+        <v>3.9379019639069045E-3</v>
       </c>
       <c r="S26">
-        <v>-3.7060446292431072E-4</v>
+        <v>3.7506768743641762E-3</v>
       </c>
       <c r="T26">
-        <v>-6.1975807112222422E-5</v>
+        <v>3.5538676803986932E-3</v>
       </c>
       <c r="U26">
-        <v>-3.1448617303492916E-4</v>
+        <v>6.5457510085627623E-3</v>
       </c>
       <c r="V26">
-        <v>-1.4936512243180795E-4</v>
+        <v>4.1618808185465844E-3</v>
       </c>
       <c r="W26">
-        <v>-2.5598047167513493E-4</v>
+        <v>4.2896306068334411E-3</v>
       </c>
       <c r="X26">
-        <v>-2.4129424255733928E-4</v>
+        <v>4.1485892398685411E-3</v>
       </c>
       <c r="Y26">
-        <v>-2.4863666861131301E-4</v>
+        <v>4.5067796378181028E-3</v>
       </c>
       <c r="Z26">
-        <v>-1.0604655990724388E-4</v>
+        <v>1.6826897430707907E-3</v>
       </c>
       <c r="AA26">
-        <v>4.0534614110994144E-3</v>
+        <v>2.3029137143105897E-2</v>
       </c>
       <c r="AB26">
-        <v>7.906437760467857E-4</v>
+        <v>1.4939010954830949E-3</v>
       </c>
       <c r="AC26">
-        <v>-5.8412094472513453E-6</v>
+        <v>-1.9219460589285848E-5</v>
       </c>
       <c r="AD26">
-        <v>-9.096200513727139E-4</v>
+        <v>-2.4687806403688692E-4</v>
       </c>
       <c r="AE26">
-        <v>8.1059336180796962E-4</v>
+        <v>-2.0548575099587875E-4</v>
       </c>
       <c r="AF26">
-        <v>1.5987703405011271E-3</v>
+        <v>-6.2040791143166193E-5</v>
+      </c>
+      <c r="AG26">
+        <v>6.4665043798398168E-5</v>
+      </c>
+      <c r="AH26">
+        <v>-1.6537909300323408E-4</v>
+      </c>
+      <c r="AI26">
+        <v>-1.4137016628899921E-4</v>
+      </c>
+      <c r="AJ26">
+        <v>-1.2097113708995234E-4</v>
+      </c>
+      <c r="AK26">
+        <v>-1.868826381787931E-4</v>
+      </c>
+      <c r="AL26">
+        <v>-6.3127040317329398E-6</v>
+      </c>
+      <c r="AM26">
+        <v>-3.6139784449231506E-4</v>
+      </c>
+      <c r="AN26">
+        <v>4.7301250268515032E-4</v>
+      </c>
+      <c r="AO26">
+        <v>5.334419155189069E-3</v>
+      </c>
+      <c r="AP26">
+        <v>-9.2713739123573401E-3</v>
       </c>
     </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>38</v>
       </c>
       <c r="B27">
-        <v>8.4215867358136673E-2</v>
+        <v>-0.21346411439612528</v>
       </c>
       <c r="C27">
-        <v>1.9346771455097677E-5</v>
+        <v>-2.7027227406896798E-5</v>
       </c>
       <c r="D27">
-        <v>-4.37111033549549E-5</v>
+        <v>3.9857353105700842E-5</v>
       </c>
       <c r="E27">
-        <v>5.9964560833659268E-7</v>
+        <v>-1.2520889908363005E-6</v>
       </c>
       <c r="F27">
-        <v>-1.5091809039732948E-5</v>
+        <v>-1.6280678759891354E-4</v>
       </c>
       <c r="G27">
-        <v>-4.8603812532399852E-5</v>
+        <v>-9.7380284950361097E-5</v>
       </c>
       <c r="H27">
-        <v>-1.6483260493021059E-5</v>
+        <v>-5.6858170959505684E-5</v>
       </c>
       <c r="I27">
-        <v>-6.9332360169555387E-5</v>
+        <v>-5.9019406989655517E-5</v>
       </c>
       <c r="J27">
-        <v>-4.4105683785933378E-5</v>
+        <v>-3.3482622108227714E-5</v>
       </c>
       <c r="K27">
-        <v>5.5214484269356973E-6</v>
+        <v>-1.7531601378694773E-5</v>
       </c>
       <c r="L27">
-        <v>6.7860537026259119E-5</v>
+        <v>7.4233047102914714E-5</v>
       </c>
       <c r="M27">
-        <v>-1.9797213126812043E-5</v>
+        <v>2.8460218057013405E-4</v>
       </c>
       <c r="N27">
-        <v>9.1966178694389005E-5</v>
+        <v>1.0618924550838003E-4</v>
       </c>
       <c r="O27">
-        <v>-3.5236329918160328E-4</v>
+        <v>6.8225948247787249E-4</v>
       </c>
       <c r="P27">
-        <v>-1.9171875709240831E-4</v>
+        <v>3.7381468572869928E-4</v>
       </c>
       <c r="Q27">
-        <v>1.9687079064206801E-4</v>
+        <v>6.5069366495756203E-4</v>
       </c>
       <c r="R27">
-        <v>-8.4003396433393032E-5</v>
+        <v>5.4858269430288313E-4</v>
       </c>
       <c r="S27">
-        <v>-2.7033595762525993E-4</v>
+        <v>2.1419746983587554E-4</v>
       </c>
       <c r="T27">
-        <v>-1.9305222792210955E-6</v>
+        <v>4.6106910329600666E-4</v>
       </c>
       <c r="U27">
-        <v>-2.5650292090165911E-4</v>
+        <v>6.8731260979232377E-4</v>
       </c>
       <c r="V27">
-        <v>9.0923009748039693E-5</v>
+        <v>8.5054765331505949E-4</v>
       </c>
       <c r="W27">
-        <v>-6.7341290994294583E-5</v>
+        <v>7.835467944381885E-4</v>
       </c>
       <c r="X27">
-        <v>-1.7546927837554254E-4</v>
+        <v>6.3174760861943913E-4</v>
       </c>
       <c r="Y27">
-        <v>-1.4475303038542948E-4</v>
+        <v>6.908244200843134E-4</v>
       </c>
       <c r="Z27">
-        <v>-1.2701964426740123E-4</v>
+        <v>5.6084740014147709E-4</v>
       </c>
       <c r="AA27">
-        <v>7.906437760467857E-4</v>
+        <v>1.4939010954830949E-3</v>
       </c>
       <c r="AB27">
-        <v>4.4547470729170893E-3</v>
+        <v>7.577975553838232E-3</v>
       </c>
       <c r="AC27">
-        <v>4.3364124045632978E-5</v>
+        <v>9.4332141775242456E-5</v>
       </c>
       <c r="AD27">
-        <v>-8.9523759819373457E-4</v>
+        <v>-7.924931770945316E-5</v>
       </c>
       <c r="AE27">
-        <v>6.1799608931991035E-5</v>
+        <v>-1.3595820633839354E-4</v>
       </c>
       <c r="AF27">
-        <v>2.5819594381777671E-3</v>
+        <v>-9.6865058397882763E-5</v>
+      </c>
+      <c r="AG27">
+        <v>-9.0981278261641839E-5</v>
+      </c>
+      <c r="AH27">
+        <v>-1.6054321281455284E-4</v>
+      </c>
+      <c r="AI27">
+        <v>-9.0173341301724843E-5</v>
+      </c>
+      <c r="AJ27">
+        <v>-2.1927322008343905E-4</v>
+      </c>
+      <c r="AK27">
+        <v>5.7259898275580979E-4</v>
+      </c>
+      <c r="AL27">
+        <v>-2.2543647945610256E-4</v>
+      </c>
+      <c r="AM27">
+        <v>-5.0629895511201614E-4</v>
+      </c>
+      <c r="AN27">
+        <v>-6.8384123743197385E-5</v>
+      </c>
+      <c r="AO27">
+        <v>-6.359847200000312E-4</v>
+      </c>
+      <c r="AP27">
+        <v>-9.3709279834130175E-4</v>
       </c>
     </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>39</v>
       </c>
       <c r="B28">
-        <v>-0.47689607236742615</v>
+        <v>-0.10001065960830192</v>
       </c>
       <c r="C28">
-        <v>-8.5206271170738937E-6</v>
+        <v>7.4784670202262093E-6</v>
       </c>
       <c r="D28">
-        <v>-5.7483922405465911E-5</v>
+        <v>-5.4665700489507022E-5</v>
       </c>
       <c r="E28">
-        <v>8.6386851775463133E-7</v>
+        <v>9.7447617253322515E-7</v>
       </c>
       <c r="F28">
-        <v>1.5780785762827161E-5</v>
+        <v>4.3968781107485303E-5</v>
       </c>
       <c r="G28">
-        <v>3.1947794391678315E-4</v>
+        <v>2.2835823655353009E-5</v>
       </c>
       <c r="H28">
-        <v>4.8536917546892675E-4</v>
+        <v>4.8434330924966362E-5</v>
       </c>
       <c r="I28">
-        <v>1.609415858674669E-4</v>
+        <v>-6.2878773545956012E-5</v>
       </c>
       <c r="J28">
-        <v>7.777302847041586E-5</v>
+        <v>-6.1859437384845185E-6</v>
       </c>
       <c r="K28">
-        <v>1.3798068443338866E-4</v>
+        <v>1.7858657583539207E-6</v>
       </c>
       <c r="L28">
-        <v>2.8999327648147801E-4</v>
+        <v>3.860255248659206E-5</v>
       </c>
       <c r="M28">
-        <v>3.0147059722249658E-4</v>
+        <v>7.6415206701586978E-5</v>
       </c>
       <c r="N28">
-        <v>1.1749946571311745E-4</v>
+        <v>3.1046720655801378E-6</v>
       </c>
       <c r="O28">
-        <v>8.836250317549463E-4</v>
+        <v>3.6383399894679389E-5</v>
       </c>
       <c r="P28">
-        <v>6.2520699498085975E-4</v>
+        <v>3.8401810266868195E-5</v>
       </c>
       <c r="Q28">
-        <v>7.9523786611517303E-4</v>
+        <v>4.7132749667803172E-5</v>
       </c>
       <c r="R28">
-        <v>7.9651402997497314E-4</v>
+        <v>5.1881788722194584E-5</v>
       </c>
       <c r="S28">
-        <v>2.2938060598892002E-4</v>
+        <v>2.4502872166657855E-5</v>
       </c>
       <c r="T28">
-        <v>8.5193195049797937E-4</v>
+        <v>2.8426102905114052E-5</v>
       </c>
       <c r="U28">
-        <v>9.9765743259814339E-4</v>
+        <v>9.6556733151582455E-5</v>
       </c>
       <c r="V28">
-        <v>9.5626338923415831E-4</v>
+        <v>3.1414973637600591E-5</v>
       </c>
       <c r="W28">
-        <v>9.9398358505750368E-4</v>
+        <v>1.11314512355422E-4</v>
       </c>
       <c r="X28">
-        <v>9.2668157156582196E-4</v>
+        <v>1.7245075275301592E-4</v>
       </c>
       <c r="Y28">
-        <v>1.0714562091791425E-3</v>
+        <v>1.7514571422318079E-4</v>
       </c>
       <c r="Z28">
-        <v>-2.2404405524717008E-5</v>
+        <v>2.4316950526984368E-5</v>
       </c>
       <c r="AA28">
-        <v>-5.8412094472513453E-6</v>
+        <v>-1.9219460589285848E-5</v>
       </c>
       <c r="AB28">
-        <v>4.3364124045632978E-5</v>
+        <v>9.4332141775242456E-5</v>
       </c>
       <c r="AC28">
-        <v>3.7327240946998549E-3</v>
+        <v>4.6256262932518818E-3</v>
       </c>
       <c r="AD28">
-        <v>1.6012931728277824E-3</v>
+        <v>2.7922343252610115E-3</v>
       </c>
       <c r="AE28">
-        <v>5.766615819541059E-4</v>
+        <v>2.7948974655587063E-3</v>
       </c>
       <c r="AF28">
-        <v>-2.6107629693339482E-4</v>
+        <v>2.7938344532522927E-3</v>
+      </c>
+      <c r="AG28">
+        <v>2.7947938118867356E-3</v>
+      </c>
+      <c r="AH28">
+        <v>2.7871537314076208E-3</v>
+      </c>
+      <c r="AI28">
+        <v>2.7981909503284035E-3</v>
+      </c>
+      <c r="AJ28">
+        <v>2.7959588382399326E-3</v>
+      </c>
+      <c r="AK28">
+        <v>2.7856389699262192E-3</v>
+      </c>
+      <c r="AL28">
+        <v>2.7948626355866722E-3</v>
+      </c>
+      <c r="AM28">
+        <v>2.807344597977374E-3</v>
+      </c>
+      <c r="AN28">
+        <v>2.7890302827802563E-3</v>
+      </c>
+      <c r="AO28">
+        <v>2.7653074056122086E-3</v>
+      </c>
+      <c r="AP28">
+        <v>-2.1694029751480395E-3</v>
       </c>
     </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>40</v>
       </c>
       <c r="B29">
-        <v>-0.19765628023852819</v>
+        <v>-2.1928660374120963E-2</v>
       </c>
       <c r="C29">
-        <v>-4.8491751454143037E-4</v>
+        <v>-5.9860052688067599E-6</v>
       </c>
       <c r="D29">
-        <v>3.0594389090943946E-4</v>
+        <v>-4.7464121990653139E-5</v>
       </c>
       <c r="E29">
-        <v>-6.7249685989256738E-6</v>
+        <v>8.7283678387166684E-7</v>
       </c>
       <c r="F29">
-        <v>9.6731761536263811E-4</v>
+        <v>-5.2876722559791391E-5</v>
       </c>
       <c r="G29">
-        <v>1.0561272165055353E-3</v>
+        <v>-5.1390189181962258E-5</v>
       </c>
       <c r="H29">
-        <v>7.7981861282318612E-4</v>
+        <v>8.3822554608010719E-5</v>
       </c>
       <c r="I29">
-        <v>-5.0331829423211133E-4</v>
+        <v>3.0044011387992883E-5</v>
       </c>
       <c r="J29">
-        <v>-1.9751254821681347E-4</v>
+        <v>5.6484891149170607E-5</v>
       </c>
       <c r="K29">
-        <v>1.6042587488563406E-4</v>
+        <v>-5.8389396325273543E-5</v>
       </c>
       <c r="L29">
-        <v>4.1427333061940137E-5</v>
+        <v>7.6833970969237306E-5</v>
       </c>
       <c r="M29">
-        <v>1.082859674476654E-3</v>
+        <v>6.7395160468889195E-5</v>
       </c>
       <c r="N29">
-        <v>5.7524318997224499E-4</v>
+        <v>7.5862598318748604E-5</v>
       </c>
       <c r="O29">
-        <v>4.0826869466348507E-3</v>
+        <v>-1.0350351886452737E-5</v>
       </c>
       <c r="P29">
-        <v>3.7233483070655462E-3</v>
+        <v>1.796077361887569E-5</v>
       </c>
       <c r="Q29">
-        <v>3.7674862622241877E-3</v>
+        <v>4.3185787827978149E-5</v>
       </c>
       <c r="R29">
-        <v>3.8274021701565058E-3</v>
+        <v>4.8457227515339698E-5</v>
       </c>
       <c r="S29">
-        <v>3.6968217157761557E-3</v>
+        <v>4.0783914542143776E-5</v>
       </c>
       <c r="T29">
-        <v>3.4698126787947644E-3</v>
+        <v>-8.8277763434726239E-6</v>
       </c>
       <c r="U29">
-        <v>6.2194003388472557E-3</v>
+        <v>3.5404624202797959E-5</v>
       </c>
       <c r="V29">
-        <v>4.0539456518666056E-3</v>
+        <v>6.6797044915135146E-5</v>
       </c>
       <c r="W29">
-        <v>4.2351790780349313E-3</v>
+        <v>1.0664485783086068E-4</v>
       </c>
       <c r="X29">
-        <v>4.056550328183816E-3</v>
+        <v>1.0520961430668857E-4</v>
       </c>
       <c r="Y29">
-        <v>4.2163983927284605E-3</v>
+        <v>1.5254935321406632E-4</v>
       </c>
       <c r="Z29">
-        <v>1.6178544856595257E-4</v>
+        <v>-5.9313884211468224E-5</v>
       </c>
       <c r="AA29">
-        <v>-9.096200513727139E-4</v>
+        <v>-2.4687806403688692E-4</v>
       </c>
       <c r="AB29">
-        <v>-8.9523759819373457E-4</v>
+        <v>-7.924931770945316E-5</v>
       </c>
       <c r="AC29">
-        <v>1.6012931728277824E-3</v>
+        <v>2.7922343252610115E-3</v>
       </c>
       <c r="AD29">
-        <v>2.225403998112464E-2</v>
+        <v>4.4161604147211044E-3</v>
       </c>
       <c r="AE29">
-        <v>1.529557390671136E-3</v>
+        <v>2.803399511089706E-3</v>
       </c>
       <c r="AF29">
-        <v>-1.0982463197712714E-2</v>
+        <v>2.7978822254337409E-3</v>
+      </c>
+      <c r="AG29">
+        <v>2.798371457877123E-3</v>
+      </c>
+      <c r="AH29">
+        <v>2.7920832671859768E-3</v>
+      </c>
+      <c r="AI29">
+        <v>2.802926645939108E-3</v>
+      </c>
+      <c r="AJ29">
+        <v>2.7905655499360152E-3</v>
+      </c>
+      <c r="AK29">
+        <v>2.7797938732662978E-3</v>
+      </c>
+      <c r="AL29">
+        <v>2.7967911155299145E-3</v>
+      </c>
+      <c r="AM29">
+        <v>2.8053571802248147E-3</v>
+      </c>
+      <c r="AN29">
+        <v>2.7844917204466694E-3</v>
+      </c>
+      <c r="AO29">
+        <v>2.7372169113132859E-3</v>
+      </c>
+      <c r="AP29">
+        <v>-2.2228187633354362E-3</v>
       </c>
     </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>41</v>
       </c>
       <c r="B30">
-        <v>-0.21167740125123374</v>
+        <v>-8.0816739216561739E-2</v>
       </c>
       <c r="C30">
-        <v>-1.6263788564520126E-5</v>
+        <v>-3.4440625634049764E-5</v>
       </c>
       <c r="D30">
-        <v>4.5938859206975024E-5</v>
+        <v>1.1316046713941022E-5</v>
       </c>
       <c r="E30">
-        <v>-1.3239563656416592E-6</v>
+        <v>-1.008928501183113E-7</v>
       </c>
       <c r="F30">
-        <v>-1.5371471592788392E-4</v>
+        <v>1.0265418675298394E-4</v>
       </c>
       <c r="G30">
-        <v>-9.6399030472008593E-5</v>
+        <v>4.9621277999441844E-5</v>
       </c>
       <c r="H30">
-        <v>-3.4721657098736841E-5</v>
+        <v>2.0352282851995472E-5</v>
       </c>
       <c r="I30">
-        <v>-5.8199699141244453E-5</v>
+        <v>2.0333155571847054E-5</v>
       </c>
       <c r="J30">
-        <v>-1.3259019736037081E-5</v>
+        <v>1.87603462226136E-4</v>
       </c>
       <c r="K30">
-        <v>1.4390576215908237E-4</v>
+        <v>8.8222964537976178E-5</v>
       </c>
       <c r="L30">
-        <v>1.4636320971836723E-4</v>
+        <v>1.5457398178008439E-4</v>
       </c>
       <c r="M30">
-        <v>3.3483355004522593E-4</v>
+        <v>2.4916420691754437E-4</v>
       </c>
       <c r="N30">
-        <v>1.2756104613542886E-4</v>
+        <v>1.9107427119520806E-4</v>
       </c>
       <c r="O30">
-        <v>6.9708163366788954E-4</v>
+        <v>-5.5908665382212592E-5</v>
       </c>
       <c r="P30">
-        <v>4.2949958651375013E-4</v>
+        <v>-3.0957818563876805E-6</v>
       </c>
       <c r="Q30">
-        <v>6.705768760565373E-4</v>
+        <v>1.3595470718979021E-5</v>
       </c>
       <c r="R30">
-        <v>5.647207535889677E-4</v>
+        <v>-1.6489966512436393E-5</v>
       </c>
       <c r="S30">
-        <v>2.3555444547826711E-4</v>
+        <v>1.7370945709111775E-5</v>
       </c>
       <c r="T30">
-        <v>4.6553896826760589E-4</v>
+        <v>3.8163882471270287E-5</v>
       </c>
       <c r="U30">
-        <v>6.9886718084717701E-4</v>
+        <v>-3.6528879631264448E-5</v>
       </c>
       <c r="V30">
-        <v>8.540285919441603E-4</v>
+        <v>-1.144355416136467E-5</v>
       </c>
       <c r="W30">
-        <v>7.9533769129889759E-4</v>
+        <v>6.2374502017648124E-5</v>
       </c>
       <c r="X30">
-        <v>6.1811414330239589E-4</v>
+        <v>7.6535642257911213E-5</v>
       </c>
       <c r="Y30">
-        <v>7.452836621582215E-4</v>
+        <v>1.2885266391750067E-4</v>
       </c>
       <c r="Z30">
-        <v>-2.9776083124929033E-5</v>
+        <v>-6.5765981379933513E-6</v>
       </c>
       <c r="AA30">
-        <v>8.1059336180796962E-4</v>
+        <v>-2.0548575099587875E-4</v>
       </c>
       <c r="AB30">
-        <v>6.1799608931991035E-5</v>
+        <v>-1.3595820633839354E-4</v>
       </c>
       <c r="AC30">
-        <v>5.766615819541059E-4</v>
+        <v>2.7948974655587063E-3</v>
       </c>
       <c r="AD30">
-        <v>1.529557390671136E-3</v>
+        <v>2.803399511089706E-3</v>
       </c>
       <c r="AE30">
-        <v>7.6222554067838667E-3</v>
+        <v>4.6032602839382788E-3</v>
       </c>
       <c r="AF30">
-        <v>-7.879032034509223E-4</v>
+        <v>2.8122138959540046E-3</v>
+      </c>
+      <c r="AG30">
+        <v>2.8080899120969398E-3</v>
+      </c>
+      <c r="AH30">
+        <v>2.7967980318033647E-3</v>
+      </c>
+      <c r="AI30">
+        <v>2.7998023826113117E-3</v>
+      </c>
+      <c r="AJ30">
+        <v>2.8038864714148466E-3</v>
+      </c>
+      <c r="AK30">
+        <v>2.7700743811121219E-3</v>
+      </c>
+      <c r="AL30">
+        <v>2.7954647076284646E-3</v>
+      </c>
+      <c r="AM30">
+        <v>2.799875185711365E-3</v>
+      </c>
+      <c r="AN30">
+        <v>2.7817040956983194E-3</v>
+      </c>
+      <c r="AO30">
+        <v>2.7123875480151126E-3</v>
+      </c>
+      <c r="AP30">
+        <v>-3.2155995597387948E-3</v>
       </c>
     </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>42</v>
       </c>
       <c r="B31">
-        <v>-3.8644909703584878</v>
+        <v>-4.1588022528626957E-2</v>
       </c>
       <c r="C31">
-        <v>1.2366993500762848E-4</v>
+        <v>-6.6903555485593632E-6</v>
       </c>
       <c r="D31">
-        <v>-1.6808632573797836E-2</v>
+        <v>7.14974823305594E-7</v>
       </c>
       <c r="E31">
-        <v>3.0706765633689022E-4</v>
+        <v>5.4569807281148585E-8</v>
       </c>
       <c r="F31">
-        <v>-1.2787263037740082E-2</v>
+        <v>1.0435313997194631E-4</v>
       </c>
       <c r="G31">
-        <v>-7.8759709211673103E-3</v>
+        <v>2.7235759662248707E-5</v>
       </c>
       <c r="H31">
-        <v>-8.3513290753085521E-3</v>
+        <v>2.1017427230243379E-4</v>
       </c>
       <c r="I31">
-        <v>-5.7212067258735344E-3</v>
+        <v>-1.8080654508568182E-5</v>
       </c>
       <c r="J31">
-        <v>-5.7682647594389045E-3</v>
+        <v>9.1277848479440205E-5</v>
       </c>
       <c r="K31">
-        <v>-7.0144060457698106E-3</v>
+        <v>1.3190545015576453E-4</v>
       </c>
       <c r="L31">
-        <v>-6.4809373635966987E-3</v>
+        <v>1.5001854905039589E-4</v>
       </c>
       <c r="M31">
-        <v>-6.8969492390412186E-3</v>
+        <v>2.0779822521699537E-4</v>
       </c>
       <c r="N31">
-        <v>-9.1896095843771019E-3</v>
+        <v>1.7188203949332955E-4</v>
       </c>
       <c r="O31">
-        <v>-7.5071007540232692E-3</v>
+        <v>1.0982039910966931E-5</v>
       </c>
       <c r="P31">
-        <v>-6.7386493439850507E-3</v>
+        <v>-3.2746874619239393E-5</v>
       </c>
       <c r="Q31">
-        <v>-7.5447656928781604E-3</v>
+        <v>-3.0583766077687115E-5</v>
       </c>
       <c r="R31">
-        <v>-6.1490466953348505E-3</v>
+        <v>-4.5143872800999536E-5</v>
       </c>
       <c r="S31">
-        <v>-6.1852708304634399E-3</v>
+        <v>-4.09725545687064E-5</v>
       </c>
       <c r="T31">
-        <v>-6.833533655218561E-3</v>
+        <v>-7.049010263927727E-5</v>
       </c>
       <c r="U31">
-        <v>-6.8252074618705685E-3</v>
+        <v>2.3026649255446707E-5</v>
       </c>
       <c r="V31">
-        <v>-6.8430847914009076E-3</v>
+        <v>7.7074272780367414E-5</v>
       </c>
       <c r="W31">
-        <v>-6.6672566230439817E-3</v>
+        <v>4.4927216154986649E-5</v>
       </c>
       <c r="X31">
-        <v>-8.1235657763158893E-3</v>
+        <v>1.2215194341674504E-4</v>
       </c>
       <c r="Y31">
-        <v>-4.1967151553959411E-3</v>
+        <v>8.3843002373435111E-5</v>
       </c>
       <c r="Z31">
-        <v>-5.1025476033362508E-4</v>
+        <v>-1.1386214138434004E-5</v>
       </c>
       <c r="AA31">
-        <v>1.5987703405011271E-3</v>
+        <v>-6.2040791143166193E-5</v>
       </c>
       <c r="AB31">
-        <v>2.5819594381777671E-3</v>
+        <v>-9.6865058397882763E-5</v>
       </c>
       <c r="AC31">
-        <v>-2.6107629693339482E-4</v>
+        <v>2.7938344532522927E-3</v>
       </c>
       <c r="AD31">
-        <v>-1.0982463197712714E-2</v>
+        <v>2.7978822254337409E-3</v>
       </c>
       <c r="AE31">
-        <v>-7.879032034509223E-4</v>
+        <v>2.8122138959540046E-3</v>
       </c>
       <c r="AF31">
-        <v>0.24905340225726197</v>
+        <v>4.7704975467675039E-3</v>
+      </c>
+      <c r="AG31">
+        <v>2.8034677158425805E-3</v>
+      </c>
+      <c r="AH31">
+        <v>2.7892516917618669E-3</v>
+      </c>
+      <c r="AI31">
+        <v>2.809454000652886E-3</v>
+      </c>
+      <c r="AJ31">
+        <v>2.8005363018920228E-3</v>
+      </c>
+      <c r="AK31">
+        <v>2.7867758135248707E-3</v>
+      </c>
+      <c r="AL31">
+        <v>2.8060971820213134E-3</v>
+      </c>
+      <c r="AM31">
+        <v>2.7926286351793086E-3</v>
+      </c>
+      <c r="AN31">
+        <v>2.7970571526103093E-3</v>
+      </c>
+      <c r="AO31">
+        <v>2.8033468256801926E-3</v>
+      </c>
+      <c r="AP31">
+        <v>-3.0278295306614324E-3</v>
+      </c>
+    </row>
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32">
+        <v>-0.14899383767970173</v>
+      </c>
+      <c r="C32">
+        <v>2.0004222741746143E-5</v>
+      </c>
+      <c r="D32">
+        <v>-1.4995529296624177E-5</v>
+      </c>
+      <c r="E32">
+        <v>2.5505135890218776E-7</v>
+      </c>
+      <c r="F32">
+        <v>1.8140607605269957E-4</v>
+      </c>
+      <c r="G32">
+        <v>9.3173130435845498E-7</v>
+      </c>
+      <c r="H32">
+        <v>1.8430231044319059E-4</v>
+      </c>
+      <c r="I32">
+        <v>-1.4884399641707565E-4</v>
+      </c>
+      <c r="J32">
+        <v>1.5445587154096175E-4</v>
+      </c>
+      <c r="K32">
+        <v>-3.8258627026767095E-5</v>
+      </c>
+      <c r="L32">
+        <v>3.1563677486416437E-5</v>
+      </c>
+      <c r="M32">
+        <v>8.8427619594778559E-5</v>
+      </c>
+      <c r="N32">
+        <v>2.2553842389188596E-5</v>
+      </c>
+      <c r="O32">
+        <v>5.7407714437415357E-5</v>
+      </c>
+      <c r="P32">
+        <v>1.5888366228743612E-4</v>
+      </c>
+      <c r="Q32">
+        <v>8.7438116574985354E-5</v>
+      </c>
+      <c r="R32">
+        <v>6.4144129479145858E-5</v>
+      </c>
+      <c r="S32">
+        <v>1.8535986158098989E-4</v>
+      </c>
+      <c r="T32">
+        <v>1.733331154990731E-5</v>
+      </c>
+      <c r="U32">
+        <v>1.6981086772963581E-4</v>
+      </c>
+      <c r="V32">
+        <v>9.0949698897917512E-5</v>
+      </c>
+      <c r="W32">
+        <v>2.0306690885231449E-4</v>
+      </c>
+      <c r="X32">
+        <v>2.2512109619011555E-4</v>
+      </c>
+      <c r="Y32">
+        <v>1.4180528153370689E-4</v>
+      </c>
+      <c r="Z32">
+        <v>-1.7982595831144804E-5</v>
+      </c>
+      <c r="AA32">
+        <v>6.4665043798398168E-5</v>
+      </c>
+      <c r="AB32">
+        <v>-9.0981278261641839E-5</v>
+      </c>
+      <c r="AC32">
+        <v>2.7947938118867356E-3</v>
+      </c>
+      <c r="AD32">
+        <v>2.798371457877123E-3</v>
+      </c>
+      <c r="AE32">
+        <v>2.8080899120969398E-3</v>
+      </c>
+      <c r="AF32">
+        <v>2.8034677158425805E-3</v>
+      </c>
+      <c r="AG32">
+        <v>5.3345056205678781E-3</v>
+      </c>
+      <c r="AH32">
+        <v>2.7981862478457576E-3</v>
+      </c>
+      <c r="AI32">
+        <v>2.8174268088397934E-3</v>
+      </c>
+      <c r="AJ32">
+        <v>2.807234602491139E-3</v>
+      </c>
+      <c r="AK32">
+        <v>2.7937178277389679E-3</v>
+      </c>
+      <c r="AL32">
+        <v>2.8219456100222629E-3</v>
+      </c>
+      <c r="AM32">
+        <v>2.8037468755655777E-3</v>
+      </c>
+      <c r="AN32">
+        <v>2.8067340603516689E-3</v>
+      </c>
+      <c r="AO32">
+        <v>2.8147786943018074E-3</v>
+      </c>
+      <c r="AP32">
+        <v>-2.7804765536355207E-3</v>
+      </c>
+    </row>
+    <row r="33" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>44</v>
+      </c>
+      <c r="B33">
+        <v>-6.04812098889876E-2</v>
+      </c>
+      <c r="C33">
+        <v>1.4649876089515727E-5</v>
+      </c>
+      <c r="D33">
+        <v>-5.5909991886769587E-5</v>
+      </c>
+      <c r="E33">
+        <v>9.4372926843673001E-7</v>
+      </c>
+      <c r="F33">
+        <v>-9.2841039450234936E-5</v>
+      </c>
+      <c r="G33">
+        <v>-7.3161646185764158E-6</v>
+      </c>
+      <c r="H33">
+        <v>1.3903663627384062E-4</v>
+      </c>
+      <c r="I33">
+        <v>1.0436353515452541E-4</v>
+      </c>
+      <c r="J33">
+        <v>3.1072551629293937E-5</v>
+      </c>
+      <c r="K33">
+        <v>1.5296807243682636E-5</v>
+      </c>
+      <c r="L33">
+        <v>4.2685896266316144E-5</v>
+      </c>
+      <c r="M33">
+        <v>9.8256598358846536E-5</v>
+      </c>
+      <c r="N33">
+        <v>6.4287552542194835E-5</v>
+      </c>
+      <c r="O33">
+        <v>-1.2616885342125366E-5</v>
+      </c>
+      <c r="P33">
+        <v>1.6095695695878464E-4</v>
+      </c>
+      <c r="Q33">
+        <v>9.9632230893494751E-5</v>
+      </c>
+      <c r="R33">
+        <v>1.2751112905863798E-4</v>
+      </c>
+      <c r="S33">
+        <v>8.3691610920700742E-5</v>
+      </c>
+      <c r="T33">
+        <v>-5.9298160870827022E-5</v>
+      </c>
+      <c r="U33">
+        <v>1.1883749501080871E-4</v>
+      </c>
+      <c r="V33">
+        <v>8.0479858898312769E-5</v>
+      </c>
+      <c r="W33">
+        <v>9.7790367365283752E-5</v>
+      </c>
+      <c r="X33">
+        <v>1.8785836796904798E-4</v>
+      </c>
+      <c r="Y33">
+        <v>7.8670555083259499E-5</v>
+      </c>
+      <c r="Z33">
+        <v>-9.8054533502596138E-6</v>
+      </c>
+      <c r="AA33">
+        <v>-1.6537909300323408E-4</v>
+      </c>
+      <c r="AB33">
+        <v>-1.6054321281455284E-4</v>
+      </c>
+      <c r="AC33">
+        <v>2.7871537314076208E-3</v>
+      </c>
+      <c r="AD33">
+        <v>2.7920832671859768E-3</v>
+      </c>
+      <c r="AE33">
+        <v>2.7967980318033647E-3</v>
+      </c>
+      <c r="AF33">
+        <v>2.7892516917618669E-3</v>
+      </c>
+      <c r="AG33">
+        <v>2.7981862478457576E-3</v>
+      </c>
+      <c r="AH33">
+        <v>5.4084014700862834E-3</v>
+      </c>
+      <c r="AI33">
+        <v>2.8059232765621097E-3</v>
+      </c>
+      <c r="AJ33">
+        <v>2.8147677317541305E-3</v>
+      </c>
+      <c r="AK33">
+        <v>2.7772598034579146E-3</v>
+      </c>
+      <c r="AL33">
+        <v>2.8035920220187104E-3</v>
+      </c>
+      <c r="AM33">
+        <v>2.8042635933217108E-3</v>
+      </c>
+      <c r="AN33">
+        <v>2.7878484632812769E-3</v>
+      </c>
+      <c r="AO33">
+        <v>2.7350048546795937E-3</v>
+      </c>
+      <c r="AP33">
+        <v>-2.1558277590149454E-3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>45</v>
+      </c>
+      <c r="B34">
+        <v>-0.1932393215395406</v>
+      </c>
+      <c r="C34">
+        <v>3.8804370643321105E-5</v>
+      </c>
+      <c r="D34">
+        <v>-3.6563505017555425E-5</v>
+      </c>
+      <c r="E34">
+        <v>6.3413159001905403E-7</v>
+      </c>
+      <c r="F34">
+        <v>3.3204683387832177E-4</v>
+      </c>
+      <c r="G34">
+        <v>4.0122703423495741E-5</v>
+      </c>
+      <c r="H34">
+        <v>-1.3912756673658015E-5</v>
+      </c>
+      <c r="I34">
+        <v>-1.6112883930819322E-4</v>
+      </c>
+      <c r="J34">
+        <v>1.725537363159689E-5</v>
+      </c>
+      <c r="K34">
+        <v>-3.2175113224578757E-5</v>
+      </c>
+      <c r="L34">
+        <v>-1.259806917185656E-5</v>
+      </c>
+      <c r="M34">
+        <v>2.0744591881098444E-5</v>
+      </c>
+      <c r="N34">
+        <v>1.5310477926092081E-6</v>
+      </c>
+      <c r="O34">
+        <v>3.0369908489851719E-4</v>
+      </c>
+      <c r="P34">
+        <v>1.624958308977804E-4</v>
+      </c>
+      <c r="Q34">
+        <v>7.6933662023978338E-5</v>
+      </c>
+      <c r="R34">
+        <v>2.1614045157685E-4</v>
+      </c>
+      <c r="S34">
+        <v>1.0224178545349704E-4</v>
+      </c>
+      <c r="T34">
+        <v>1.9815304664909557E-4</v>
+      </c>
+      <c r="U34">
+        <v>1.6537411036645364E-4</v>
+      </c>
+      <c r="V34">
+        <v>2.010058464021287E-4</v>
+      </c>
+      <c r="W34">
+        <v>2.322419260665082E-4</v>
+      </c>
+      <c r="X34">
+        <v>4.3959020936331565E-4</v>
+      </c>
+      <c r="Y34">
+        <v>2.3438448419749354E-4</v>
+      </c>
+      <c r="Z34">
+        <v>6.2954379101127058E-6</v>
+      </c>
+      <c r="AA34">
+        <v>-1.4137016628899921E-4</v>
+      </c>
+      <c r="AB34">
+        <v>-9.0173341301724843E-5</v>
+      </c>
+      <c r="AC34">
+        <v>2.7981909503284035E-3</v>
+      </c>
+      <c r="AD34">
+        <v>2.802926645939108E-3</v>
+      </c>
+      <c r="AE34">
+        <v>2.7998023826113117E-3</v>
+      </c>
+      <c r="AF34">
+        <v>2.809454000652886E-3</v>
+      </c>
+      <c r="AG34">
+        <v>2.8174268088397934E-3</v>
+      </c>
+      <c r="AH34">
+        <v>2.8059232765621097E-3</v>
+      </c>
+      <c r="AI34">
+        <v>6.1215685062393213E-3</v>
+      </c>
+      <c r="AJ34">
+        <v>2.8419282649502966E-3</v>
+      </c>
+      <c r="AK34">
+        <v>2.7851796125773669E-3</v>
+      </c>
+      <c r="AL34">
+        <v>2.8196601655474194E-3</v>
+      </c>
+      <c r="AM34">
+        <v>2.8445054409635172E-3</v>
+      </c>
+      <c r="AN34">
+        <v>2.8229303727496623E-3</v>
+      </c>
+      <c r="AO34">
+        <v>2.7053009103389543E-3</v>
+      </c>
+      <c r="AP34">
+        <v>-2.5293813266591718E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>46</v>
+      </c>
+      <c r="B35">
+        <v>-0.28937870058413306</v>
+      </c>
+      <c r="C35">
+        <v>8.783647549707519E-5</v>
+      </c>
+      <c r="D35">
+        <v>1.5202161530642778E-5</v>
+      </c>
+      <c r="E35">
+        <v>-3.9019777466520363E-7</v>
+      </c>
+      <c r="F35">
+        <v>2.723793467413263E-4</v>
+      </c>
+      <c r="G35">
+        <v>8.0121728651233806E-5</v>
+      </c>
+      <c r="H35">
+        <v>3.0000546713841725E-4</v>
+      </c>
+      <c r="I35">
+        <v>-2.665490913543022E-4</v>
+      </c>
+      <c r="J35">
+        <v>1.7380397806892808E-4</v>
+      </c>
+      <c r="K35">
+        <v>1.6763358653464934E-4</v>
+      </c>
+      <c r="L35">
+        <v>-8.4165941093897884E-5</v>
+      </c>
+      <c r="M35">
+        <v>-2.064096736118827E-5</v>
+      </c>
+      <c r="N35">
+        <v>-6.960616684839778E-5</v>
+      </c>
+      <c r="O35">
+        <v>2.1505759542186746E-4</v>
+      </c>
+      <c r="P35">
+        <v>5.867348019234029E-5</v>
+      </c>
+      <c r="Q35">
+        <v>3.9460230495682669E-4</v>
+      </c>
+      <c r="R35">
+        <v>1.0637346683165807E-4</v>
+      </c>
+      <c r="S35">
+        <v>3.3526067415163554E-4</v>
+      </c>
+      <c r="T35">
+        <v>7.6405101634254924E-5</v>
+      </c>
+      <c r="U35">
+        <v>8.2377089879363081E-5</v>
+      </c>
+      <c r="V35">
+        <v>3.1381260212924719E-4</v>
+      </c>
+      <c r="W35">
+        <v>1.3299822163657547E-4</v>
+      </c>
+      <c r="X35">
+        <v>3.2698336473956655E-4</v>
+      </c>
+      <c r="Y35">
+        <v>7.2498158909919995E-5</v>
+      </c>
+      <c r="Z35">
+        <v>1.1694831471503484E-4</v>
+      </c>
+      <c r="AA35">
+        <v>-1.2097113708995234E-4</v>
+      </c>
+      <c r="AB35">
+        <v>-2.1927322008343905E-4</v>
+      </c>
+      <c r="AC35">
+        <v>2.7959588382399326E-3</v>
+      </c>
+      <c r="AD35">
+        <v>2.7905655499360152E-3</v>
+      </c>
+      <c r="AE35">
+        <v>2.8038864714148466E-3</v>
+      </c>
+      <c r="AF35">
+        <v>2.8005363018920228E-3</v>
+      </c>
+      <c r="AG35">
+        <v>2.807234602491139E-3</v>
+      </c>
+      <c r="AH35">
+        <v>2.8147677317541305E-3</v>
+      </c>
+      <c r="AI35">
+        <v>2.8419282649502966E-3</v>
+      </c>
+      <c r="AJ35">
+        <v>6.9107127935787507E-3</v>
+      </c>
+      <c r="AK35">
+        <v>2.8255911645498925E-3</v>
+      </c>
+      <c r="AL35">
+        <v>2.8420611469023018E-3</v>
+      </c>
+      <c r="AM35">
+        <v>2.855838831918092E-3</v>
+      </c>
+      <c r="AN35">
+        <v>2.8212286645389615E-3</v>
+      </c>
+      <c r="AO35">
+        <v>2.8602383228067737E-3</v>
+      </c>
+      <c r="AP35">
+        <v>-3.2222788935626114E-3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>47</v>
+      </c>
+      <c r="B36">
+        <v>-5.480460334502156E-2</v>
+      </c>
+      <c r="C36">
+        <v>4.7995511203565377E-5</v>
+      </c>
+      <c r="D36">
+        <v>1.0934904013128882E-5</v>
+      </c>
+      <c r="E36">
+        <v>-2.4995715028938281E-7</v>
+      </c>
+      <c r="F36">
+        <v>3.4019014235276129E-4</v>
+      </c>
+      <c r="G36">
+        <v>1.9453057665350798E-5</v>
+      </c>
+      <c r="H36">
+        <v>1.880965996353557E-4</v>
+      </c>
+      <c r="I36">
+        <v>-3.2665423607252525E-4</v>
+      </c>
+      <c r="J36">
+        <v>-1.8628384327871225E-4</v>
+      </c>
+      <c r="K36">
+        <v>-1.4550526727856884E-4</v>
+      </c>
+      <c r="L36">
+        <v>-1.6535094387331358E-4</v>
+      </c>
+      <c r="M36">
+        <v>-8.8043006408054098E-5</v>
+      </c>
+      <c r="N36">
+        <v>-2.9315875440666037E-4</v>
+      </c>
+      <c r="O36">
+        <v>-6.4940322376040452E-5</v>
+      </c>
+      <c r="P36">
+        <v>-5.3963370825540168E-5</v>
+      </c>
+      <c r="Q36">
+        <v>-7.4057170780641134E-5</v>
+      </c>
+      <c r="R36">
+        <v>5.6130672978440491E-5</v>
+      </c>
+      <c r="S36">
+        <v>-6.9398955693350008E-5</v>
+      </c>
+      <c r="T36">
+        <v>-1.078488017600002E-5</v>
+      </c>
+      <c r="U36">
+        <v>-3.6219508769482801E-5</v>
+      </c>
+      <c r="V36">
+        <v>4.7694319335384126E-5</v>
+      </c>
+      <c r="W36">
+        <v>2.6142780263536339E-5</v>
+      </c>
+      <c r="X36">
+        <v>1.3697271737599798E-4</v>
+      </c>
+      <c r="Y36">
+        <v>-4.9212304672168437E-5</v>
+      </c>
+      <c r="Z36">
+        <v>-1.453065995145351E-4</v>
+      </c>
+      <c r="AA36">
+        <v>-1.868826381787931E-4</v>
+      </c>
+      <c r="AB36">
+        <v>5.7259898275580979E-4</v>
+      </c>
+      <c r="AC36">
+        <v>2.7856389699262192E-3</v>
+      </c>
+      <c r="AD36">
+        <v>2.7797938732662978E-3</v>
+      </c>
+      <c r="AE36">
+        <v>2.7700743811121219E-3</v>
+      </c>
+      <c r="AF36">
+        <v>2.7867758135248707E-3</v>
+      </c>
+      <c r="AG36">
+        <v>2.7937178277389679E-3</v>
+      </c>
+      <c r="AH36">
+        <v>2.7772598034579146E-3</v>
+      </c>
+      <c r="AI36">
+        <v>2.7851796125773669E-3</v>
+      </c>
+      <c r="AJ36">
+        <v>2.8255911645498925E-3</v>
+      </c>
+      <c r="AK36">
+        <v>6.087756881697149E-3</v>
+      </c>
+      <c r="AL36">
+        <v>2.8056826787257851E-3</v>
+      </c>
+      <c r="AM36">
+        <v>2.8195761717021367E-3</v>
+      </c>
+      <c r="AN36">
+        <v>2.777804468706813E-3</v>
+      </c>
+      <c r="AO36">
+        <v>2.7858183793778579E-3</v>
+      </c>
+      <c r="AP36">
+        <v>-2.7781111747519124E-3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>48</v>
+      </c>
+      <c r="B37">
+        <v>-9.5169165893101579E-2</v>
+      </c>
+      <c r="C37">
+        <v>2.5863602629088659E-5</v>
+      </c>
+      <c r="D37">
+        <v>-2.8845380680408636E-5</v>
+      </c>
+      <c r="E37">
+        <v>3.1910575266509678E-7</v>
+      </c>
+      <c r="F37">
+        <v>3.6075602653079953E-4</v>
+      </c>
+      <c r="G37">
+        <v>1.471616493165487E-4</v>
+      </c>
+      <c r="H37">
+        <v>8.6816632504247305E-5</v>
+      </c>
+      <c r="I37">
+        <v>-2.5722103043426467E-4</v>
+      </c>
+      <c r="J37">
+        <v>-4.7792762222859976E-5</v>
+      </c>
+      <c r="K37">
+        <v>-1.5534491934933968E-5</v>
+      </c>
+      <c r="L37">
+        <v>1.1756830425562609E-4</v>
+      </c>
+      <c r="M37">
+        <v>1.9737493857880338E-4</v>
+      </c>
+      <c r="N37">
+        <v>5.2927891228261685E-5</v>
+      </c>
+      <c r="O37">
+        <v>-3.4097706900666769E-6</v>
+      </c>
+      <c r="P37">
+        <v>2.4130729278264065E-4</v>
+      </c>
+      <c r="Q37">
+        <v>4.014360613573552E-4</v>
+      </c>
+      <c r="R37">
+        <v>6.7617957688943624E-5</v>
+      </c>
+      <c r="S37">
+        <v>9.5371269915595861E-5</v>
+      </c>
+      <c r="T37">
+        <v>1.0121783690703046E-4</v>
+      </c>
+      <c r="U37">
+        <v>7.5382926559541038E-5</v>
+      </c>
+      <c r="V37">
+        <v>3.0464728641229396E-4</v>
+      </c>
+      <c r="W37">
+        <v>2.6518210579589644E-4</v>
+      </c>
+      <c r="X37">
+        <v>2.7365750791416652E-4</v>
+      </c>
+      <c r="Y37">
+        <v>8.5715926743694252E-5</v>
+      </c>
+      <c r="Z37">
+        <v>-1.1636752989817589E-4</v>
+      </c>
+      <c r="AA37">
+        <v>-6.3127040317329398E-6</v>
+      </c>
+      <c r="AB37">
+        <v>-2.2543647945610256E-4</v>
+      </c>
+      <c r="AC37">
+        <v>2.7948626355866722E-3</v>
+      </c>
+      <c r="AD37">
+        <v>2.7967911155299145E-3</v>
+      </c>
+      <c r="AE37">
+        <v>2.7954647076284646E-3</v>
+      </c>
+      <c r="AF37">
+        <v>2.8060971820213134E-3</v>
+      </c>
+      <c r="AG37">
+        <v>2.8219456100222629E-3</v>
+      </c>
+      <c r="AH37">
+        <v>2.8035920220187104E-3</v>
+      </c>
+      <c r="AI37">
+        <v>2.8196601655474194E-3</v>
+      </c>
+      <c r="AJ37">
+        <v>2.8420611469023018E-3</v>
+      </c>
+      <c r="AK37">
+        <v>2.8056826787257851E-3</v>
+      </c>
+      <c r="AL37">
+        <v>6.3748578492801794E-3</v>
+      </c>
+      <c r="AM37">
+        <v>2.8617074894118693E-3</v>
+      </c>
+      <c r="AN37">
+        <v>2.8247217542899531E-3</v>
+      </c>
+      <c r="AO37">
+        <v>2.8383559760561256E-3</v>
+      </c>
+      <c r="AP37">
+        <v>-2.6322502850870148E-3</v>
+      </c>
+    </row>
+    <row r="38" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>49</v>
+      </c>
+      <c r="B38">
+        <v>-7.1576043753522806E-2</v>
+      </c>
+      <c r="C38">
+        <v>-1.2376637487951109E-4</v>
+      </c>
+      <c r="D38">
+        <v>1.3893432878530655E-4</v>
+      </c>
+      <c r="E38">
+        <v>-2.265882714184075E-6</v>
+      </c>
+      <c r="F38">
+        <v>6.8543040571977278E-4</v>
+      </c>
+      <c r="G38">
+        <v>2.0533844589095459E-4</v>
+      </c>
+      <c r="H38">
+        <v>1.6031937910752133E-4</v>
+      </c>
+      <c r="I38">
+        <v>-4.9771116396402429E-4</v>
+      </c>
+      <c r="J38">
+        <v>-3.420883685228901E-4</v>
+      </c>
+      <c r="K38">
+        <v>1.3323231265487036E-4</v>
+      </c>
+      <c r="L38">
+        <v>-7.0886701697830089E-5</v>
+      </c>
+      <c r="M38">
+        <v>-2.7130259746770396E-4</v>
+      </c>
+      <c r="N38">
+        <v>-2.6580397456910099E-4</v>
+      </c>
+      <c r="O38">
+        <v>-1.6657577601283252E-4</v>
+      </c>
+      <c r="P38">
+        <v>8.4483162783728985E-5</v>
+      </c>
+      <c r="Q38">
+        <v>-5.0510647529924783E-5</v>
+      </c>
+      <c r="R38">
+        <v>1.3852603806465726E-5</v>
+      </c>
+      <c r="S38">
+        <v>2.1248648945708924E-4</v>
+      </c>
+      <c r="T38">
+        <v>-1.0675186839905577E-4</v>
+      </c>
+      <c r="U38">
+        <v>2.1497535242427732E-5</v>
+      </c>
+      <c r="V38">
+        <v>1.1760027042182061E-4</v>
+      </c>
+      <c r="W38">
+        <v>2.5758220921477323E-4</v>
+      </c>
+      <c r="X38">
+        <v>7.854314535588494E-4</v>
+      </c>
+      <c r="Y38">
+        <v>-8.3712329792238766E-5</v>
+      </c>
+      <c r="Z38">
+        <v>-3.5705730854794987E-4</v>
+      </c>
+      <c r="AA38">
+        <v>-3.6139784449231506E-4</v>
+      </c>
+      <c r="AB38">
+        <v>-5.0629895511201614E-4</v>
+      </c>
+      <c r="AC38">
+        <v>2.807344597977374E-3</v>
+      </c>
+      <c r="AD38">
+        <v>2.8053571802248147E-3</v>
+      </c>
+      <c r="AE38">
+        <v>2.799875185711365E-3</v>
+      </c>
+      <c r="AF38">
+        <v>2.7926286351793086E-3</v>
+      </c>
+      <c r="AG38">
+        <v>2.8037468755655777E-3</v>
+      </c>
+      <c r="AH38">
+        <v>2.8042635933217108E-3</v>
+      </c>
+      <c r="AI38">
+        <v>2.8445054409635172E-3</v>
+      </c>
+      <c r="AJ38">
+        <v>2.855838831918092E-3</v>
+      </c>
+      <c r="AK38">
+        <v>2.8195761717021367E-3</v>
+      </c>
+      <c r="AL38">
+        <v>2.8617074894118693E-3</v>
+      </c>
+      <c r="AM38">
+        <v>7.2675185400153108E-3</v>
+      </c>
+      <c r="AN38">
+        <v>2.83432261567838E-3</v>
+      </c>
+      <c r="AO38">
+        <v>2.8441166573524267E-3</v>
+      </c>
+      <c r="AP38">
+        <v>-4.7774170183604928E-3</v>
+      </c>
+    </row>
+    <row r="39" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>50</v>
+      </c>
+      <c r="B39">
+        <v>-0.1114382609754147</v>
+      </c>
+      <c r="C39">
+        <v>-3.5963592568216901E-6</v>
+      </c>
+      <c r="D39">
+        <v>-5.3416192538011283E-5</v>
+      </c>
+      <c r="E39">
+        <v>8.1361826427441952E-7</v>
+      </c>
+      <c r="F39">
+        <v>1.3790508204609107E-4</v>
+      </c>
+      <c r="G39">
+        <v>1.3532117857273547E-6</v>
+      </c>
+      <c r="H39">
+        <v>-2.3696677730575657E-4</v>
+      </c>
+      <c r="I39">
+        <v>-2.6837823075678922E-4</v>
+      </c>
+      <c r="J39">
+        <v>6.5534582542681533E-6</v>
+      </c>
+      <c r="K39">
+        <v>-1.8202646069953761E-5</v>
+      </c>
+      <c r="L39">
+        <v>-8.5091522172746695E-5</v>
+      </c>
+      <c r="M39">
+        <v>-4.7014219085509019E-5</v>
+      </c>
+      <c r="N39">
+        <v>-1.1245674836937811E-4</v>
+      </c>
+      <c r="O39">
+        <v>-3.1483677810228853E-5</v>
+      </c>
+      <c r="P39">
+        <v>1.3479951180683466E-4</v>
+      </c>
+      <c r="Q39">
+        <v>1.6353820279961908E-4</v>
+      </c>
+      <c r="R39">
+        <v>7.5757804317568792E-5</v>
+      </c>
+      <c r="S39">
+        <v>4.0420432253620978E-4</v>
+      </c>
+      <c r="T39">
+        <v>1.136351337243035E-4</v>
+      </c>
+      <c r="U39">
+        <v>1.4277880949873961E-4</v>
+      </c>
+      <c r="V39">
+        <v>1.6631779816697568E-4</v>
+      </c>
+      <c r="W39">
+        <v>4.4105673409162278E-4</v>
+      </c>
+      <c r="X39">
+        <v>2.7528335927253953E-4</v>
+      </c>
+      <c r="Y39">
+        <v>9.3380854805229317E-5</v>
+      </c>
+      <c r="Z39">
+        <v>5.7797568376490488E-5</v>
+      </c>
+      <c r="AA39">
+        <v>4.7301250268515032E-4</v>
+      </c>
+      <c r="AB39">
+        <v>-6.8384123743197385E-5</v>
+      </c>
+      <c r="AC39">
+        <v>2.7890302827802563E-3</v>
+      </c>
+      <c r="AD39">
+        <v>2.7844917204466694E-3</v>
+      </c>
+      <c r="AE39">
+        <v>2.7817040956983194E-3</v>
+      </c>
+      <c r="AF39">
+        <v>2.7970571526103093E-3</v>
+      </c>
+      <c r="AG39">
+        <v>2.8067340603516689E-3</v>
+      </c>
+      <c r="AH39">
+        <v>2.7878484632812769E-3</v>
+      </c>
+      <c r="AI39">
+        <v>2.8229303727496623E-3</v>
+      </c>
+      <c r="AJ39">
+        <v>2.8212286645389615E-3</v>
+      </c>
+      <c r="AK39">
+        <v>2.777804468706813E-3</v>
+      </c>
+      <c r="AL39">
+        <v>2.8247217542899531E-3</v>
+      </c>
+      <c r="AM39">
+        <v>2.83432261567838E-3</v>
+      </c>
+      <c r="AN39">
+        <v>7.0962296930525406E-3</v>
+      </c>
+      <c r="AO39">
+        <v>2.6518273538886777E-3</v>
+      </c>
+      <c r="AP39">
+        <v>-2.0754509439134452E-3</v>
+      </c>
+    </row>
+    <row r="40" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>51</v>
+      </c>
+      <c r="B40">
+        <v>-0.35118935533852574</v>
+      </c>
+      <c r="C40">
+        <v>1.3509571378930317E-4</v>
+      </c>
+      <c r="D40">
+        <v>8.0277675077015248E-5</v>
+      </c>
+      <c r="E40">
+        <v>-1.5675230351619549E-6</v>
+      </c>
+      <c r="F40">
+        <v>8.5273610688927845E-4</v>
+      </c>
+      <c r="G40">
+        <v>8.5425961333449214E-4</v>
+      </c>
+      <c r="H40">
+        <v>1.2524687784377236E-4</v>
+      </c>
+      <c r="I40">
+        <v>-3.9039734697497372E-4</v>
+      </c>
+      <c r="J40">
+        <v>-3.6729874495605372E-4</v>
+      </c>
+      <c r="K40">
+        <v>-3.1383857833337803E-4</v>
+      </c>
+      <c r="L40">
+        <v>-2.138436910267133E-6</v>
+      </c>
+      <c r="M40">
+        <v>8.0999524739723203E-4</v>
+      </c>
+      <c r="N40">
+        <v>-4.18941376147626E-4</v>
+      </c>
+      <c r="O40">
+        <v>1.8906649392489445E-3</v>
+      </c>
+      <c r="P40">
+        <v>1.9807767901645641E-3</v>
+      </c>
+      <c r="Q40">
+        <v>6.0398932375780277E-4</v>
+      </c>
+      <c r="R40">
+        <v>4.4231807610293963E-4</v>
+      </c>
+      <c r="S40">
+        <v>8.9499919287356917E-4</v>
+      </c>
+      <c r="T40">
+        <v>3.7944698820241429E-4</v>
+      </c>
+      <c r="U40">
+        <v>1.3971079436535926E-3</v>
+      </c>
+      <c r="V40">
+        <v>3.7247775096117298E-4</v>
+      </c>
+      <c r="W40">
+        <v>4.1579308905015031E-4</v>
+      </c>
+      <c r="X40">
+        <v>3.7985727573123899E-4</v>
+      </c>
+      <c r="Y40">
+        <v>1.2002889366924379E-3</v>
+      </c>
+      <c r="Z40">
+        <v>-6.9522810621687903E-4</v>
+      </c>
+      <c r="AA40">
+        <v>5.334419155189069E-3</v>
+      </c>
+      <c r="AB40">
+        <v>-6.359847200000312E-4</v>
+      </c>
+      <c r="AC40">
+        <v>2.7653074056122086E-3</v>
+      </c>
+      <c r="AD40">
+        <v>2.7372169113132859E-3</v>
+      </c>
+      <c r="AE40">
+        <v>2.7123875480151126E-3</v>
+      </c>
+      <c r="AF40">
+        <v>2.8033468256801926E-3</v>
+      </c>
+      <c r="AG40">
+        <v>2.8147786943018074E-3</v>
+      </c>
+      <c r="AH40">
+        <v>2.7350048546795937E-3</v>
+      </c>
+      <c r="AI40">
+        <v>2.7053009103389543E-3</v>
+      </c>
+      <c r="AJ40">
+        <v>2.8602383228067737E-3</v>
+      </c>
+      <c r="AK40">
+        <v>2.7858183793778579E-3</v>
+      </c>
+      <c r="AL40">
+        <v>2.8383559760561256E-3</v>
+      </c>
+      <c r="AM40">
+        <v>2.8441166573524267E-3</v>
+      </c>
+      <c r="AN40">
+        <v>2.6518273538886777E-3</v>
+      </c>
+      <c r="AO40">
+        <v>1.6718918145613094E-2</v>
+      </c>
+      <c r="AP40">
+        <v>-5.350167022283036E-3</v>
+      </c>
+    </row>
+    <row r="41" spans="1:42" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41">
+        <v>-3.9035308926357573</v>
+      </c>
+      <c r="C41">
+        <v>4.5561383890587847E-4</v>
+      </c>
+      <c r="D41">
+        <v>-1.8380139386570998E-2</v>
+      </c>
+      <c r="E41">
+        <v>3.3475279048161117E-4</v>
+      </c>
+      <c r="F41">
+        <v>-1.1668539620610523E-2</v>
+      </c>
+      <c r="G41">
+        <v>-8.1730895959561175E-3</v>
+      </c>
+      <c r="H41">
+        <v>-1.0324638928380625E-2</v>
+      </c>
+      <c r="I41">
+        <v>-1.2642002368749055E-2</v>
+      </c>
+      <c r="J41">
+        <v>-1.0449555467615017E-2</v>
+      </c>
+      <c r="K41">
+        <v>-1.2429016341074498E-2</v>
+      </c>
+      <c r="L41">
+        <v>-1.227583196286604E-2</v>
+      </c>
+      <c r="M41">
+        <v>-1.2135560927561734E-2</v>
+      </c>
+      <c r="N41">
+        <v>-1.4122897017889163E-2</v>
+      </c>
+      <c r="O41">
+        <v>-7.5941362888467812E-3</v>
+      </c>
+      <c r="P41">
+        <v>-6.474054926744922E-3</v>
+      </c>
+      <c r="Q41">
+        <v>-8.0770417159786098E-3</v>
+      </c>
+      <c r="R41">
+        <v>-6.5461510893532471E-3</v>
+      </c>
+      <c r="S41">
+        <v>-5.947665373213824E-3</v>
+      </c>
+      <c r="T41">
+        <v>-7.1529429852400118E-3</v>
+      </c>
+      <c r="U41">
+        <v>-6.9663188088251804E-3</v>
+      </c>
+      <c r="V41">
+        <v>-7.4122159488518059E-3</v>
+      </c>
+      <c r="W41">
+        <v>-6.3353044574033669E-3</v>
+      </c>
+      <c r="X41">
+        <v>-8.9143066260666572E-3</v>
+      </c>
+      <c r="Y41">
+        <v>-4.8076095563179032E-3</v>
+      </c>
+      <c r="Z41">
+        <v>-1.0085313309827234E-3</v>
+      </c>
+      <c r="AA41">
+        <v>-9.2713739123573401E-3</v>
+      </c>
+      <c r="AB41">
+        <v>-9.3709279834130175E-4</v>
+      </c>
+      <c r="AC41">
+        <v>-2.1694029751480395E-3</v>
+      </c>
+      <c r="AD41">
+        <v>-2.2228187633354362E-3</v>
+      </c>
+      <c r="AE41">
+        <v>-3.2155995597387948E-3</v>
+      </c>
+      <c r="AF41">
+        <v>-3.0278295306614324E-3</v>
+      </c>
+      <c r="AG41">
+        <v>-2.7804765536355207E-3</v>
+      </c>
+      <c r="AH41">
+        <v>-2.1558277590149454E-3</v>
+      </c>
+      <c r="AI41">
+        <v>-2.5293813266591718E-3</v>
+      </c>
+      <c r="AJ41">
+        <v>-3.2222788935626114E-3</v>
+      </c>
+      <c r="AK41">
+        <v>-2.7781111747519124E-3</v>
+      </c>
+      <c r="AL41">
+        <v>-2.6322502850870148E-3</v>
+      </c>
+      <c r="AM41">
+        <v>-4.7774170183604928E-3</v>
+      </c>
+      <c r="AN41">
+        <v>-2.0754509439134452E-3</v>
+      </c>
+      <c r="AO41">
+        <v>-5.350167022283036E-3</v>
+      </c>
+      <c r="AP41">
+        <v>0.27096580578731977</v>
       </c>
     </row>
   </sheetData>
